--- a/documents/STI2004-pinout-check.xlsx
+++ b/documents/STI2004-pinout-check.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="484">
   <si>
     <t>Status</t>
   </si>
@@ -166,6 +166,9 @@
     <t>EN(STi)-21</t>
   </si>
   <si>
+    <t>Harness side is grounded at engine ground GE-1 (WI-77)</t>
+  </si>
+  <si>
     <t>D4</t>
   </si>
   <si>
@@ -451,543 +454,546 @@
     <t>(not in I/O table)</t>
   </si>
   <si>
+    <t>WI-112</t>
+  </si>
+  <si>
+    <t>Not in the FSM I/O table; see note; Red/white wire to data link connector pin 6 (WI-112); function not in the I/O table. Leave unconnected.</t>
+  </si>
+  <si>
+    <t>D30</t>
+  </si>
+  <si>
+    <t>D31</t>
+  </si>
+  <si>
+    <t>Rear oxygen sensor shield</t>
+  </si>
+  <si>
+    <t>shield</t>
+  </si>
+  <si>
+    <t>B136</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>Fuel injector #4</t>
+  </si>
+  <si>
+    <t>injector low-side</t>
+  </si>
+  <si>
+    <t>OUT_INJ4</t>
+  </si>
+  <si>
+    <t>Q4.D_2</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>Fuel injector #3</t>
+  </si>
+  <si>
+    <t>OUT_INJ3</t>
+  </si>
+  <si>
+    <t>Q3.D_2</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>Fuel injector #2</t>
+  </si>
+  <si>
+    <t>OUT_INJ2</t>
+  </si>
+  <si>
+    <t>Q2.D_2</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>Fuel injector #1</t>
+  </si>
+  <si>
+    <t>OUT_INJ1</t>
+  </si>
+  <si>
+    <t>Q1.D_2</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>Cruise main switch</t>
+  </si>
+  <si>
+    <t>EN(STi)-22</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>Brake switch 2</t>
+  </si>
+  <si>
+    <t>pressed 10-13 / released 0</t>
+  </si>
+  <si>
+    <t>pressed 13-14 / released 0</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>Brake switch 1</t>
+  </si>
+  <si>
+    <t>pressed 0 / released 10-13</t>
+  </si>
+  <si>
+    <t>pressed 0 / released 13-14</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>RESUME/ACCEL switch</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>SET/COAST switch</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>Fuel temperature sensor signal</t>
+  </si>
+  <si>
+    <t>analog in (thermistor)</t>
+  </si>
+  <si>
+    <t>2.5-3.8</t>
+  </si>
+  <si>
+    <t>At 25 C</t>
+  </si>
+  <si>
+    <t>C13</t>
+  </si>
+  <si>
+    <t>Intake air temperature sensor signal</t>
+  </si>
+  <si>
+    <t>0.3-4.6</t>
+  </si>
+  <si>
+    <t>IN_IAT</t>
+  </si>
+  <si>
+    <t>M1.IN_IAT_S26</t>
+  </si>
+  <si>
+    <t>In the MAF housing</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>Engine coolant temperature sensor signal</t>
+  </si>
+  <si>
+    <t>1.0-1.4</t>
+  </si>
+  <si>
+    <t>IN_ECT</t>
+  </si>
+  <si>
+    <t>M1.IN_CLT_S28</t>
+  </si>
+  <si>
+    <t>After warm-up</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>Accelerator position sensor power supply</t>
+  </si>
+  <si>
+    <t>5 V sensor supply out</t>
+  </si>
+  <si>
+    <t>APS_PS_5V</t>
+  </si>
+  <si>
+    <t>+5VAS</t>
+  </si>
+  <si>
+    <t>M14.5VP_V4</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>Sensor power supply</t>
+  </si>
+  <si>
+    <t>5v OUT SENSOR_PS_5V</t>
+  </si>
+  <si>
+    <t>SENSOR_PS_5V</t>
+  </si>
+  <si>
+    <t>Feeds throttle TPS; MAP; TGV sensors</t>
+  </si>
+  <si>
+    <t>C17</t>
+  </si>
+  <si>
+    <t>Accelerator position sensor main</t>
+  </si>
+  <si>
+    <t>analog in</t>
+  </si>
+  <si>
+    <t>closed 1 / open 3.5</t>
+  </si>
+  <si>
+    <t>IN_APS_MAIN</t>
+  </si>
+  <si>
+    <t>IN_PPS_MAIN</t>
+  </si>
+  <si>
+    <t>M1.IN_PPS_S31</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>Electric throttle main (TPS1)</t>
+  </si>
+  <si>
+    <t>0.64-0.72 / open 3.96</t>
+  </si>
+  <si>
+    <t>0.64-0.72</t>
+  </si>
+  <si>
+    <t>IN_TPS_MAIN</t>
+  </si>
+  <si>
+    <t>M1.IN_TPS_S30</t>
+  </si>
+  <si>
+    <t>C19</t>
+  </si>
+  <si>
+    <t>C20</t>
+  </si>
+  <si>
+    <t>Fuel level sensor</t>
+  </si>
+  <si>
+    <t>0.12-4.75</t>
+  </si>
+  <si>
+    <t>IN_FUEL_LEVEL</t>
+  </si>
+  <si>
+    <t>C21</t>
+  </si>
+  <si>
+    <t>Fuel tank pressure sensor signal</t>
+  </si>
+  <si>
+    <t>2.3-2.7</t>
+  </si>
+  <si>
+    <t>C22</t>
+  </si>
+  <si>
+    <t>Manifold absolute pressure sensor signal</t>
+  </si>
+  <si>
+    <t>1.7-2.4</t>
+  </si>
+  <si>
+    <t>1.1-1.6</t>
+  </si>
+  <si>
+    <t>C23</t>
+  </si>
+  <si>
+    <t>Mass air flow sensor signal</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>0.3-4.5</t>
+  </si>
+  <si>
+    <t>IN_MAP</t>
+  </si>
+  <si>
+    <t>M1.IN_MAP1_S21</t>
+  </si>
+  <si>
+    <t>Expected a net matching 'MAF'</t>
+  </si>
+  <si>
+    <t>C24</t>
+  </si>
+  <si>
+    <t>C25</t>
+  </si>
+  <si>
+    <t>Knock sensor signal</t>
+  </si>
+  <si>
+    <t>knock in</t>
+  </si>
+  <si>
+    <t>IN_KNOCK_RAW</t>
+  </si>
+  <si>
+    <t>M13.IN_KNOCK_W1</t>
+  </si>
+  <si>
+    <t>C26</t>
+  </si>
+  <si>
+    <t>Tumble generator valve position sensor LH</t>
+  </si>
+  <si>
+    <t>closed 3.8-4.9 / open 0.2-0.9</t>
+  </si>
+  <si>
+    <t>same</t>
+  </si>
+  <si>
+    <t>IN_TUMBLE_SENSOR_LH</t>
+  </si>
+  <si>
+    <t>C27</t>
+  </si>
+  <si>
+    <t>Tumble generator valve position sensor RH</t>
+  </si>
+  <si>
+    <t>IN_TUMBLE_SENSOR_RH</t>
+  </si>
+  <si>
+    <t>C28</t>
+  </si>
+  <si>
+    <t>Accelerator position sensor sub</t>
+  </si>
+  <si>
+    <t>IN_APS_SUB</t>
+  </si>
+  <si>
+    <t>IN_PPS_SUB</t>
+  </si>
+  <si>
+    <t>M1.IN_PPS2_S33</t>
+  </si>
+  <si>
+    <t>C29</t>
+  </si>
+  <si>
+    <t>Electric throttle sub (TPS2)</t>
+  </si>
+  <si>
+    <t>1.51-1.58 / open 4.17</t>
+  </si>
+  <si>
+    <t>1.51-1.58</t>
+  </si>
+  <si>
+    <t>IN_TPS_SUB</t>
+  </si>
+  <si>
+    <t>M1.IN_TPS2_S32</t>
+  </si>
+  <si>
+    <t>C30</t>
+  </si>
+  <si>
+    <t>C31</t>
+  </si>
+  <si>
+    <t>Mass air flow sensor GND</t>
+  </si>
+  <si>
+    <t>C32</t>
+  </si>
+  <si>
+    <t>Mass air flow sensor shield</t>
+  </si>
+  <si>
+    <t>C33</t>
+  </si>
+  <si>
+    <t>Knock sensor shield</t>
+  </si>
+  <si>
+    <t>C34</t>
+  </si>
+  <si>
+    <t>Accelerator position sensor GND (sensor)</t>
+  </si>
+  <si>
+    <t>APS_GND</t>
+  </si>
+  <si>
+    <t>C35</t>
+  </si>
+  <si>
+    <t>GND (sensor)</t>
+  </si>
+  <si>
+    <t>Return for ECT; rear O2; TGV; MAP; fuel tank pressure</t>
+  </si>
+  <si>
+    <t>B135</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>GND (power supply)</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>Rear oxygen sensor heater signal</t>
+  </si>
+  <si>
+    <t>heater low-side</t>
+  </si>
+  <si>
+    <t>0-1.0</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>B5</t>
+  </si>
+  <si>
+    <t>Control unit power supply</t>
+  </si>
+  <si>
+    <t>12 V in (main relay)</t>
+  </si>
+  <si>
+    <t>12V IN</t>
+  </si>
+  <si>
+    <t>+12V_RAW</t>
+  </si>
+  <si>
+    <t>B6</t>
+  </si>
+  <si>
+    <t>B7</t>
+  </si>
+  <si>
+    <t>B8</t>
+  </si>
+  <si>
+    <t>Camshaft position sensor (LH)</t>
+  </si>
+  <si>
+    <t>cam sensor in</t>
+  </si>
+  <si>
+    <t>ON 0 / OFF 4.7-5.3</t>
+  </si>
+  <si>
+    <t>Sensor output waveform</t>
+  </si>
+  <si>
+    <t>IN_CAM_HALL_CAM_LH</t>
+  </si>
+  <si>
+    <t>M6.VR+_W2</t>
+  </si>
+  <si>
+    <t>B9</t>
+  </si>
+  <si>
+    <t>Camshaft position sensor (RH)</t>
+  </si>
+  <si>
+    <t>IN_CAM_HALL_CAM_RH</t>
+  </si>
+  <si>
+    <t>B10</t>
+  </si>
+  <si>
+    <t>Crankshaft position sensor signal (+)</t>
+  </si>
+  <si>
+    <t>VR in</t>
+  </si>
+  <si>
+    <t>-7 to +7</t>
+  </si>
+  <si>
+    <t>IN_CRANK+</t>
+  </si>
+  <si>
+    <t>M5.VR+_W2</t>
+  </si>
+  <si>
+    <t>B11</t>
+  </si>
+  <si>
+    <t>B12</t>
+  </si>
+  <si>
+    <t>GND (ignition system)</t>
+  </si>
+  <si>
+    <t>B13</t>
+  </si>
+  <si>
+    <t>B14</t>
+  </si>
+  <si>
+    <t>B15</t>
+  </si>
+  <si>
+    <t>Ignition control #4</t>
+  </si>
+  <si>
+    <t>igniter output</t>
+  </si>
+  <si>
     <t>WI-107</t>
   </si>
   <si>
-    <t>Not in the FSM I/O table; see note; Wiring diagram shows a line from D29 toward the data link connector</t>
-  </si>
-  <si>
-    <t>D30</t>
-  </si>
-  <si>
-    <t>D31</t>
-  </si>
-  <si>
-    <t>Rear oxygen sensor shield</t>
-  </si>
-  <si>
-    <t>shield</t>
-  </si>
-  <si>
-    <t>B136</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>Fuel injector #4</t>
-  </si>
-  <si>
-    <t>injector low-side</t>
-  </si>
-  <si>
-    <t>OUT_INJ4</t>
-  </si>
-  <si>
-    <t>Q4.D_2</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>Fuel injector #3</t>
-  </si>
-  <si>
-    <t>OUT_INJ3</t>
-  </si>
-  <si>
-    <t>Q3.D_2</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>Fuel injector #2</t>
-  </si>
-  <si>
-    <t>OUT_INJ2</t>
-  </si>
-  <si>
-    <t>Q2.D_2</t>
-  </si>
-  <si>
-    <t>C6</t>
-  </si>
-  <si>
-    <t>Fuel injector #1</t>
-  </si>
-  <si>
-    <t>OUT_INJ1</t>
-  </si>
-  <si>
-    <t>Q1.D_2</t>
-  </si>
-  <si>
-    <t>C7</t>
-  </si>
-  <si>
-    <t>Cruise main switch</t>
-  </si>
-  <si>
-    <t>EN(STi)-22</t>
-  </si>
-  <si>
-    <t>C8</t>
-  </si>
-  <si>
-    <t>Brake switch 2</t>
-  </si>
-  <si>
-    <t>pressed 10-13 / released 0</t>
-  </si>
-  <si>
-    <t>pressed 13-14 / released 0</t>
-  </si>
-  <si>
-    <t>C9</t>
-  </si>
-  <si>
-    <t>Brake switch 1</t>
-  </si>
-  <si>
-    <t>pressed 0 / released 10-13</t>
-  </si>
-  <si>
-    <t>pressed 0 / released 13-14</t>
-  </si>
-  <si>
-    <t>C10</t>
-  </si>
-  <si>
-    <t>RESUME/ACCEL switch</t>
-  </si>
-  <si>
-    <t>C11</t>
-  </si>
-  <si>
-    <t>SET/COAST switch</t>
-  </si>
-  <si>
-    <t>C12</t>
-  </si>
-  <si>
-    <t>Fuel temperature sensor signal</t>
-  </si>
-  <si>
-    <t>analog in (thermistor)</t>
-  </si>
-  <si>
-    <t>2.5-3.8</t>
-  </si>
-  <si>
-    <t>At 25 C</t>
-  </si>
-  <si>
-    <t>C13</t>
-  </si>
-  <si>
-    <t>Intake air temperature sensor signal</t>
-  </si>
-  <si>
-    <t>0.3-4.6</t>
-  </si>
-  <si>
-    <t>IN_IAT</t>
-  </si>
-  <si>
-    <t>M1.IN_IAT_S26</t>
-  </si>
-  <si>
-    <t>In the MAF housing</t>
-  </si>
-  <si>
-    <t>C14</t>
-  </si>
-  <si>
-    <t>Engine coolant temperature sensor signal</t>
-  </si>
-  <si>
-    <t>1.0-1.4</t>
-  </si>
-  <si>
-    <t>IN_ECT</t>
-  </si>
-  <si>
-    <t>M1.IN_CLT_S28</t>
-  </si>
-  <si>
-    <t>After warm-up</t>
-  </si>
-  <si>
-    <t>C15</t>
-  </si>
-  <si>
-    <t>Accelerator position sensor power supply</t>
-  </si>
-  <si>
-    <t>5 V sensor supply out</t>
-  </si>
-  <si>
-    <t>APS_PS_5V</t>
-  </si>
-  <si>
-    <t>+5VAS</t>
-  </si>
-  <si>
-    <t>M14.5VP_V4</t>
-  </si>
-  <si>
-    <t>C16</t>
-  </si>
-  <si>
-    <t>Sensor power supply</t>
-  </si>
-  <si>
-    <t>5v OUT SENSOR_PS_5V</t>
-  </si>
-  <si>
-    <t>SENSOR_PS_5V</t>
-  </si>
-  <si>
-    <t>Feeds throttle TPS; MAP; TGV sensors</t>
-  </si>
-  <si>
-    <t>C17</t>
-  </si>
-  <si>
-    <t>Accelerator position sensor main</t>
-  </si>
-  <si>
-    <t>analog in</t>
-  </si>
-  <si>
-    <t>closed 1 / open 3.5</t>
-  </si>
-  <si>
-    <t>IN_APS_MAIN</t>
-  </si>
-  <si>
-    <t>IN_PPS_MAIN</t>
-  </si>
-  <si>
-    <t>M1.IN_PPS_S31</t>
-  </si>
-  <si>
-    <t>C18</t>
-  </si>
-  <si>
-    <t>Electric throttle main (TPS1)</t>
-  </si>
-  <si>
-    <t>0.64-0.72 / open 3.96</t>
-  </si>
-  <si>
-    <t>0.64-0.72</t>
-  </si>
-  <si>
-    <t>IN_TPS_MAIN</t>
-  </si>
-  <si>
-    <t>M1.IN_TPS_S30</t>
-  </si>
-  <si>
-    <t>C19</t>
-  </si>
-  <si>
-    <t>C20</t>
-  </si>
-  <si>
-    <t>Fuel level sensor</t>
-  </si>
-  <si>
-    <t>0.12-4.75</t>
-  </si>
-  <si>
-    <t>IN_FUEL_LEVEL</t>
-  </si>
-  <si>
-    <t>C21</t>
-  </si>
-  <si>
-    <t>Fuel tank pressure sensor signal</t>
-  </si>
-  <si>
-    <t>2.3-2.7</t>
-  </si>
-  <si>
-    <t>C22</t>
-  </si>
-  <si>
-    <t>Manifold absolute pressure sensor signal</t>
-  </si>
-  <si>
-    <t>1.7-2.4</t>
-  </si>
-  <si>
-    <t>1.1-1.6</t>
-  </si>
-  <si>
-    <t>C23</t>
-  </si>
-  <si>
-    <t>Mass air flow sensor signal</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>0.3-4.5</t>
-  </si>
-  <si>
-    <t>IN_MAP</t>
-  </si>
-  <si>
-    <t>M1.IN_MAP1_S21</t>
-  </si>
-  <si>
-    <t>Expected a net matching 'MAF'</t>
-  </si>
-  <si>
-    <t>C24</t>
-  </si>
-  <si>
-    <t>C25</t>
-  </si>
-  <si>
-    <t>Knock sensor signal</t>
-  </si>
-  <si>
-    <t>knock in</t>
-  </si>
-  <si>
-    <t>IN_KNOCK_RAW</t>
-  </si>
-  <si>
-    <t>M13.IN_KNOCK_W1</t>
-  </si>
-  <si>
-    <t>C26</t>
-  </si>
-  <si>
-    <t>Tumble generator valve position sensor LH</t>
-  </si>
-  <si>
-    <t>closed 3.8-4.9 / open 0.2-0.9</t>
-  </si>
-  <si>
-    <t>same</t>
-  </si>
-  <si>
-    <t>IN_TUMBLE_SENSOR_LH</t>
-  </si>
-  <si>
-    <t>C27</t>
-  </si>
-  <si>
-    <t>Tumble generator valve position sensor RH</t>
-  </si>
-  <si>
-    <t>IN_TUMBLE_SENSOR_RH</t>
-  </si>
-  <si>
-    <t>C28</t>
-  </si>
-  <si>
-    <t>Accelerator position sensor sub</t>
-  </si>
-  <si>
-    <t>IN_APS_SUB</t>
-  </si>
-  <si>
-    <t>IN_PPS_SUB</t>
-  </si>
-  <si>
-    <t>M1.IN_PPS2_S33</t>
-  </si>
-  <si>
-    <t>C29</t>
-  </si>
-  <si>
-    <t>Electric throttle sub (TPS2)</t>
-  </si>
-  <si>
-    <t>1.51-1.58 / open 4.17</t>
-  </si>
-  <si>
-    <t>1.51-1.58</t>
-  </si>
-  <si>
-    <t>IN_TPS_SUB</t>
-  </si>
-  <si>
-    <t>M1.IN_TPS2_S32</t>
-  </si>
-  <si>
-    <t>C30</t>
-  </si>
-  <si>
-    <t>C31</t>
-  </si>
-  <si>
-    <t>Mass air flow sensor GND</t>
-  </si>
-  <si>
-    <t>C32</t>
-  </si>
-  <si>
-    <t>Mass air flow sensor shield</t>
-  </si>
-  <si>
-    <t>C33</t>
-  </si>
-  <si>
-    <t>Knock sensor shield</t>
-  </si>
-  <si>
-    <t>C34</t>
-  </si>
-  <si>
-    <t>Accelerator position sensor GND (sensor)</t>
-  </si>
-  <si>
-    <t>APS_GND</t>
-  </si>
-  <si>
-    <t>C35</t>
-  </si>
-  <si>
-    <t>GND (sensor)</t>
-  </si>
-  <si>
-    <t>Return for ECT; rear O2; TGV; MAP; fuel tank pressure</t>
-  </si>
-  <si>
-    <t>B135</t>
-  </si>
-  <si>
-    <t>B1</t>
-  </si>
-  <si>
-    <t>GND (power supply)</t>
-  </si>
-  <si>
-    <t>B2</t>
-  </si>
-  <si>
-    <t>Rear oxygen sensor heater signal</t>
-  </si>
-  <si>
-    <t>heater low-side</t>
-  </si>
-  <si>
-    <t>0-1.0</t>
-  </si>
-  <si>
-    <t>B3</t>
-  </si>
-  <si>
-    <t>B4</t>
-  </si>
-  <si>
-    <t>B5</t>
-  </si>
-  <si>
-    <t>Control unit power supply</t>
-  </si>
-  <si>
-    <t>12 V in (main relay)</t>
-  </si>
-  <si>
-    <t>12V IN</t>
-  </si>
-  <si>
-    <t>+12V_RAW</t>
-  </si>
-  <si>
-    <t>B6</t>
-  </si>
-  <si>
-    <t>B7</t>
-  </si>
-  <si>
-    <t>B8</t>
-  </si>
-  <si>
-    <t>Camshaft position sensor (LH)</t>
-  </si>
-  <si>
-    <t>cam sensor in</t>
-  </si>
-  <si>
-    <t>ON 0 / OFF 4.7-5.3</t>
-  </si>
-  <si>
-    <t>Sensor output waveform</t>
-  </si>
-  <si>
-    <t>IN_CAM_HALL_CAM_LH</t>
-  </si>
-  <si>
-    <t>M6.VR+_W2</t>
-  </si>
-  <si>
-    <t>B9</t>
-  </si>
-  <si>
-    <t>Camshaft position sensor (RH)</t>
-  </si>
-  <si>
-    <t>IN_CAM_HALL_CAM_RH</t>
-  </si>
-  <si>
-    <t>B10</t>
-  </si>
-  <si>
-    <t>Crankshaft position sensor signal (+)</t>
-  </si>
-  <si>
-    <t>VR in</t>
-  </si>
-  <si>
-    <t>-7 to +7</t>
-  </si>
-  <si>
-    <t>IN_CRANK+</t>
-  </si>
-  <si>
-    <t>M5.VR+_W2</t>
-  </si>
-  <si>
-    <t>B11</t>
-  </si>
-  <si>
-    <t>B12</t>
-  </si>
-  <si>
-    <t>GND (ignition system)</t>
-  </si>
-  <si>
-    <t>B13</t>
-  </si>
-  <si>
-    <t>B14</t>
-  </si>
-  <si>
-    <t>B15</t>
-  </si>
-  <si>
-    <t>Ignition control #4</t>
-  </si>
-  <si>
-    <t>igniter output</t>
-  </si>
-  <si>
     <t>Net-(F1-Pad1)</t>
   </si>
   <si>
@@ -1201,12 +1207,18 @@
     <t>Front A/F sensor heater signal 2</t>
   </si>
   <si>
+    <t>Joined with A3 in the harness to A/F heater B18 pin 1 (WI-113); heater +12 V comes from the main relay</t>
+  </si>
+  <si>
     <t>A3</t>
   </si>
   <si>
     <t>Front A/F sensor heater signal 1</t>
   </si>
   <si>
+    <t>Joined with A2 in the harness to A/F heater B18 pin 1 (WI-113)</t>
+  </si>
+  <si>
     <t>A4</t>
   </si>
   <si>
@@ -1342,6 +1354,15 @@
     <t>A22</t>
   </si>
   <si>
+    <t>(not in I/O table) wire to charging system</t>
+  </si>
+  <si>
+    <t>WI-111</t>
+  </si>
+  <si>
+    <t>Not in the FSM I/O table; see note; Blue (L) wire to REF. TO CHG-01 (charging system); function not in the I/O table, likely alternator signal. Not spare: do not ground or drive it. Measure on the car.</t>
+  </si>
+  <si>
     <t>A23</t>
   </si>
   <si>
@@ -1381,7 +1402,7 @@
     <t>2.4-2.7</t>
   </si>
   <si>
-    <t>Denso 5-wire A/F sensor; not a Bosch LSU</t>
+    <t>Denso 4-wire A/F sensor (plug B18 pin 4; WI-113); not a Bosch LSU</t>
   </si>
   <si>
     <t>A27</t>
@@ -1436,6 +1457,9 @@
   </si>
   <si>
     <t>2.8-3.2</t>
+  </si>
+  <si>
+    <t>Denso 4-wire A/F sensor (plug B18 pin 3; WI-113); not a Bosch LSU</t>
   </si>
   <si>
     <t>A34</t>
@@ -1734,7 +1758,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -1745,7 +1769,7 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
@@ -1942,7 +1966,7 @@
       </c>
       <c r="O3" s="4"/>
     </row>
-    <row r="4" ht="57.75">
+    <row r="4" ht="98.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -1983,7 +2007,9 @@
       <c r="N4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="O4" s="4"/>
+      <c r="O4" s="4" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="5" ht="44.25">
       <c r="A5" s="4">
@@ -1996,40 +2022,40 @@
         <v>4</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I5" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N5" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" ht="57.75">
@@ -2043,40 +2069,40 @@
         <v>5</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N6" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" ht="84.75">
@@ -2090,32 +2116,32 @@
         <v>6</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G7" s="5">
         <v>46308</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J7" s="4"/>
       <c r="K7" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N7" s="4" t="s">
         <v>3</v>
@@ -2133,10 +2159,10 @@
         <v>7</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>41</v>
@@ -2152,17 +2178,17 @@
       </c>
       <c r="J8" s="4"/>
       <c r="K8" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M8" s="4"/>
       <c r="N8" s="4" t="s">
         <v>5</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" ht="98.25">
@@ -2176,13 +2202,13 @@
         <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
@@ -2191,21 +2217,21 @@
         <v>0</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J9" s="4"/>
       <c r="K9" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M9" s="4"/>
       <c r="N9" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10" ht="84.75">
@@ -2219,36 +2245,36 @@
         <v>9</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M10" s="4"/>
       <c r="N10" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" ht="98.25">
@@ -2262,38 +2288,38 @@
         <v>10</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G11" s="5">
         <v>46308</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M11" s="4"/>
       <c r="N11" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="12" ht="44.25">
@@ -2307,19 +2333,19 @@
         <v>11</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>42</v>
@@ -2344,19 +2370,19 @@
         <v>12</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>91</v>
-      </c>
       <c r="H13" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>42</v>
@@ -2381,19 +2407,19 @@
         <v>13</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>42</v>
@@ -2406,7 +2432,7 @@
         <v>9</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" ht="44.25">
@@ -2420,13 +2446,13 @@
         <v>14</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G15" s="4">
         <v>5</v>
@@ -2435,7 +2461,7 @@
         <v>5</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
@@ -2445,7 +2471,7 @@
         <v>9</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" ht="30.75">
@@ -2459,32 +2485,32 @@
         <v>15</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G16" s="5">
         <v>46308</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N16" s="4" t="s">
         <v>3</v>
@@ -2502,22 +2528,22 @@
         <v>16</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
@@ -2539,34 +2565,34 @@
         <v>17</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N18" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="19" ht="30.75">
@@ -2580,10 +2606,10 @@
         <v>18</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
@@ -2609,10 +2635,10 @@
         <v>19</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>116</v>
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
@@ -2638,19 +2664,19 @@
         <v>20</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>42</v>
@@ -2675,10 +2701,10 @@
         <v>21</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
@@ -2704,10 +2730,10 @@
         <v>22</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
@@ -2715,19 +2741,19 @@
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N23" s="4" t="s">
         <v>11</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" ht="30.75">
@@ -2741,10 +2767,10 @@
         <v>23</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
@@ -2770,13 +2796,13 @@
         <v>24</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G25" s="4">
         <v>0</v>
@@ -2795,7 +2821,7 @@
         <v>9</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" ht="57.75">
@@ -2809,22 +2835,22 @@
         <v>25</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G26" s="4">
         <v>0</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
@@ -2846,10 +2872,10 @@
         <v>26</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -2875,10 +2901,10 @@
         <v>27</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -2904,39 +2930,39 @@
         <v>28</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G29" s="5">
         <v>46308</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J29" s="4"/>
       <c r="K29" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M29" s="4"/>
       <c r="N29" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="30" ht="178.5">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="30" ht="232.5">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -2947,16 +2973,16 @@
         <v>29</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
@@ -2966,7 +2992,7 @@
         <v>11</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" ht="30.75">
@@ -2980,10 +3006,10 @@
         <v>30</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
@@ -3009,13 +3035,13 @@
         <v>31</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G32" s="4">
         <v>0</v>
@@ -3024,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J32" s="4"/>
       <c r="K32" s="4" t="s">
@@ -3046,16 +3072,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C33" s="4">
         <v>1</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -3075,16 +3101,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C34" s="4">
         <v>2</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -3104,19 +3130,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C35" s="4">
         <v>3</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G35" s="5">
         <v>46308</v>
@@ -3125,17 +3151,17 @@
         <v>46036</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J35" s="4"/>
       <c r="K35" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N35" s="4" t="s">
         <v>3</v>
@@ -3147,19 +3173,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C36" s="4">
         <v>4</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G36" s="5">
         <v>46308</v>
@@ -3168,17 +3194,17 @@
         <v>46036</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J36" s="4"/>
       <c r="K36" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N36" s="4" t="s">
         <v>3</v>
@@ -3190,19 +3216,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C37" s="4">
         <v>5</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G37" s="5">
         <v>46308</v>
@@ -3211,17 +3237,17 @@
         <v>46036</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J37" s="4"/>
       <c r="K37" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N37" s="4" t="s">
         <v>3</v>
@@ -3233,19 +3259,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C38" s="4">
         <v>6</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="G38" s="5">
         <v>46308</v>
@@ -3254,17 +3280,17 @@
         <v>46036</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J38" s="4"/>
       <c r="K38" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N38" s="4" t="s">
         <v>3</v>
@@ -3276,28 +3302,28 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C39" s="4">
         <v>7</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
@@ -3313,28 +3339,28 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C40" s="4">
         <v>8</v>
       </c>
       <c r="D40" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="I40" s="4" t="s">
         <v>174</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>173</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
@@ -3350,25 +3376,25 @@
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C41" s="4">
         <v>9</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>49</v>
@@ -3387,28 +3413,28 @@
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C42" s="4">
         <v>10</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
@@ -3424,25 +3450,25 @@
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C43" s="4">
         <v>11</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>49</v>
@@ -3461,25 +3487,25 @@
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C44" s="4">
         <v>12</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>42</v>
@@ -3492,7 +3518,7 @@
         <v>9</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="45" ht="71.25">
@@ -3500,44 +3526,44 @@
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C45" s="4">
         <v>13</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J45" s="4"/>
       <c r="K45" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N45" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" ht="71.25">
@@ -3545,44 +3571,44 @@
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C46" s="4">
         <v>14</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J46" s="4"/>
       <c r="K46" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N46" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="47" ht="71.25">
@@ -3590,19 +3616,19 @@
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C47" s="4">
         <v>15</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G47" s="4">
         <v>5</v>
@@ -3615,13 +3641,13 @@
       </c>
       <c r="J47" s="4"/>
       <c r="K47" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N47" s="4" t="s">
         <v>3</v>
@@ -3633,19 +3659,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C48" s="4">
         <v>16</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G48" s="4">
         <v>5</v>
@@ -3654,25 +3680,25 @@
         <v>5</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N48" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="49" ht="57.75">
@@ -3680,40 +3706,40 @@
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C49" s="4">
         <v>17</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="N49" s="4" t="s">
         <v>3</v>
@@ -3725,40 +3751,40 @@
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C50" s="4">
         <v>18</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N50" s="4" t="s">
         <v>3</v>
@@ -3770,16 +3796,16 @@
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C51" s="4">
         <v>19</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
@@ -3799,42 +3825,42 @@
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C52" s="4">
         <v>20</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J52" s="4"/>
       <c r="K52" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M52" s="4"/>
       <c r="N52" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" ht="57.75">
@@ -3842,25 +3868,25 @@
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C53" s="4">
         <v>21</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>42</v>
@@ -3879,25 +3905,25 @@
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C54" s="4">
         <v>22</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>42</v>
@@ -3916,44 +3942,44 @@
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C55" s="4">
         <v>23</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M55" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N55" s="4" t="s">
         <v>5</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="56" ht="30.75">
@@ -3961,16 +3987,16 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C56" s="4">
         <v>24</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
@@ -3990,19 +4016,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C57" s="4">
         <v>25</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G57" s="4">
         <v>2.8</v>
@@ -4011,17 +4037,17 @@
         <v>2.8</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="M57" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="N57" s="4" t="s">
         <v>3</v>
@@ -4033,44 +4059,44 @@
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C58" s="4">
         <v>26</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M58" s="4"/>
       <c r="N58" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="59" ht="84.75">
@@ -4078,44 +4104,44 @@
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C59" s="4">
         <v>27</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M59" s="4"/>
       <c r="N59" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" ht="57.75">
@@ -4123,40 +4149,40 @@
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C60" s="4">
         <v>28</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N60" s="4" t="s">
         <v>3</v>
@@ -4168,40 +4194,40 @@
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C61" s="4">
         <v>29</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N61" s="4" t="s">
         <v>3</v>
@@ -4213,16 +4239,16 @@
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C62" s="4">
         <v>30</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F62" s="4"/>
       <c r="G62" s="4"/>
@@ -4242,16 +4268,16 @@
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C63" s="4">
         <v>31</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>48</v>
@@ -4263,7 +4289,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4" t="s">
@@ -4285,19 +4311,19 @@
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C64" s="4">
         <v>32</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G64" s="4">
         <v>0</v>
@@ -4306,7 +4332,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J64" s="4"/>
       <c r="K64" s="4" t="s">
@@ -4328,19 +4354,19 @@
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C65" s="4">
         <v>33</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G65" s="4">
         <v>0</v>
@@ -4349,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J65" s="4"/>
       <c r="K65" s="4" t="s">
@@ -4371,16 +4397,16 @@
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C66" s="4">
         <v>34</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>48</v>
@@ -4395,7 +4421,7 @@
         <v>49</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K66" s="4" t="s">
         <v>43</v>
@@ -4416,16 +4442,16 @@
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C67" s="4">
         <v>35</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>48</v>
@@ -4437,7 +4463,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J67" s="4"/>
       <c r="K67" s="4" t="s">
@@ -4453,7 +4479,7 @@
         <v>3</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="68" ht="44.25">
@@ -4461,16 +4487,16 @@
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C68" s="4">
         <v>1</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>41</v>
@@ -4504,28 +4530,28 @@
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C69" s="4">
         <v>2</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J69" s="4"/>
       <c r="K69" s="4"/>
@@ -4541,16 +4567,16 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C70" s="4">
         <v>3</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
@@ -4570,16 +4596,16 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C71" s="4">
         <v>4</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>41</v>
@@ -4613,37 +4639,37 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C72" s="4">
         <v>5</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G72" s="5">
         <v>46308</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M72" s="4" t="s">
         <v>44</v>
@@ -4658,37 +4684,37 @@
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C73" s="4">
         <v>6</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G73" s="5">
         <v>46308</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="M73" s="4" t="s">
         <v>44</v>
@@ -4703,16 +4729,16 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C74" s="4">
         <v>7</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="4"/>
@@ -4732,40 +4758,40 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C75" s="4">
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M75" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N75" s="4" t="s">
         <v>3</v>
@@ -4777,44 +4803,44 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C76" s="4">
         <v>9</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="M76" s="4"/>
       <c r="N76" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="77" ht="71.25">
@@ -4822,40 +4848,40 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C77" s="4">
         <v>10</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G77" s="4">
         <v>0</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M77" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N77" s="4" t="s">
         <v>3</v>
@@ -4867,16 +4893,16 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C78" s="4">
         <v>11</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
@@ -4896,16 +4922,16 @@
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C79" s="4">
         <v>12</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>41</v>
@@ -4939,16 +4965,16 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C80" s="4">
         <v>13</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
@@ -4968,16 +4994,16 @@
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C81" s="4">
         <v>14</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
@@ -4997,44 +5023,44 @@
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C82" s="4">
         <v>15</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G82" s="4">
         <v>0</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>145</v>
+        <v>325</v>
       </c>
       <c r="J82" s="4"/>
       <c r="K82" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M82" s="4" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="N82" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="83" ht="57.75">
@@ -5042,38 +5068,38 @@
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C83" s="4">
         <v>16</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G83" s="4">
         <v>0</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J83" s="4"/>
       <c r="K83" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M83" s="4" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N83" s="4" t="s">
         <v>3</v>
@@ -5085,38 +5111,38 @@
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C84" s="4">
         <v>17</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G84" s="4">
         <v>0</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J84" s="4"/>
       <c r="K84" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M84" s="4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N84" s="4" t="s">
         <v>3</v>
@@ -5128,38 +5154,38 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C85" s="4">
         <v>18</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G85" s="4">
         <v>0</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J85" s="4"/>
       <c r="K85" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M85" s="4" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="N85" s="4" t="s">
         <v>3</v>
@@ -5171,44 +5197,44 @@
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C86" s="4">
         <v>19</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="G86" s="5">
         <v>46308</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J86" s="4"/>
       <c r="K86" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M86" s="4" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N86" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" ht="30.75">
@@ -5216,16 +5242,16 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C87" s="4">
         <v>20</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="4"/>
@@ -5245,16 +5271,16 @@
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C88" s="4">
         <v>21</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
@@ -5274,19 +5300,19 @@
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C89" s="4">
         <v>22</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G89" s="4">
         <v>0</v>
@@ -5295,19 +5321,19 @@
         <v>0</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L89" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M89" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N89" s="4" t="s">
         <v>3</v>
@@ -5319,16 +5345,16 @@
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C90" s="4">
         <v>23</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="4"/>
@@ -5348,44 +5374,44 @@
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C91" s="4">
         <v>24</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J91" s="4"/>
       <c r="K91" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M91" s="4" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N91" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="92" ht="57.75">
@@ -5393,38 +5419,38 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C92" s="4">
         <v>25</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J92" s="4"/>
       <c r="K92" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M92" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N92" s="4" t="s">
         <v>3</v>
@@ -5436,42 +5462,42 @@
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C93" s="4">
         <v>26</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J93" s="4"/>
       <c r="K93" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M93" s="4"/>
       <c r="N93" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="94" ht="125.25">
@@ -5479,40 +5505,40 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C94" s="4">
         <v>27</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="M94" s="4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="N94" s="4" t="s">
         <v>3</v>
@@ -5524,16 +5550,16 @@
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C95" s="4">
         <v>28</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
@@ -5553,16 +5579,16 @@
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C96" s="4">
         <v>29</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F96" s="4"/>
       <c r="G96" s="4"/>
@@ -5582,16 +5608,16 @@
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C97" s="4">
         <v>30</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F97" s="4"/>
       <c r="G97" s="4"/>
@@ -5611,19 +5637,19 @@
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C98" s="4">
         <v>31</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G98" s="4">
         <v>0</v>
@@ -5632,7 +5658,7 @@
         <v>0</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J98" s="4"/>
       <c r="K98" s="4" t="s">
@@ -5654,16 +5680,16 @@
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C99" s="4">
         <v>32</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
@@ -5683,28 +5709,28 @@
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C100" s="4">
         <v>33</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J100" s="4"/>
       <c r="K100" s="4"/>
@@ -5714,7 +5740,7 @@
         <v>9</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="101" ht="30.75">
@@ -5722,16 +5748,16 @@
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C101" s="4">
         <v>34</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
@@ -5751,44 +5777,44 @@
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C102" s="4">
         <v>35</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J102" s="4"/>
       <c r="K102" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M102" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N102" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="103" ht="71.25">
@@ -5796,73 +5822,73 @@
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C103" s="4">
         <v>1</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="I103" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M103" s="4"/>
       <c r="N103" s="4" t="s">
         <v>5</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="104" ht="57.75">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="104" ht="178.5">
       <c r="A104" s="4">
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C104" s="4">
         <v>2</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J104" s="4"/>
       <c r="K104" s="4"/>
@@ -5871,35 +5897,37 @@
       <c r="N104" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="O104" s="4"/>
-    </row>
-    <row r="105" ht="57.75">
+      <c r="O104" s="4" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="105" ht="111.75">
       <c r="A105" s="4">
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C105" s="4">
         <v>3</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
@@ -5908,23 +5936,25 @@
       <c r="N105" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="O105" s="4"/>
+      <c r="O105" s="4" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="106" ht="30.75">
       <c r="A106" s="4">
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C106" s="4">
         <v>4</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F106" s="4"/>
       <c r="G106" s="4"/>
@@ -5944,16 +5974,16 @@
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C107" s="4">
         <v>5</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F107" s="4"/>
       <c r="G107" s="4"/>
@@ -5973,16 +6003,16 @@
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C108" s="4">
         <v>6</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>41</v>
@@ -6016,16 +6046,16 @@
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C109" s="4">
         <v>7</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>41</v>
@@ -6059,28 +6089,28 @@
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C110" s="4">
         <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="I110" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
@@ -6096,28 +6126,28 @@
         <v>110</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C111" s="4">
         <v>9</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="E111" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="F111" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="F111" s="4" t="s">
-        <v>405</v>
-      </c>
       <c r="G111" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
@@ -6133,28 +6163,28 @@
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C112" s="4">
         <v>10</v>
       </c>
       <c r="D112" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="E112" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="F112" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="G112" s="4" t="s">
         <v>410</v>
       </c>
-      <c r="E112" s="4" t="s">
+      <c r="H112" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="F112" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="G112" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="H112" s="4" t="s">
-        <v>407</v>
-      </c>
       <c r="I112" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
@@ -6170,28 +6200,28 @@
         <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C113" s="4">
         <v>11</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
@@ -6207,25 +6237,25 @@
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C114" s="4">
         <v>12</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="I114" s="4" t="s">
         <v>42</v>
@@ -6244,25 +6274,25 @@
         <v>114</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C115" s="4">
         <v>13</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E115" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="F115" s="4" t="s">
         <v>420</v>
       </c>
-      <c r="F115" s="4" t="s">
-        <v>416</v>
-      </c>
       <c r="G115" s="4" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="I115" s="4" t="s">
         <v>42</v>
@@ -6281,42 +6311,42 @@
         <v>115</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C116" s="4">
         <v>14</v>
       </c>
       <c r="D116" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="E116" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="G116" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="E116" s="4" t="s">
+      <c r="H116" s="4" t="s">
         <v>422</v>
-      </c>
-      <c r="F116" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="G116" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="H116" s="4" t="s">
-        <v>418</v>
       </c>
       <c r="I116" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J116" s="4"/>
       <c r="K116" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="M116" s="4"/>
       <c r="N116" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O116" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="117" ht="44.25">
@@ -6324,25 +6354,25 @@
         <v>116</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C117" s="4">
         <v>15</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I117" s="4" t="s">
         <v>49</v>
@@ -6361,25 +6391,25 @@
         <v>117</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C118" s="4">
         <v>16</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I118" s="4" t="s">
         <v>49</v>
@@ -6398,25 +6428,25 @@
         <v>118</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C119" s="4">
         <v>17</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="E119" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="F119" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="F119" s="4" t="s">
-        <v>426</v>
-      </c>
       <c r="G119" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I119" s="4" t="s">
         <v>42</v>
@@ -6429,7 +6459,7 @@
         <v>9</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="120" ht="84.75">
@@ -6437,44 +6467,44 @@
         <v>119</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C120" s="4">
         <v>18</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I120" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="L120" s="4" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="M120" s="4"/>
       <c r="N120" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O120" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="121" ht="84.75">
@@ -6482,44 +6512,44 @@
         <v>120</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C121" s="4">
         <v>19</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I121" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="L121" s="4" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="M121" s="4"/>
       <c r="N121" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O121" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="122" ht="30.75">
@@ -6527,16 +6557,16 @@
         <v>121</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C122" s="4">
         <v>20</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F122" s="4"/>
       <c r="G122" s="4"/>
@@ -6556,16 +6586,16 @@
         <v>122</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C123" s="4">
         <v>21</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F123" s="4"/>
       <c r="G123" s="4"/>
@@ -6580,78 +6610,82 @@
       </c>
       <c r="O123" s="4"/>
     </row>
-    <row r="124" ht="30.75">
+    <row r="124" ht="326.25">
       <c r="A124" s="4">
         <v>123</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C124" s="4">
         <v>22</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>116</v>
+        <v>446</v>
       </c>
       <c r="F124" s="4"/>
       <c r="G124" s="4"/>
       <c r="H124" s="4"/>
-      <c r="I124" s="4"/>
+      <c r="I124" s="4" t="s">
+        <v>447</v>
+      </c>
       <c r="J124" s="4"/>
       <c r="K124" s="4"/>
       <c r="L124" s="4"/>
       <c r="M124" s="4"/>
       <c r="N124" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="O124" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="O124" s="4" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="125" ht="98.25">
       <c r="A125" s="4">
         <v>124</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C125" s="4">
         <v>23</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="I125" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="L125" s="4" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="M125" s="4"/>
       <c r="N125" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O125" s="4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="126" ht="57.75">
@@ -6659,25 +6693,25 @@
         <v>125</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C126" s="4">
         <v>24</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="I126" s="4" t="s">
         <v>42</v>
@@ -6696,19 +6730,19 @@
         <v>126</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C127" s="4">
         <v>25</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G127" s="4">
         <v>0</v>
@@ -6728,30 +6762,30 @@
       </c>
       <c r="O127" s="4"/>
     </row>
-    <row r="128" ht="84.75">
+    <row r="128" ht="125.25">
       <c r="A128" s="4">
         <v>127</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C128" s="4">
         <v>26</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="I128" s="4" t="s">
         <v>42</v>
@@ -6764,7 +6798,7 @@
         <v>9</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
     </row>
     <row r="129" ht="30.75">
@@ -6772,16 +6806,16 @@
         <v>128</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C129" s="4">
         <v>27</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F129" s="4"/>
       <c r="G129" s="4"/>
@@ -6801,19 +6835,19 @@
         <v>129</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C130" s="4">
         <v>28</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="G130" s="4">
         <v>0</v>
@@ -6825,20 +6859,20 @@
         <v>49</v>
       </c>
       <c r="J130" s="4" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="L130" s="4" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="M130" s="4"/>
       <c r="N130" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O130" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="131" ht="84.75">
@@ -6846,19 +6880,19 @@
         <v>130</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C131" s="4">
         <v>29</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="G131" s="4">
         <v>0</v>
@@ -6870,20 +6904,20 @@
         <v>49</v>
       </c>
       <c r="J131" s="4" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="K131" s="4" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="L131" s="4" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="M131" s="4"/>
       <c r="N131" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O131" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="132" ht="30.75">
@@ -6891,16 +6925,16 @@
         <v>131</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C132" s="4">
         <v>30</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F132" s="4"/>
       <c r="G132" s="4"/>
@@ -6920,16 +6954,16 @@
         <v>132</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C133" s="4">
         <v>31</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F133" s="4"/>
       <c r="G133" s="4"/>
@@ -6949,70 +6983,70 @@
         <v>133</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C134" s="4">
         <v>32</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J134" s="4" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="L134" s="4" t="s">
-        <v>470</v>
+        <v>477</v>
       </c>
       <c r="M134" s="4"/>
       <c r="N134" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O134" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="135" ht="84.75">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="135" ht="125.25">
       <c r="A135" s="4">
         <v>134</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C135" s="4">
         <v>33</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>471</v>
+        <v>478</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="I135" s="4" t="s">
         <v>42</v>
@@ -7025,7 +7059,7 @@
         <v>9</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>455</v>
+        <v>481</v>
       </c>
     </row>
     <row r="136" ht="84.75">
@@ -7033,16 +7067,16 @@
         <v>135</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C136" s="4">
         <v>34</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>41</v>
@@ -7050,7 +7084,7 @@
       <c r="G136" s="4"/>
       <c r="H136" s="4"/>
       <c r="I136" s="4" t="s">
-        <v>145</v>
+        <v>325</v>
       </c>
       <c r="J136" s="4"/>
       <c r="K136" s="4"/>
@@ -7060,7 +7094,7 @@
         <v>9</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>475</v>
+        <v>483</v>
       </c>
     </row>
   </sheetData>

--- a/documents/STI2004-pinout-check.xlsx
+++ b/documents/STI2004-pinout-check.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="518">
   <si>
     <t>Status</t>
   </si>
@@ -82,7 +82,7 @@
     <t>Schematics</t>
   </si>
   <si>
-    <t>master, rev-b</t>
+    <t>master, rev-b-wiring</t>
   </si>
   <si>
     <t>Status judged on the last one</t>
@@ -121,10 +121,10 @@
     <t>Net: master</t>
   </si>
   <si>
-    <t>Net: rev-b</t>
-  </si>
-  <si>
-    <t>Reaches (rev-b)</t>
+    <t>Net: rev-b-wiring</t>
+  </si>
+  <si>
+    <t>Reaches (rev-b-wiring)</t>
   </si>
   <si>
     <t>Notes</t>
@@ -229,9 +229,6 @@
     <t>GND_INJECTORS</t>
   </si>
   <si>
-    <t>Expected a net matching '^GND$'</t>
-  </si>
-  <si>
     <t>D8</t>
   </si>
   <si>
@@ -247,7 +244,10 @@
     <t>IN_STARTER_SWITCH</t>
   </si>
   <si>
-    <t>Net is named but reaches no module or rail; Cranking: 8-14</t>
+    <t>M1.IN_SENS2_S8; R19.1</t>
+  </si>
+  <si>
+    <t>Cranking: 8-14</t>
   </si>
   <si>
     <t>D9</t>
@@ -265,813 +265,870 @@
     <t>IN_NEUTRAL_SWITCH</t>
   </si>
   <si>
+    <t>M1.IN_AUX2_S12</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>Power steering oil pressure switch</t>
+  </si>
+  <si>
+    <t>digital in (to ground)</t>
+  </si>
+  <si>
+    <t>ON 0 / OFF 13-14</t>
+  </si>
+  <si>
+    <t>IN_PS_PRESSURE_SWIITCH | DIGITAL 12-0 OFF ON</t>
+  </si>
+  <si>
+    <t>IN_PS_PRESSURE_SWIITCH</t>
+  </si>
+  <si>
+    <t>IN_PS_PRESSURE_SWITCH</t>
+  </si>
+  <si>
+    <t>M1.IN_AUX3_S11</t>
+  </si>
+  <si>
+    <t>D11</t>
+  </si>
+  <si>
+    <t>Rear defogger switch</t>
+  </si>
+  <si>
+    <t>ON 0 / OFF 10-13</t>
+  </si>
+  <si>
+    <t>D12</t>
+  </si>
+  <si>
+    <t>Small light switch</t>
+  </si>
+  <si>
+    <t>D13</t>
+  </si>
+  <si>
+    <t>Blower fan switch</t>
+  </si>
+  <si>
+    <t>Also shown to auto A/C module (WI-106)</t>
+  </si>
+  <si>
+    <t>D14</t>
+  </si>
+  <si>
+    <t>Test mode connector</t>
+  </si>
+  <si>
+    <t>digital in (5 V pull-up)</t>
+  </si>
+  <si>
+    <t>When connected: 0</t>
+  </si>
+  <si>
+    <t>D15</t>
+  </si>
+  <si>
+    <t>Ignition switch</t>
+  </si>
+  <si>
+    <t>12 V switched in</t>
+  </si>
+  <si>
+    <t>+12V_IGN</t>
+  </si>
+  <si>
+    <t>M14.IN_VIGN_V2</t>
+  </si>
+  <si>
+    <t>D16</t>
+  </si>
+  <si>
+    <t>A/C switch</t>
+  </si>
+  <si>
+    <t>IN_AC_REQUEST</t>
+  </si>
+  <si>
+    <t>M1.IN_SENS3_S7; R20.1</t>
+  </si>
+  <si>
+    <t>D17</t>
+  </si>
+  <si>
+    <t>Main relay control</t>
+  </si>
+  <si>
+    <t>low-side output (relay)</t>
+  </si>
+  <si>
+    <t>WI-106</t>
+  </si>
+  <si>
+    <t>OUT_MAIN_RELAY</t>
+  </si>
+  <si>
+    <t>Q5.D_2</t>
+  </si>
+  <si>
+    <t>Not in the I/O table; wiring diagram shows D17 to the main relay coil</t>
+  </si>
+  <si>
+    <t>D18</t>
+  </si>
+  <si>
+    <t>(not used)</t>
+  </si>
+  <si>
+    <t>D19</t>
+  </si>
+  <si>
+    <t>D20</t>
+  </si>
+  <si>
+    <t>SSM/GST communication line</t>
+  </si>
+  <si>
+    <t>K-line serial</t>
+  </si>
+  <si>
+    <t>&lt;1 &lt;-&gt; &gt;4</t>
+  </si>
+  <si>
+    <t>D21</t>
+  </si>
+  <si>
+    <t>D22</t>
+  </si>
+  <si>
+    <t>IN_CRANK-</t>
+  </si>
+  <si>
+    <t>D23</t>
+  </si>
+  <si>
+    <t>D24</t>
+  </si>
+  <si>
+    <t>Blow-by leak diagnosis signal</t>
+  </si>
+  <si>
+    <t>digital in</t>
+  </si>
+  <si>
+    <t>Disconnected (fault): 5</t>
+  </si>
+  <si>
+    <t>D25</t>
+  </si>
+  <si>
+    <t>Rear oxygen sensor signal</t>
+  </si>
+  <si>
+    <t>analog in (narrowband O2)</t>
+  </si>
+  <si>
+    <t>0-0.9</t>
+  </si>
+  <si>
+    <t>EN(STi)-18</t>
+  </si>
+  <si>
+    <t>IN_O2S</t>
+  </si>
+  <si>
+    <t>M1.IN_O2S_S16</t>
+  </si>
+  <si>
+    <t>D26</t>
+  </si>
+  <si>
+    <t>D27</t>
+  </si>
+  <si>
+    <t>D28</t>
+  </si>
+  <si>
+    <t>Fuel pump control unit signal 2</t>
+  </si>
+  <si>
+    <t>12 V to FPCU</t>
+  </si>
+  <si>
+    <t>FUEL_PUMP_SIGNAL2</t>
+  </si>
+  <si>
     <t>Net is named but reaches no module or rail</t>
   </si>
   <si>
-    <t>D10</t>
-  </si>
-  <si>
-    <t>Power steering oil pressure switch</t>
-  </si>
-  <si>
-    <t>digital in (to ground)</t>
-  </si>
-  <si>
-    <t>ON 0 / OFF 13-14</t>
-  </si>
-  <si>
-    <t>IN_PS_PRESSURE_SWIITCH | DIGITAL 12-0 OFF ON</t>
-  </si>
-  <si>
-    <t>IN_PS_PRESSURE_SWIITCH</t>
-  </si>
-  <si>
-    <t>D11</t>
-  </si>
-  <si>
-    <t>Rear defogger switch</t>
-  </si>
-  <si>
-    <t>ON 0 / OFF 10-13</t>
-  </si>
-  <si>
-    <t>D12</t>
-  </si>
-  <si>
-    <t>Small light switch</t>
-  </si>
-  <si>
-    <t>D13</t>
-  </si>
-  <si>
-    <t>Blower fan switch</t>
-  </si>
-  <si>
-    <t>Also shown to auto A/C module (WI-106)</t>
-  </si>
-  <si>
-    <t>D14</t>
-  </si>
-  <si>
-    <t>Test mode connector</t>
-  </si>
-  <si>
-    <t>digital in (5 V pull-up)</t>
-  </si>
-  <si>
-    <t>When connected: 0</t>
-  </si>
-  <si>
-    <t>D15</t>
-  </si>
-  <si>
-    <t>Ignition switch</t>
-  </si>
-  <si>
-    <t>12 V switched in</t>
-  </si>
-  <si>
-    <t>+12V_IGN</t>
-  </si>
-  <si>
-    <t>M14.IN_VIGN_V2</t>
-  </si>
-  <si>
-    <t>D16</t>
-  </si>
-  <si>
-    <t>A/C switch</t>
-  </si>
-  <si>
-    <t>D17</t>
-  </si>
-  <si>
-    <t>Main relay control</t>
-  </si>
-  <si>
-    <t>low-side output (relay)</t>
-  </si>
-  <si>
-    <t>WI-106</t>
-  </si>
-  <si>
-    <t>OUT_MAIN_RELAY</t>
-  </si>
-  <si>
-    <t>Q5.D_2</t>
-  </si>
-  <si>
-    <t>Not in the I/O table; wiring diagram shows D17 to the main relay coil</t>
-  </si>
-  <si>
-    <t>D18</t>
-  </si>
-  <si>
-    <t>(not used)</t>
-  </si>
-  <si>
-    <t>D19</t>
-  </si>
-  <si>
-    <t>D20</t>
-  </si>
-  <si>
-    <t>SSM/GST communication line</t>
-  </si>
-  <si>
-    <t>K-line serial</t>
-  </si>
-  <si>
-    <t>&lt;1 &lt;-&gt; &gt;4</t>
-  </si>
-  <si>
-    <t>D21</t>
-  </si>
-  <si>
-    <t>D22</t>
-  </si>
-  <si>
-    <t>IN_CRANK-</t>
+    <t>D29</t>
+  </si>
+  <si>
+    <t>(not in I/O table)</t>
+  </si>
+  <si>
+    <t>WI-112</t>
+  </si>
+  <si>
+    <t>Not in the FSM I/O table; see note; Red/white wire to data link connector pin 6 (WI-112); function not in the I/O table. Leave unconnected.</t>
+  </si>
+  <si>
+    <t>D30</t>
+  </si>
+  <si>
+    <t>D31</t>
+  </si>
+  <si>
+    <t>Rear oxygen sensor shield</t>
+  </si>
+  <si>
+    <t>shield</t>
+  </si>
+  <si>
+    <t>B136</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>Fuel injector #4</t>
+  </si>
+  <si>
+    <t>injector low-side</t>
+  </si>
+  <si>
+    <t>OUT_INJ4</t>
+  </si>
+  <si>
+    <t>Q4.D_2</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>Fuel injector #3</t>
+  </si>
+  <si>
+    <t>OUT_INJ3</t>
+  </si>
+  <si>
+    <t>Q3.D_2</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>Fuel injector #2</t>
+  </si>
+  <si>
+    <t>OUT_INJ2</t>
+  </si>
+  <si>
+    <t>Q2.D_2</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>Fuel injector #1</t>
+  </si>
+  <si>
+    <t>OUT_INJ1</t>
+  </si>
+  <si>
+    <t>Q1.D_2</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>Cruise main switch</t>
+  </si>
+  <si>
+    <t>EN(STi)-22</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>Brake switch 2</t>
+  </si>
+  <si>
+    <t>pressed 10-13 / released 0</t>
+  </si>
+  <si>
+    <t>pressed 13-14 / released 0</t>
+  </si>
+  <si>
+    <t>IN_BRAKE_SW2</t>
+  </si>
+  <si>
+    <t>M1.IN_SENS4_S6; R21.1</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>Brake switch 1</t>
+  </si>
+  <si>
+    <t>pressed 0 / released 10-13</t>
+  </si>
+  <si>
+    <t>pressed 0 / released 13-14</t>
+  </si>
+  <si>
+    <t>IN_BRAKE_SW1</t>
+  </si>
+  <si>
+    <t>M1.IN_O2S2_S15; R23.1</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>RESUME/ACCEL switch</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>SET/COAST switch</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>Fuel temperature sensor signal</t>
+  </si>
+  <si>
+    <t>analog in (thermistor)</t>
+  </si>
+  <si>
+    <t>2.5-3.8</t>
+  </si>
+  <si>
+    <t>At 25 C</t>
+  </si>
+  <si>
+    <t>C13</t>
+  </si>
+  <si>
+    <t>Intake air temperature sensor signal</t>
+  </si>
+  <si>
+    <t>0.3-4.6</t>
+  </si>
+  <si>
+    <t>IN_IAT</t>
+  </si>
+  <si>
+    <t>M1.IN_IAT_S26</t>
+  </si>
+  <si>
+    <t>In the MAF housing</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>Engine coolant temperature sensor signal</t>
+  </si>
+  <si>
+    <t>1.0-1.4</t>
+  </si>
+  <si>
+    <t>IN_ECT</t>
+  </si>
+  <si>
+    <t>M1.IN_CLT_S28</t>
+  </si>
+  <si>
+    <t>After warm-up</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>Accelerator position sensor power supply</t>
+  </si>
+  <si>
+    <t>5 V sensor supply out</t>
+  </si>
+  <si>
+    <t>APS_PS_5V</t>
+  </si>
+  <si>
+    <t>+5VAS</t>
+  </si>
+  <si>
+    <t>M14.5VP_V4</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>Sensor power supply</t>
+  </si>
+  <si>
+    <t>5v OUT SENSOR_PS_5V</t>
+  </si>
+  <si>
+    <t>SENSOR_PS_5V</t>
+  </si>
+  <si>
+    <t>Feeds throttle TPS; MAP; TGV sensors</t>
+  </si>
+  <si>
+    <t>C17</t>
+  </si>
+  <si>
+    <t>Accelerator position sensor main</t>
+  </si>
+  <si>
+    <t>analog in</t>
+  </si>
+  <si>
+    <t>closed 1 / open 3.5</t>
+  </si>
+  <si>
+    <t>IN_APS_MAIN</t>
+  </si>
+  <si>
+    <t>IN_PPS_MAIN</t>
+  </si>
+  <si>
+    <t>M1.IN_PPS_S31</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>Electric throttle main (TPS1)</t>
+  </si>
+  <si>
+    <t>0.64-0.72 / open 3.96</t>
+  </si>
+  <si>
+    <t>0.64-0.72</t>
+  </si>
+  <si>
+    <t>IN_TPS_MAIN</t>
+  </si>
+  <si>
+    <t>M1.IN_TPS_S30</t>
+  </si>
+  <si>
+    <t>C19</t>
+  </si>
+  <si>
+    <t>C20</t>
+  </si>
+  <si>
+    <t>Fuel level sensor</t>
+  </si>
+  <si>
+    <t>0.12-4.75</t>
+  </si>
+  <si>
+    <t>IN_FUEL_LEVEL</t>
+  </si>
+  <si>
+    <t>M1.IN_AT1_S27</t>
+  </si>
+  <si>
+    <t>C21</t>
+  </si>
+  <si>
+    <t>Fuel tank pressure sensor signal</t>
+  </si>
+  <si>
+    <t>2.3-2.7</t>
+  </si>
+  <si>
+    <t>C22</t>
+  </si>
+  <si>
+    <t>Manifold absolute pressure sensor signal</t>
+  </si>
+  <si>
+    <t>1.7-2.4</t>
+  </si>
+  <si>
+    <t>1.1-1.6</t>
+  </si>
+  <si>
+    <t>IN_MAP</t>
+  </si>
+  <si>
+    <t>M1.IN_MAP1_S21</t>
+  </si>
+  <si>
+    <t>C23</t>
+  </si>
+  <si>
+    <t>Mass air flow sensor signal</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>0.3-4.5</t>
+  </si>
+  <si>
+    <t>IN_MAF</t>
+  </si>
+  <si>
+    <t>M1.IN_SENS1_S9</t>
+  </si>
+  <si>
+    <t>C24</t>
+  </si>
+  <si>
+    <t>C25</t>
+  </si>
+  <si>
+    <t>Knock sensor signal</t>
+  </si>
+  <si>
+    <t>knock in</t>
+  </si>
+  <si>
+    <t>IN_KNOCK_RAW</t>
+  </si>
+  <si>
+    <t>M13.IN_KNOCK_W1</t>
+  </si>
+  <si>
+    <t>C26</t>
+  </si>
+  <si>
+    <t>Tumble generator valve position sensor LH</t>
+  </si>
+  <si>
+    <t>closed 3.8-4.9 / open 0.2-0.9</t>
+  </si>
+  <si>
+    <t>same</t>
+  </si>
+  <si>
+    <t>IN_TUMBLE_SENSOR_LH</t>
+  </si>
+  <si>
+    <t>M1.IN_MAP2_S20</t>
+  </si>
+  <si>
+    <t>C27</t>
+  </si>
+  <si>
+    <t>Tumble generator valve position sensor RH</t>
+  </si>
+  <si>
+    <t>IN_TUMBLE_SENSOR_RH</t>
+  </si>
+  <si>
+    <t>M1.IN_MAP3_S19</t>
+  </si>
+  <si>
+    <t>C28</t>
+  </si>
+  <si>
+    <t>Accelerator position sensor sub</t>
+  </si>
+  <si>
+    <t>IN_APS_SUB</t>
+  </si>
+  <si>
+    <t>IN_PPS_SUB</t>
+  </si>
+  <si>
+    <t>M1.IN_PPS2_S33</t>
+  </si>
+  <si>
+    <t>C29</t>
+  </si>
+  <si>
+    <t>Electric throttle sub (TPS2)</t>
+  </si>
+  <si>
+    <t>1.51-1.58 / open 4.17</t>
+  </si>
+  <si>
+    <t>1.51-1.58</t>
+  </si>
+  <si>
+    <t>IN_TPS_SUB</t>
+  </si>
+  <si>
+    <t>M1.IN_TPS2_S32</t>
+  </si>
+  <si>
+    <t>C30</t>
+  </si>
+  <si>
+    <t>C31</t>
+  </si>
+  <si>
+    <t>Mass air flow sensor GND</t>
+  </si>
+  <si>
+    <t>C32</t>
+  </si>
+  <si>
+    <t>Mass air flow sensor shield</t>
+  </si>
+  <si>
+    <t>C33</t>
+  </si>
+  <si>
+    <t>Knock sensor shield</t>
+  </si>
+  <si>
+    <t>C34</t>
+  </si>
+  <si>
+    <t>Accelerator position sensor GND (sensor)</t>
+  </si>
+  <si>
+    <t>APS_GND</t>
+  </si>
+  <si>
+    <t>C35</t>
+  </si>
+  <si>
+    <t>GND (sensor)</t>
+  </si>
+  <si>
+    <t>Return for ECT; rear O2; TGV; MAP; fuel tank pressure</t>
+  </si>
+  <si>
+    <t>B135</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>GND (power supply)</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>Rear oxygen sensor heater signal</t>
+  </si>
+  <si>
+    <t>heater low-side</t>
+  </si>
+  <si>
+    <t>0-1.0</t>
+  </si>
+  <si>
+    <t>OUT_O2_HEATER_REAR</t>
+  </si>
+  <si>
+    <t>Q14.D_2</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>B5</t>
+  </si>
+  <si>
+    <t>Control unit power supply</t>
+  </si>
+  <si>
+    <t>12 V in (main relay)</t>
+  </si>
+  <si>
+    <t>12V IN</t>
+  </si>
+  <si>
+    <t>+12V_RAW</t>
+  </si>
+  <si>
+    <t>B6</t>
+  </si>
+  <si>
+    <t>B7</t>
+  </si>
+  <si>
+    <t>B8</t>
+  </si>
+  <si>
+    <t>Camshaft position sensor (LH)</t>
+  </si>
+  <si>
+    <t>cam sensor in</t>
+  </si>
+  <si>
+    <t>ON 0 / OFF 4.7-5.3</t>
+  </si>
+  <si>
+    <t>Sensor output waveform</t>
+  </si>
+  <si>
+    <t>IN_CAM_HALL_CAM_LH</t>
+  </si>
+  <si>
+    <t>IN_CAM</t>
+  </si>
+  <si>
+    <t>M1.IN_CAM_S24</t>
+  </si>
+  <si>
+    <t>B9</t>
+  </si>
+  <si>
+    <t>Camshaft position sensor (RH)</t>
+  </si>
+  <si>
+    <t>IN_CAM_HALL_CAM_RH</t>
+  </si>
+  <si>
+    <t>IN_CAM_RH</t>
+  </si>
+  <si>
+    <t>M1.IN_AUX1_S13</t>
+  </si>
+  <si>
+    <t>B10</t>
+  </si>
+  <si>
+    <t>Crankshaft position sensor signal (+)</t>
+  </si>
+  <si>
+    <t>VR in</t>
+  </si>
+  <si>
+    <t>-7 to +7</t>
+  </si>
+  <si>
+    <t>IN_CRANK+</t>
+  </si>
+  <si>
+    <t>M5.VR+_W2</t>
+  </si>
+  <si>
+    <t>B11</t>
+  </si>
+  <si>
+    <t>B12</t>
+  </si>
+  <si>
+    <t>GND (ignition system)</t>
+  </si>
+  <si>
+    <t>B13</t>
+  </si>
+  <si>
+    <t>B14</t>
+  </si>
+  <si>
+    <t>B15</t>
+  </si>
+  <si>
+    <t>Ignition control #4</t>
+  </si>
+  <si>
+    <t>igniter output</t>
+  </si>
+  <si>
+    <t>WI-107</t>
+  </si>
+  <si>
+    <t>Net-(F1-Pad1)</t>
+  </si>
+  <si>
+    <t>F1 -&gt; OUT_IGN4 -&gt; M1.IGN4_W8</t>
+  </si>
+  <si>
+    <t>I/O table (EN(STi)-19) prints B135 16 for both #3 and #4; wiring diagram shows B15 to coil 4</t>
+  </si>
+  <si>
+    <t>B16</t>
+  </si>
+  <si>
+    <t>Ignition control #3</t>
+  </si>
+  <si>
+    <t>Net-(F2-Pad1)</t>
+  </si>
+  <si>
+    <t>F2 -&gt; OUT_IGN3 -&gt; M1.IGN3_W9</t>
+  </si>
+  <si>
+    <t>B17</t>
+  </si>
+  <si>
+    <t>Ignition control #2</t>
+  </si>
+  <si>
+    <t>Net-(F3-Pad1)</t>
+  </si>
+  <si>
+    <t>F3 -&gt; OUT_IGN2 -&gt; M1.IGN2_W10</t>
+  </si>
+  <si>
+    <t>B18</t>
+  </si>
+  <si>
+    <t>Ignition control #1</t>
+  </si>
+  <si>
+    <t>Net-(F4-Pad1)</t>
+  </si>
+  <si>
+    <t>F4 -&gt; OUT_IGN1 -&gt; M1.IGN1_W11</t>
+  </si>
+  <si>
+    <t>B19</t>
+  </si>
+  <si>
+    <t>Back-up power supply</t>
+  </si>
+  <si>
+    <t>12 V permanent in</t>
+  </si>
+  <si>
+    <t>+12V_BACK_UP</t>
+  </si>
+  <si>
+    <t>M14.V12_PERM_V1</t>
+  </si>
+  <si>
+    <t>Ignition OFF: 10-13</t>
+  </si>
+  <si>
+    <t>B20</t>
+  </si>
+  <si>
+    <t>B21</t>
+  </si>
+  <si>
+    <t>B22</t>
+  </si>
+  <si>
+    <t>Crankshaft position sensor signal (-)</t>
+  </si>
+  <si>
+    <t>A/C relay control</t>
   </si>
   <si>
     <t>M5.VR-_W1</t>
   </si>
   <si>
-    <t>Car does not use this pin, but the schematic connects it</t>
-  </si>
-  <si>
-    <t>D23</t>
-  </si>
-  <si>
-    <t>D24</t>
-  </si>
-  <si>
-    <t>Blow-by leak diagnosis signal</t>
-  </si>
-  <si>
-    <t>digital in</t>
-  </si>
-  <si>
-    <t>Disconnected (fault): 5</t>
-  </si>
-  <si>
-    <t>D25</t>
-  </si>
-  <si>
-    <t>Rear oxygen sensor signal</t>
-  </si>
-  <si>
-    <t>analog in (narrowband O2)</t>
-  </si>
-  <si>
-    <t>0-0.9</t>
-  </si>
-  <si>
-    <t>EN(STi)-18</t>
-  </si>
-  <si>
-    <t>D26</t>
-  </si>
-  <si>
-    <t>D27</t>
-  </si>
-  <si>
-    <t>D28</t>
-  </si>
-  <si>
-    <t>Fuel pump control unit signal 2</t>
-  </si>
-  <si>
-    <t>12 V to FPCU</t>
-  </si>
-  <si>
-    <t>FUEL_PUMP_SIGNAL2</t>
-  </si>
-  <si>
-    <t>D29</t>
-  </si>
-  <si>
-    <t>(not in I/O table)</t>
-  </si>
-  <si>
-    <t>WI-112</t>
-  </si>
-  <si>
-    <t>Not in the FSM I/O table; see note; Red/white wire to data link connector pin 6 (WI-112); function not in the I/O table. Leave unconnected.</t>
-  </si>
-  <si>
-    <t>D30</t>
-  </si>
-  <si>
-    <t>D31</t>
-  </si>
-  <si>
-    <t>Rear oxygen sensor shield</t>
-  </si>
-  <si>
-    <t>shield</t>
-  </si>
-  <si>
-    <t>B136</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>Fuel injector #4</t>
-  </si>
-  <si>
-    <t>injector low-side</t>
-  </si>
-  <si>
-    <t>OUT_INJ4</t>
-  </si>
-  <si>
-    <t>Q4.D_2</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>Fuel injector #3</t>
-  </si>
-  <si>
-    <t>OUT_INJ3</t>
-  </si>
-  <si>
-    <t>Q3.D_2</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>Fuel injector #2</t>
-  </si>
-  <si>
-    <t>OUT_INJ2</t>
-  </si>
-  <si>
-    <t>Q2.D_2</t>
-  </si>
-  <si>
-    <t>C6</t>
-  </si>
-  <si>
-    <t>Fuel injector #1</t>
-  </si>
-  <si>
-    <t>OUT_INJ1</t>
-  </si>
-  <si>
-    <t>Q1.D_2</t>
-  </si>
-  <si>
-    <t>C7</t>
-  </si>
-  <si>
-    <t>Cruise main switch</t>
-  </si>
-  <si>
-    <t>EN(STi)-22</t>
-  </si>
-  <si>
-    <t>C8</t>
-  </si>
-  <si>
-    <t>Brake switch 2</t>
-  </si>
-  <si>
-    <t>pressed 10-13 / released 0</t>
-  </si>
-  <si>
-    <t>pressed 13-14 / released 0</t>
-  </si>
-  <si>
-    <t>C9</t>
-  </si>
-  <si>
-    <t>Brake switch 1</t>
-  </si>
-  <si>
-    <t>pressed 0 / released 10-13</t>
-  </si>
-  <si>
-    <t>pressed 0 / released 13-14</t>
-  </si>
-  <si>
-    <t>C10</t>
-  </si>
-  <si>
-    <t>RESUME/ACCEL switch</t>
-  </si>
-  <si>
-    <t>C11</t>
-  </si>
-  <si>
-    <t>SET/COAST switch</t>
-  </si>
-  <si>
-    <t>C12</t>
-  </si>
-  <si>
-    <t>Fuel temperature sensor signal</t>
-  </si>
-  <si>
-    <t>analog in (thermistor)</t>
-  </si>
-  <si>
-    <t>2.5-3.8</t>
-  </si>
-  <si>
-    <t>At 25 C</t>
-  </si>
-  <si>
-    <t>C13</t>
-  </si>
-  <si>
-    <t>Intake air temperature sensor signal</t>
-  </si>
-  <si>
-    <t>0.3-4.6</t>
-  </si>
-  <si>
-    <t>IN_IAT</t>
-  </si>
-  <si>
-    <t>M1.IN_IAT_S26</t>
-  </si>
-  <si>
-    <t>In the MAF housing</t>
-  </si>
-  <si>
-    <t>C14</t>
-  </si>
-  <si>
-    <t>Engine coolant temperature sensor signal</t>
-  </si>
-  <si>
-    <t>1.0-1.4</t>
-  </si>
-  <si>
-    <t>IN_ECT</t>
-  </si>
-  <si>
-    <t>M1.IN_CLT_S28</t>
-  </si>
-  <si>
-    <t>After warm-up</t>
-  </si>
-  <si>
-    <t>C15</t>
-  </si>
-  <si>
-    <t>Accelerator position sensor power supply</t>
-  </si>
-  <si>
-    <t>5 V sensor supply out</t>
-  </si>
-  <si>
-    <t>APS_PS_5V</t>
-  </si>
-  <si>
-    <t>+5VAS</t>
-  </si>
-  <si>
-    <t>M14.5VP_V4</t>
-  </si>
-  <si>
-    <t>C16</t>
-  </si>
-  <si>
-    <t>Sensor power supply</t>
-  </si>
-  <si>
-    <t>5v OUT SENSOR_PS_5V</t>
-  </si>
-  <si>
-    <t>SENSOR_PS_5V</t>
-  </si>
-  <si>
-    <t>Feeds throttle TPS; MAP; TGV sensors</t>
-  </si>
-  <si>
-    <t>C17</t>
-  </si>
-  <si>
-    <t>Accelerator position sensor main</t>
-  </si>
-  <si>
-    <t>analog in</t>
-  </si>
-  <si>
-    <t>closed 1 / open 3.5</t>
-  </si>
-  <si>
-    <t>IN_APS_MAIN</t>
-  </si>
-  <si>
-    <t>IN_PPS_MAIN</t>
-  </si>
-  <si>
-    <t>M1.IN_PPS_S31</t>
-  </si>
-  <si>
-    <t>C18</t>
-  </si>
-  <si>
-    <t>Electric throttle main (TPS1)</t>
-  </si>
-  <si>
-    <t>0.64-0.72 / open 3.96</t>
-  </si>
-  <si>
-    <t>0.64-0.72</t>
-  </si>
-  <si>
-    <t>IN_TPS_MAIN</t>
-  </si>
-  <si>
-    <t>M1.IN_TPS_S30</t>
-  </si>
-  <si>
-    <t>C19</t>
-  </si>
-  <si>
-    <t>C20</t>
-  </si>
-  <si>
-    <t>Fuel level sensor</t>
-  </si>
-  <si>
-    <t>0.12-4.75</t>
-  </si>
-  <si>
-    <t>IN_FUEL_LEVEL</t>
-  </si>
-  <si>
-    <t>C21</t>
-  </si>
-  <si>
-    <t>Fuel tank pressure sensor signal</t>
-  </si>
-  <si>
-    <t>2.3-2.7</t>
-  </si>
-  <si>
-    <t>C22</t>
-  </si>
-  <si>
-    <t>Manifold absolute pressure sensor signal</t>
-  </si>
-  <si>
-    <t>1.7-2.4</t>
-  </si>
-  <si>
-    <t>1.1-1.6</t>
-  </si>
-  <si>
-    <t>C23</t>
-  </si>
-  <si>
-    <t>Mass air flow sensor signal</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>0.3-4.5</t>
-  </si>
-  <si>
-    <t>IN_MAP</t>
-  </si>
-  <si>
-    <t>M1.IN_MAP1_S21</t>
-  </si>
-  <si>
-    <t>Expected a net matching 'MAF'</t>
-  </si>
-  <si>
-    <t>C24</t>
-  </si>
-  <si>
-    <t>C25</t>
-  </si>
-  <si>
-    <t>Knock sensor signal</t>
-  </si>
-  <si>
-    <t>knock in</t>
-  </si>
-  <si>
-    <t>IN_KNOCK_RAW</t>
-  </si>
-  <si>
-    <t>M13.IN_KNOCK_W1</t>
-  </si>
-  <si>
-    <t>C26</t>
-  </si>
-  <si>
-    <t>Tumble generator valve position sensor LH</t>
-  </si>
-  <si>
-    <t>closed 3.8-4.9 / open 0.2-0.9</t>
-  </si>
-  <si>
-    <t>same</t>
-  </si>
-  <si>
-    <t>IN_TUMBLE_SENSOR_LH</t>
-  </si>
-  <si>
-    <t>C27</t>
-  </si>
-  <si>
-    <t>Tumble generator valve position sensor RH</t>
-  </si>
-  <si>
-    <t>IN_TUMBLE_SENSOR_RH</t>
-  </si>
-  <si>
-    <t>C28</t>
-  </si>
-  <si>
-    <t>Accelerator position sensor sub</t>
-  </si>
-  <si>
-    <t>IN_APS_SUB</t>
-  </si>
-  <si>
-    <t>IN_PPS_SUB</t>
-  </si>
-  <si>
-    <t>M1.IN_PPS2_S33</t>
-  </si>
-  <si>
-    <t>C29</t>
-  </si>
-  <si>
-    <t>Electric throttle sub (TPS2)</t>
-  </si>
-  <si>
-    <t>1.51-1.58 / open 4.17</t>
-  </si>
-  <si>
-    <t>1.51-1.58</t>
-  </si>
-  <si>
-    <t>IN_TPS_SUB</t>
-  </si>
-  <si>
-    <t>M1.IN_TPS2_S32</t>
-  </si>
-  <si>
-    <t>C30</t>
-  </si>
-  <si>
-    <t>C31</t>
-  </si>
-  <si>
-    <t>Mass air flow sensor GND</t>
-  </si>
-  <si>
-    <t>C32</t>
-  </si>
-  <si>
-    <t>Mass air flow sensor shield</t>
-  </si>
-  <si>
-    <t>C33</t>
-  </si>
-  <si>
-    <t>Knock sensor shield</t>
-  </si>
-  <si>
-    <t>C34</t>
-  </si>
-  <si>
-    <t>Accelerator position sensor GND (sensor)</t>
-  </si>
-  <si>
-    <t>APS_GND</t>
-  </si>
-  <si>
-    <t>C35</t>
-  </si>
-  <si>
-    <t>GND (sensor)</t>
-  </si>
-  <si>
-    <t>Return for ECT; rear O2; TGV; MAP; fuel tank pressure</t>
-  </si>
-  <si>
-    <t>B135</t>
-  </si>
-  <si>
-    <t>B1</t>
-  </si>
-  <si>
-    <t>GND (power supply)</t>
-  </si>
-  <si>
-    <t>B2</t>
-  </si>
-  <si>
-    <t>Rear oxygen sensor heater signal</t>
-  </si>
-  <si>
-    <t>heater low-side</t>
-  </si>
-  <si>
-    <t>0-1.0</t>
-  </si>
-  <si>
-    <t>B3</t>
-  </si>
-  <si>
-    <t>B4</t>
-  </si>
-  <si>
-    <t>B5</t>
-  </si>
-  <si>
-    <t>Control unit power supply</t>
-  </si>
-  <si>
-    <t>12 V in (main relay)</t>
-  </si>
-  <si>
-    <t>12V IN</t>
-  </si>
-  <si>
-    <t>+12V_RAW</t>
-  </si>
-  <si>
-    <t>B6</t>
-  </si>
-  <si>
-    <t>B7</t>
-  </si>
-  <si>
-    <t>B8</t>
-  </si>
-  <si>
-    <t>Camshaft position sensor (LH)</t>
-  </si>
-  <si>
-    <t>cam sensor in</t>
-  </si>
-  <si>
-    <t>ON 0 / OFF 4.7-5.3</t>
-  </si>
-  <si>
-    <t>Sensor output waveform</t>
-  </si>
-  <si>
-    <t>IN_CAM_HALL_CAM_LH</t>
-  </si>
-  <si>
-    <t>M6.VR+_W2</t>
-  </si>
-  <si>
-    <t>B9</t>
-  </si>
-  <si>
-    <t>Camshaft position sensor (RH)</t>
-  </si>
-  <si>
-    <t>IN_CAM_HALL_CAM_RH</t>
-  </si>
-  <si>
-    <t>B10</t>
-  </si>
-  <si>
-    <t>Crankshaft position sensor signal (+)</t>
-  </si>
-  <si>
-    <t>VR in</t>
-  </si>
-  <si>
-    <t>-7 to +7</t>
-  </si>
-  <si>
-    <t>IN_CRANK+</t>
-  </si>
-  <si>
-    <t>M5.VR+_W2</t>
-  </si>
-  <si>
-    <t>B11</t>
-  </si>
-  <si>
-    <t>B12</t>
-  </si>
-  <si>
-    <t>GND (ignition system)</t>
-  </si>
-  <si>
-    <t>B13</t>
-  </si>
-  <si>
-    <t>B14</t>
-  </si>
-  <si>
-    <t>B15</t>
-  </si>
-  <si>
-    <t>Ignition control #4</t>
-  </si>
-  <si>
-    <t>igniter output</t>
-  </si>
-  <si>
-    <t>WI-107</t>
-  </si>
-  <si>
-    <t>Net-(F1-Pad1)</t>
-  </si>
-  <si>
-    <t>F1 -&gt; OUT_IGN4 -&gt; M1.IGN4_W8</t>
-  </si>
-  <si>
-    <t>I/O table (EN(STi)-19) prints B135 16 for both #3 and #4; wiring diagram shows B15 to coil 4</t>
-  </si>
-  <si>
-    <t>B16</t>
-  </si>
-  <si>
-    <t>Ignition control #3</t>
-  </si>
-  <si>
-    <t>Net-(F2-Pad1)</t>
-  </si>
-  <si>
-    <t>F2 -&gt; OUT_IGN3 -&gt; M1.IGN3_W9</t>
-  </si>
-  <si>
-    <t>B17</t>
-  </si>
-  <si>
-    <t>Ignition control #2</t>
-  </si>
-  <si>
-    <t>Net-(F3-Pad1)</t>
-  </si>
-  <si>
-    <t>F3 -&gt; OUT_IGN2 -&gt; M1.IGN2_W10</t>
-  </si>
-  <si>
-    <t>B18</t>
-  </si>
-  <si>
-    <t>Ignition control #1</t>
-  </si>
-  <si>
-    <t>Net-(F4-Pad1)</t>
-  </si>
-  <si>
-    <t>F4 -&gt; OUT_IGN1 -&gt; M1.IGN1_W11</t>
-  </si>
-  <si>
-    <t>B19</t>
-  </si>
-  <si>
-    <t>Back-up power supply</t>
-  </si>
-  <si>
-    <t>12 V permanent in</t>
-  </si>
-  <si>
-    <t>+12V_BACK_UP</t>
-  </si>
-  <si>
-    <t>M14.V12_PERM_V1</t>
-  </si>
-  <si>
-    <t>Ignition OFF: 10-13</t>
-  </si>
-  <si>
-    <t>B20</t>
-  </si>
-  <si>
-    <t>B21</t>
-  </si>
-  <si>
-    <t>B22</t>
-  </si>
-  <si>
-    <t>Crankshaft position sensor signal (-)</t>
-  </si>
-  <si>
-    <t>A/C relay control</t>
-  </si>
-  <si>
     <t>B23</t>
   </si>
   <si>
@@ -1123,7 +1180,10 @@
     <t>FUEL_PUMP_SIGNAL1</t>
   </si>
   <si>
-    <t>Net is named but reaches no module or rail; Waveform</t>
+    <t>M1.IGN5_W7</t>
+  </si>
+  <si>
+    <t>Waveform</t>
   </si>
   <si>
     <t>B27</t>
@@ -1165,6 +1225,12 @@
     <t>B33</t>
   </si>
   <si>
+    <t>OUT_AC_RELAY</t>
+  </si>
+  <si>
+    <t>Q15.D_2</t>
+  </si>
+  <si>
     <t>I/O table (EN(STi)-19) prints B133 33; wiring diagram shows B33 to the auto A/C module</t>
   </si>
   <si>
@@ -1198,7 +1264,10 @@
     <t>IN_CLT</t>
   </si>
   <si>
-    <t>Expected a net matching 'CLUTCH'</t>
+    <t>IN_CLUTCH</t>
+  </si>
+  <si>
+    <t>M1.IN_RES1_S17; R22.1</t>
   </si>
   <si>
     <t>A2</t>
@@ -1252,12 +1321,24 @@
     <t>0 or 13-14</t>
   </si>
   <si>
+    <t>OUT_TGV_CLOSE</t>
+  </si>
+  <si>
+    <t>M9.OUT-_S2</t>
+  </si>
+  <si>
     <t>A9</t>
   </si>
   <si>
     <t>Tumble generator valve RH (open)</t>
   </si>
   <si>
+    <t>OUT_TGV_OPEN</t>
+  </si>
+  <si>
+    <t>M9.OUT+_S3</t>
+  </si>
+  <si>
     <t>A10</t>
   </si>
   <si>
@@ -1300,6 +1381,9 @@
     <t>OUT_PURGE_CONTROL</t>
   </si>
   <si>
+    <t>Q12.D_2</t>
+  </si>
+  <si>
     <t>A15</t>
   </si>
   <si>
@@ -1321,6 +1405,12 @@
     <t>Malfunction indicator lamp</t>
   </si>
   <si>
+    <t>OUT_MIL</t>
+  </si>
+  <si>
+    <t>Q13.D_2</t>
+  </si>
+  <si>
     <t>ON &lt;=1 / OFF 10-14</t>
   </si>
   <si>
@@ -1378,6 +1468,9 @@
     <t>OUT_TACH</t>
   </si>
   <si>
+    <t>Q16.D_2</t>
+  </si>
+  <si>
     <t>A24</t>
   </si>
   <si>
@@ -1420,6 +1513,9 @@
     <t>OUT_VVT_RH-</t>
   </si>
   <si>
+    <t>Q10.D_2</t>
+  </si>
+  <si>
     <t>A29</t>
   </si>
   <si>
@@ -1429,6 +1525,9 @@
     <t>OUT_VVT_LH-</t>
   </si>
   <si>
+    <t>Q11.D_2</t>
+  </si>
+  <si>
     <t>A30</t>
   </si>
   <si>
@@ -1448,6 +1547,9 @@
   </si>
   <si>
     <t>OUT_WG</t>
+  </si>
+  <si>
+    <t>Q9.D_2</t>
   </si>
   <si>
     <t>A33</t>
@@ -1714,7 +1816,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -1725,7 +1827,7 @@
         <v>5</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
@@ -1736,7 +1838,7 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -1747,7 +1849,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -1758,7 +1860,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -1769,7 +1871,7 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
@@ -1833,7 +1935,7 @@
     <col min="15" max="15" width="44.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30.75">
+    <row r="1" ht="44.25">
       <c r="A1" s="3" t="s">
         <v>24</v>
       </c>
@@ -2148,7 +2250,7 @@
       </c>
       <c r="O7" s="4"/>
     </row>
-    <row r="8" ht="57.75">
+    <row r="8" ht="44.25">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -2181,17 +2283,17 @@
         <v>70</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="M8" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="M8" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="N8" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="9" ht="98.25">
+        <v>3</v>
+      </c>
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" ht="44.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -2202,13 +2304,13 @@
         <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="F9" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>74</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
@@ -2217,24 +2319,26 @@
         <v>0</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J9" s="4"/>
       <c r="K9" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="M9" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="L9" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="M9" s="4"/>
       <c r="N9" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O9" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="10" ht="84.75">
+    <row r="10" ht="44.25">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -2251,7 +2355,7 @@
         <v>79</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>80</v>
@@ -2260,7 +2364,7 @@
         <v>81</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4" t="s">
@@ -2269,13 +2373,13 @@
       <c r="L10" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="M10" s="4"/>
+      <c r="M10" s="4" t="s">
+        <v>83</v>
+      </c>
       <c r="N10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="O10" s="4" t="s">
-        <v>83</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="O10" s="4"/>
     </row>
     <row r="11" ht="98.25">
       <c r="A11" s="4">
@@ -2312,15 +2416,15 @@
         <v>89</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="M11" s="4"/>
+        <v>90</v>
+      </c>
+      <c r="M11" s="4" t="s">
+        <v>91</v>
+      </c>
       <c r="N11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="O11" s="4" t="s">
-        <v>83</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="O11" s="4"/>
     </row>
     <row r="12" ht="44.25">
       <c r="A12" s="4">
@@ -2333,16 +2437,16 @@
         <v>11</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>86</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>87</v>
@@ -2370,16 +2474,16 @@
         <v>12</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>86</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>87</v>
@@ -2407,16 +2511,16 @@
         <v>13</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>86</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>87</v>
@@ -2432,7 +2536,7 @@
         <v>9</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" ht="44.25">
@@ -2446,13 +2550,13 @@
         <v>14</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G15" s="4">
         <v>5</v>
@@ -2461,7 +2565,7 @@
         <v>5</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
@@ -2471,7 +2575,7 @@
         <v>9</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" ht="30.75">
@@ -2485,13 +2589,13 @@
         <v>15</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G16" s="5">
         <v>46308</v>
@@ -2500,17 +2604,17 @@
         <v>65</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N16" s="4" t="s">
         <v>3</v>
@@ -2528,13 +2632,13 @@
         <v>16</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>80</v>
@@ -2543,14 +2647,18 @@
         <v>81</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
+      <c r="L17" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>112</v>
+      </c>
       <c r="N17" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O17" s="4"/>
     </row>
@@ -2565,34 +2673,34 @@
         <v>17</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="N18" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" ht="30.75">
@@ -2606,10 +2714,10 @@
         <v>18</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
@@ -2635,10 +2743,10 @@
         <v>19</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
@@ -2664,19 +2772,19 @@
         <v>20</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>42</v>
@@ -2701,10 +2809,10 @@
         <v>21</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
@@ -2719,7 +2827,7 @@
       </c>
       <c r="O22" s="4"/>
     </row>
-    <row r="23" ht="98.25">
+    <row r="23" ht="30.75">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -2730,10 +2838,10 @@
         <v>22</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
@@ -2741,20 +2849,14 @@
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>126</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="L23" s="4"/>
+      <c r="M23" s="4"/>
       <c r="N23" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="O23" s="4" t="s">
-        <v>127</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="O23" s="4"/>
     </row>
     <row r="24" ht="30.75">
       <c r="A24" s="4">
@@ -2767,10 +2869,10 @@
         <v>23</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
@@ -2796,13 +2898,13 @@
         <v>24</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G25" s="4">
         <v>0</v>
@@ -2821,7 +2923,7 @@
         <v>9</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" ht="57.75">
@@ -2835,29 +2937,33 @@
         <v>25</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G26" s="4">
         <v>0</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
+      <c r="L26" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="M26" s="4" t="s">
+        <v>141</v>
+      </c>
       <c r="N26" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O26" s="4"/>
     </row>
@@ -2872,10 +2978,10 @@
         <v>26</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -2901,10 +3007,10 @@
         <v>27</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -2930,13 +3036,13 @@
         <v>28</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="G29" s="5">
         <v>46308</v>
@@ -2945,21 +3051,21 @@
         <v>65</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J29" s="4"/>
       <c r="K29" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="M29" s="4"/>
       <c r="N29" s="4" t="s">
         <v>7</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>83</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" ht="232.5">
@@ -2973,16 +3079,16 @@
         <v>29</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
@@ -2992,7 +3098,7 @@
         <v>11</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="31" ht="30.75">
@@ -3006,10 +3112,10 @@
         <v>30</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
@@ -3035,13 +3141,13 @@
         <v>31</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G32" s="4">
         <v>0</v>
@@ -3050,7 +3156,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J32" s="4"/>
       <c r="K32" s="4" t="s">
@@ -3072,16 +3178,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C33" s="4">
         <v>1</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -3101,16 +3207,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C34" s="4">
         <v>2</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -3130,19 +3236,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C35" s="4">
         <v>3</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G35" s="5">
         <v>46308</v>
@@ -3151,17 +3257,17 @@
         <v>46036</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J35" s="4"/>
       <c r="K35" s="4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="N35" s="4" t="s">
         <v>3</v>
@@ -3173,19 +3279,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C36" s="4">
         <v>4</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G36" s="5">
         <v>46308</v>
@@ -3194,17 +3300,17 @@
         <v>46036</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J36" s="4"/>
       <c r="K36" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="N36" s="4" t="s">
         <v>3</v>
@@ -3216,19 +3322,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C37" s="4">
         <v>5</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G37" s="5">
         <v>46308</v>
@@ -3237,17 +3343,17 @@
         <v>46036</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J37" s="4"/>
       <c r="K37" s="4" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="N37" s="4" t="s">
         <v>3</v>
@@ -3259,19 +3365,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C38" s="4">
         <v>6</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="G38" s="5">
         <v>46308</v>
@@ -3280,17 +3386,17 @@
         <v>46036</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J38" s="4"/>
       <c r="K38" s="4" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="N38" s="4" t="s">
         <v>3</v>
@@ -3302,19 +3408,19 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C39" s="4">
         <v>7</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G39" s="4" t="s">
         <v>80</v>
@@ -3323,7 +3429,7 @@
         <v>81</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
@@ -3339,35 +3445,39 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C40" s="4">
         <v>8</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="4"/>
+      <c r="L40" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="M40" s="4" t="s">
+        <v>185</v>
+      </c>
       <c r="N40" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O40" s="4"/>
     </row>
@@ -3376,35 +3486,39 @@
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C41" s="4">
         <v>9</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>86</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="4"/>
+      <c r="L41" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="M41" s="4" t="s">
+        <v>191</v>
+      </c>
       <c r="N41" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O41" s="4"/>
     </row>
@@ -3413,19 +3527,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C42" s="4">
         <v>10</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>80</v>
@@ -3434,7 +3548,7 @@
         <v>81</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
@@ -3450,19 +3564,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C43" s="4">
         <v>11</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>80</v>
@@ -3487,25 +3601,25 @@
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C44" s="4">
         <v>12</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>42</v>
@@ -3518,7 +3632,7 @@
         <v>9</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
     </row>
     <row r="45" ht="71.25">
@@ -3526,44 +3640,44 @@
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C45" s="4">
         <v>13</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J45" s="4"/>
       <c r="K45" s="4" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="N45" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
     <row r="46" ht="71.25">
@@ -3571,44 +3685,44 @@
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C46" s="4">
         <v>14</v>
       </c>
       <c r="D46" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="F46" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E46" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>189</v>
-      </c>
       <c r="G46" s="4" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J46" s="4"/>
       <c r="K46" s="4" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="N46" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
     </row>
     <row r="47" ht="71.25">
@@ -3616,19 +3730,19 @@
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C47" s="4">
         <v>15</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="G47" s="4">
         <v>5</v>
@@ -3641,13 +3755,13 @@
       </c>
       <c r="J47" s="4"/>
       <c r="K47" s="4" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="N47" s="4" t="s">
         <v>3</v>
@@ -3659,19 +3773,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C48" s="4">
         <v>16</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="G48" s="4">
         <v>5</v>
@@ -3680,25 +3794,25 @@
         <v>5</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="N48" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="49" ht="57.75">
@@ -3706,40 +3820,40 @@
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C49" s="4">
         <v>17</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="N49" s="4" t="s">
         <v>3</v>
@@ -3751,40 +3865,40 @@
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C50" s="4">
         <v>18</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="N50" s="4" t="s">
         <v>3</v>
@@ -3796,16 +3910,16 @@
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C51" s="4">
         <v>19</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
@@ -3820,73 +3934,73 @@
       </c>
       <c r="O51" s="4"/>
     </row>
-    <row r="52" ht="84.75">
+    <row r="52" ht="44.25">
       <c r="A52" s="4">
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C52" s="4">
         <v>20</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J52" s="4"/>
       <c r="K52" s="4" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="M52" s="4"/>
+        <v>241</v>
+      </c>
+      <c r="M52" s="4" t="s">
+        <v>242</v>
+      </c>
       <c r="N52" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="O52" s="4" t="s">
-        <v>83</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="O52" s="4"/>
     </row>
     <row r="53" ht="57.75">
       <c r="A53" s="4">
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C53" s="4">
         <v>21</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>42</v>
@@ -3905,35 +4019,39 @@
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C54" s="4">
         <v>22</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
+      <c r="L54" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="M54" s="4" t="s">
+        <v>251</v>
+      </c>
       <c r="N54" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O54" s="4"/>
     </row>
@@ -3942,61 +4060,59 @@
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C55" s="4">
         <v>23</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="M55" s="4" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="N55" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="O55" s="4" t="s">
-        <v>246</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="O55" s="4"/>
     </row>
     <row r="56" ht="30.75">
       <c r="A56" s="4">
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C56" s="4">
         <v>24</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
@@ -4016,19 +4132,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C57" s="4">
         <v>25</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="G57" s="4">
         <v>2.8</v>
@@ -4037,152 +4153,152 @@
         <v>2.8</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="M57" s="4" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="N57" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O57" s="4"/>
     </row>
-    <row r="58" ht="84.75">
+    <row r="58" ht="71.25">
       <c r="A58" s="4">
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C58" s="4">
         <v>26</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="M58" s="4"/>
+        <v>268</v>
+      </c>
+      <c r="M58" s="4" t="s">
+        <v>269</v>
+      </c>
       <c r="N58" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="O58" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="59" ht="84.75">
+        <v>3</v>
+      </c>
+      <c r="O58" s="4"/>
+    </row>
+    <row r="59" ht="71.25">
       <c r="A59" s="4">
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C59" s="4">
         <v>27</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="M59" s="4"/>
+        <v>272</v>
+      </c>
+      <c r="M59" s="4" t="s">
+        <v>273</v>
+      </c>
       <c r="N59" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="O59" s="4" t="s">
-        <v>83</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="O59" s="4"/>
     </row>
     <row r="60" ht="57.75">
       <c r="A60" s="4">
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C60" s="4">
         <v>28</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="N60" s="4" t="s">
         <v>3</v>
@@ -4194,40 +4310,40 @@
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C61" s="4">
         <v>29</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="N61" s="4" t="s">
         <v>3</v>
@@ -4239,16 +4355,16 @@
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C62" s="4">
         <v>30</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F62" s="4"/>
       <c r="G62" s="4"/>
@@ -4268,16 +4384,16 @@
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C63" s="4">
         <v>31</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>48</v>
@@ -4289,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4" t="s">
@@ -4311,19 +4427,19 @@
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C64" s="4">
         <v>32</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G64" s="4">
         <v>0</v>
@@ -4332,7 +4448,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J64" s="4"/>
       <c r="K64" s="4" t="s">
@@ -4354,19 +4470,19 @@
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C65" s="4">
         <v>33</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G65" s="4">
         <v>0</v>
@@ -4375,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J65" s="4"/>
       <c r="K65" s="4" t="s">
@@ -4397,16 +4513,16 @@
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C66" s="4">
         <v>34</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>48</v>
@@ -4421,7 +4537,7 @@
         <v>49</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="K66" s="4" t="s">
         <v>43</v>
@@ -4442,16 +4558,16 @@
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C67" s="4">
         <v>35</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>283</v>
+        <v>296</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>48</v>
@@ -4463,7 +4579,7 @@
         <v>0</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J67" s="4"/>
       <c r="K67" s="4" t="s">
@@ -4479,7 +4595,7 @@
         <v>3</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
     </row>
     <row r="68" ht="44.25">
@@ -4487,16 +4603,16 @@
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C68" s="4">
         <v>1</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>41</v>
@@ -4530,35 +4646,39 @@
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C69" s="4">
         <v>2</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J69" s="4"/>
       <c r="K69" s="4"/>
-      <c r="L69" s="4"/>
-      <c r="M69" s="4"/>
+      <c r="L69" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="M69" s="4" t="s">
+        <v>306</v>
+      </c>
       <c r="N69" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O69" s="4"/>
     </row>
@@ -4567,16 +4687,16 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C70" s="4">
         <v>3</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
@@ -4596,16 +4716,16 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C71" s="4">
         <v>4</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>287</v>
+        <v>300</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>41</v>
@@ -4639,19 +4759,19 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C72" s="4">
         <v>5</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="G72" s="5">
         <v>46308</v>
@@ -4660,16 +4780,16 @@
         <v>65</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="M72" s="4" t="s">
         <v>44</v>
@@ -4684,19 +4804,19 @@
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C73" s="4">
         <v>6</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="G73" s="5">
         <v>46308</v>
@@ -4705,16 +4825,16 @@
         <v>65</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="M73" s="4" t="s">
         <v>44</v>
@@ -4729,16 +4849,16 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C74" s="4">
         <v>7</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="4"/>
@@ -4758,130 +4878,130 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C75" s="4">
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="M75" s="4" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="N75" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O75" s="4"/>
     </row>
-    <row r="76" ht="84.75">
+    <row r="76" ht="57.75">
       <c r="A76" s="4">
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C76" s="4">
         <v>9</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="M76" s="4"/>
+        <v>327</v>
+      </c>
+      <c r="M76" s="4" t="s">
+        <v>328</v>
+      </c>
       <c r="N76" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="O76" s="4" t="s">
-        <v>83</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="O76" s="4"/>
     </row>
     <row r="77" ht="71.25">
       <c r="A77" s="4">
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C77" s="4">
         <v>10</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="G77" s="4">
         <v>0</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="M77" s="4" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="N77" s="4" t="s">
         <v>3</v>
@@ -4893,16 +5013,16 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C78" s="4">
         <v>11</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
@@ -4922,16 +5042,16 @@
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C79" s="4">
         <v>12</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>41</v>
@@ -4965,16 +5085,16 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C80" s="4">
         <v>13</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
@@ -4994,16 +5114,16 @@
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C81" s="4">
         <v>14</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
@@ -5023,19 +5143,19 @@
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C82" s="4">
         <v>15</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="G82" s="4">
         <v>0</v>
@@ -5044,23 +5164,23 @@
         <v>65</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="J82" s="4"/>
       <c r="K82" s="4" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="M82" s="4" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="N82" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
     </row>
     <row r="83" ht="57.75">
@@ -5068,19 +5188,19 @@
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C83" s="4">
         <v>16</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="G83" s="4">
         <v>0</v>
@@ -5089,17 +5209,17 @@
         <v>65</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J83" s="4"/>
       <c r="K83" s="4" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="M83" s="4" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="N83" s="4" t="s">
         <v>3</v>
@@ -5111,19 +5231,19 @@
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C84" s="4">
         <v>17</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="G84" s="4">
         <v>0</v>
@@ -5132,17 +5252,17 @@
         <v>65</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J84" s="4"/>
       <c r="K84" s="4" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="M84" s="4" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="N84" s="4" t="s">
         <v>3</v>
@@ -5154,19 +5274,19 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C85" s="4">
         <v>18</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="G85" s="4">
         <v>0</v>
@@ -5175,17 +5295,17 @@
         <v>65</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J85" s="4"/>
       <c r="K85" s="4" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="M85" s="4" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="N85" s="4" t="s">
         <v>3</v>
@@ -5197,19 +5317,19 @@
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C86" s="4">
         <v>19</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="G86" s="5">
         <v>46308</v>
@@ -5218,23 +5338,23 @@
         <v>65</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J86" s="4"/>
       <c r="K86" s="4" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="M86" s="4" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="N86" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
     </row>
     <row r="87" ht="30.75">
@@ -5242,16 +5362,16 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C87" s="4">
         <v>20</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="4"/>
@@ -5271,16 +5391,16 @@
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C88" s="4">
         <v>21</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
@@ -5300,19 +5420,19 @@
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C89" s="4">
         <v>22</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="G89" s="4">
         <v>0</v>
@@ -5321,19 +5441,19 @@
         <v>0</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="L89" s="4" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="M89" s="4" t="s">
-        <v>126</v>
+        <v>370</v>
       </c>
       <c r="N89" s="4" t="s">
         <v>3</v>
@@ -5345,16 +5465,16 @@
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C90" s="4">
         <v>23</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>352</v>
+        <v>371</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="4"/>
@@ -5374,44 +5494,44 @@
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C91" s="4">
         <v>24</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>353</v>
+        <v>372</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>354</v>
+        <v>373</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J91" s="4"/>
       <c r="K91" s="4" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="M91" s="4" t="s">
-        <v>358</v>
+        <v>377</v>
       </c>
       <c r="N91" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>359</v>
+        <v>378</v>
       </c>
     </row>
     <row r="92" ht="57.75">
@@ -5419,85 +5539,87 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C92" s="4">
         <v>25</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>360</v>
+        <v>379</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J92" s="4"/>
       <c r="K92" s="4" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>362</v>
+        <v>381</v>
       </c>
       <c r="M92" s="4" t="s">
-        <v>363</v>
+        <v>382</v>
       </c>
       <c r="N92" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O92" s="4"/>
     </row>
-    <row r="93" ht="98.25">
+    <row r="93" ht="57.75">
       <c r="A93" s="4">
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C93" s="4">
         <v>26</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>364</v>
+        <v>383</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>366</v>
+        <v>385</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J93" s="4"/>
       <c r="K93" s="4" t="s">
-        <v>368</v>
+        <v>387</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="M93" s="4"/>
+        <v>387</v>
+      </c>
+      <c r="M93" s="4" t="s">
+        <v>388</v>
+      </c>
       <c r="N93" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
     </row>
     <row r="94" ht="125.25">
@@ -5505,40 +5627,40 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C94" s="4">
         <v>27</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>370</v>
+        <v>390</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>371</v>
+        <v>391</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>372</v>
+        <v>392</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>367</v>
+        <v>386</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>373</v>
+        <v>393</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>374</v>
+        <v>394</v>
       </c>
       <c r="M94" s="4" t="s">
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="N94" s="4" t="s">
         <v>3</v>
@@ -5550,16 +5672,16 @@
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C95" s="4">
         <v>28</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>376</v>
+        <v>396</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
@@ -5579,16 +5701,16 @@
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C96" s="4">
         <v>29</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>377</v>
+        <v>397</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F96" s="4"/>
       <c r="G96" s="4"/>
@@ -5608,16 +5730,16 @@
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C97" s="4">
         <v>30</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>378</v>
+        <v>398</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F97" s="4"/>
       <c r="G97" s="4"/>
@@ -5637,19 +5759,19 @@
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C98" s="4">
         <v>31</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>379</v>
+        <v>399</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G98" s="4">
         <v>0</v>
@@ -5658,7 +5780,7 @@
         <v>0</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J98" s="4"/>
       <c r="K98" s="4" t="s">
@@ -5680,16 +5802,16 @@
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C99" s="4">
         <v>32</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>381</v>
+        <v>401</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
@@ -5709,38 +5831,42 @@
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C100" s="4">
         <v>33</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>382</v>
+        <v>402</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>355</v>
+        <v>374</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J100" s="4"/>
       <c r="K100" s="4"/>
-      <c r="L100" s="4"/>
-      <c r="M100" s="4"/>
+      <c r="L100" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="M100" s="4" t="s">
+        <v>404</v>
+      </c>
       <c r="N100" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>383</v>
+        <v>405</v>
       </c>
     </row>
     <row r="101" ht="30.75">
@@ -5748,16 +5874,16 @@
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C101" s="4">
         <v>34</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>384</v>
+        <v>406</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
@@ -5777,22 +5903,22 @@
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C102" s="4">
         <v>35</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>385</v>
+        <v>407</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H102" s="4" t="s">
         <v>87</v>
@@ -5802,93 +5928,93 @@
       </c>
       <c r="J102" s="4"/>
       <c r="K102" s="4" t="s">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="M102" s="4" t="s">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="N102" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="103" ht="71.25">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="103" ht="57.75">
       <c r="A103" s="4">
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C103" s="4">
         <v>1</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>392</v>
+        <v>414</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>86</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="I103" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>393</v>
+        <v>415</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="M103" s="4"/>
+        <v>416</v>
+      </c>
+      <c r="M103" s="4" t="s">
+        <v>417</v>
+      </c>
       <c r="N103" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="O103" s="4" t="s">
-        <v>394</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="O103" s="4"/>
     </row>
     <row r="104" ht="178.5">
       <c r="A104" s="4">
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C104" s="4">
         <v>2</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>395</v>
+        <v>418</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>396</v>
+        <v>419</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J104" s="4"/>
       <c r="K104" s="4"/>
@@ -5898,7 +6024,7 @@
         <v>9</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>397</v>
+        <v>420</v>
       </c>
     </row>
     <row r="105" ht="111.75">
@@ -5906,28 +6032,28 @@
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C105" s="4">
         <v>3</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>399</v>
+        <v>422</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
@@ -5937,7 +6063,7 @@
         <v>9</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>400</v>
+        <v>423</v>
       </c>
     </row>
     <row r="106" ht="30.75">
@@ -5945,16 +6071,16 @@
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C106" s="4">
         <v>4</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F106" s="4"/>
       <c r="G106" s="4"/>
@@ -5974,16 +6100,16 @@
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C107" s="4">
         <v>5</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>402</v>
+        <v>425</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F107" s="4"/>
       <c r="G107" s="4"/>
@@ -6003,16 +6129,16 @@
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C108" s="4">
         <v>6</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>404</v>
+        <v>427</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>41</v>
@@ -6046,16 +6172,16 @@
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C109" s="4">
         <v>7</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>405</v>
+        <v>428</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>406</v>
+        <v>429</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>41</v>
@@ -6089,35 +6215,39 @@
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C110" s="4">
         <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>407</v>
+        <v>430</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>408</v>
+        <v>431</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>410</v>
+        <v>433</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="I110" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
-      <c r="L110" s="4"/>
-      <c r="M110" s="4"/>
+      <c r="L110" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="M110" s="4" t="s">
+        <v>436</v>
+      </c>
       <c r="N110" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O110" s="4"/>
     </row>
@@ -6126,35 +6256,39 @@
         <v>110</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C111" s="4">
         <v>9</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>412</v>
+        <v>437</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>413</v>
+        <v>438</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>410</v>
+        <v>433</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
-      <c r="L111" s="4"/>
-      <c r="M111" s="4"/>
+      <c r="L111" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="M111" s="4" t="s">
+        <v>440</v>
+      </c>
       <c r="N111" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O111" s="4"/>
     </row>
@@ -6163,35 +6297,39 @@
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C112" s="4">
         <v>10</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>415</v>
+        <v>442</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>410</v>
+        <v>433</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
-      <c r="L112" s="4"/>
-      <c r="M112" s="4"/>
+      <c r="L112" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="M112" s="4" t="s">
+        <v>436</v>
+      </c>
       <c r="N112" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O112" s="4"/>
     </row>
@@ -6200,35 +6338,39 @@
         <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C113" s="4">
         <v>11</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>416</v>
+        <v>443</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>417</v>
+        <v>444</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>409</v>
+        <v>432</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>410</v>
+        <v>433</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
-      <c r="L113" s="4"/>
-      <c r="M113" s="4"/>
+      <c r="L113" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="M113" s="4" t="s">
+        <v>440</v>
+      </c>
       <c r="N113" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O113" s="4"/>
     </row>
@@ -6237,25 +6379,25 @@
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C114" s="4">
         <v>12</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>418</v>
+        <v>445</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>419</v>
+        <v>446</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>421</v>
+        <v>448</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>422</v>
+        <v>449</v>
       </c>
       <c r="I114" s="4" t="s">
         <v>42</v>
@@ -6274,25 +6416,25 @@
         <v>114</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C115" s="4">
         <v>13</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>421</v>
+        <v>448</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>422</v>
+        <v>449</v>
       </c>
       <c r="I115" s="4" t="s">
         <v>42</v>
@@ -6306,70 +6448,70 @@
       </c>
       <c r="O115" s="4"/>
     </row>
-    <row r="116" ht="84.75">
+    <row r="116" ht="57.75">
       <c r="A116" s="4">
         <v>115</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C116" s="4">
         <v>14</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>425</v>
+        <v>452</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>421</v>
+        <v>448</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>422</v>
+        <v>449</v>
       </c>
       <c r="I116" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J116" s="4"/>
       <c r="K116" s="4" t="s">
-        <v>427</v>
+        <v>454</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>427</v>
-      </c>
-      <c r="M116" s="4"/>
+        <v>454</v>
+      </c>
+      <c r="M116" s="4" t="s">
+        <v>455</v>
+      </c>
       <c r="N116" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="O116" s="4" t="s">
-        <v>83</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="O116" s="4"/>
     </row>
     <row r="117" ht="44.25">
       <c r="A117" s="4">
         <v>116</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C117" s="4">
         <v>15</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>428</v>
+        <v>456</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>430</v>
+        <v>458</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H117" s="4" t="s">
         <v>87</v>
@@ -6391,22 +6533,22 @@
         <v>117</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C118" s="4">
         <v>16</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>431</v>
+        <v>459</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>430</v>
+        <v>458</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H118" s="4" t="s">
         <v>87</v>
@@ -6428,58 +6570,62 @@
         <v>118</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C119" s="4">
         <v>17</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>434</v>
+        <v>462</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>430</v>
+        <v>458</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="I119" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J119" s="4"/>
       <c r="K119" s="4"/>
-      <c r="L119" s="4"/>
-      <c r="M119" s="4"/>
+      <c r="L119" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="M119" s="4" t="s">
+        <v>464</v>
+      </c>
       <c r="N119" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="120" ht="84.75">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="120" ht="71.25">
       <c r="A120" s="4">
         <v>119</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C120" s="4">
         <v>18</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>436</v>
+        <v>466</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>437</v>
+        <v>467</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>438</v>
+        <v>468</v>
       </c>
       <c r="G120" s="4" t="s">
         <v>80</v>
@@ -6491,40 +6637,40 @@
         <v>49</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>439</v>
+        <v>469</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>439</v>
+        <v>469</v>
       </c>
       <c r="L120" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="M120" s="4"/>
+        <v>313</v>
+      </c>
+      <c r="M120" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="N120" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="O120" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="121" ht="84.75">
+        <v>3</v>
+      </c>
+      <c r="O120" s="4"/>
+    </row>
+    <row r="121" ht="71.25">
       <c r="A121" s="4">
         <v>120</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C121" s="4">
         <v>19</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>440</v>
+        <v>470</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>441</v>
+        <v>471</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>438</v>
+        <v>468</v>
       </c>
       <c r="G121" s="4" t="s">
         <v>80</v>
@@ -6536,37 +6682,37 @@
         <v>49</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>442</v>
+        <v>472</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>442</v>
+        <v>472</v>
       </c>
       <c r="L121" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="M121" s="4"/>
+        <v>313</v>
+      </c>
+      <c r="M121" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="N121" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="O121" s="4" t="s">
-        <v>83</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="O121" s="4"/>
     </row>
     <row r="122" ht="30.75">
       <c r="A122" s="4">
         <v>121</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C122" s="4">
         <v>20</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>443</v>
+        <v>473</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F122" s="4"/>
       <c r="G122" s="4"/>
@@ -6586,16 +6732,16 @@
         <v>122</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C123" s="4">
         <v>21</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>444</v>
+        <v>474</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F123" s="4"/>
       <c r="G123" s="4"/>
@@ -6615,22 +6761,22 @@
         <v>123</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C124" s="4">
         <v>22</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>445</v>
+        <v>475</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>446</v>
+        <v>476</v>
       </c>
       <c r="F124" s="4"/>
       <c r="G124" s="4"/>
       <c r="H124" s="4"/>
       <c r="I124" s="4" t="s">
-        <v>447</v>
+        <v>477</v>
       </c>
       <c r="J124" s="4"/>
       <c r="K124" s="4"/>
@@ -6640,52 +6786,54 @@
         <v>11</v>
       </c>
       <c r="O124" s="4" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="125" ht="98.25">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="125" ht="57.75">
       <c r="A125" s="4">
         <v>124</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C125" s="4">
         <v>23</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>449</v>
+        <v>479</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>451</v>
+        <v>481</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="I125" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="L125" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="M125" s="4"/>
+        <v>483</v>
+      </c>
+      <c r="M125" s="4" t="s">
+        <v>484</v>
+      </c>
       <c r="N125" s="4" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="O125" s="4" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
     </row>
     <row r="126" ht="57.75">
@@ -6693,25 +6841,25 @@
         <v>125</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C126" s="4">
         <v>24</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>454</v>
+        <v>485</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>455</v>
+        <v>486</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>421</v>
+        <v>448</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>422</v>
+        <v>449</v>
       </c>
       <c r="I126" s="4" t="s">
         <v>42</v>
@@ -6730,19 +6878,19 @@
         <v>126</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C127" s="4">
         <v>25</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>456</v>
+        <v>487</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>457</v>
+        <v>488</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G127" s="4">
         <v>0</v>
@@ -6767,25 +6915,25 @@
         <v>127</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C128" s="4">
         <v>26</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>458</v>
+        <v>489</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>459</v>
+        <v>490</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>461</v>
+        <v>492</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>461</v>
+        <v>492</v>
       </c>
       <c r="I128" s="4" t="s">
         <v>42</v>
@@ -6798,7 +6946,7 @@
         <v>9</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>462</v>
+        <v>493</v>
       </c>
     </row>
     <row r="129" ht="30.75">
@@ -6806,16 +6954,16 @@
         <v>128</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C129" s="4">
         <v>27</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>463</v>
+        <v>494</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F129" s="4"/>
       <c r="G129" s="4"/>
@@ -6830,24 +6978,24 @@
       </c>
       <c r="O129" s="4"/>
     </row>
-    <row r="130" ht="84.75">
+    <row r="130" ht="71.25">
       <c r="A130" s="4">
         <v>129</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C130" s="4">
         <v>28</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>464</v>
+        <v>495</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>465</v>
+        <v>496</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>466</v>
+        <v>497</v>
       </c>
       <c r="G130" s="4">
         <v>0</v>
@@ -6859,40 +7007,40 @@
         <v>49</v>
       </c>
       <c r="J130" s="4" t="s">
-        <v>467</v>
+        <v>498</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>467</v>
+        <v>498</v>
       </c>
       <c r="L130" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="M130" s="4"/>
+        <v>498</v>
+      </c>
+      <c r="M130" s="4" t="s">
+        <v>499</v>
+      </c>
       <c r="N130" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="O130" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="131" ht="84.75">
+        <v>3</v>
+      </c>
+      <c r="O130" s="4"/>
+    </row>
+    <row r="131" ht="71.25">
       <c r="A131" s="4">
         <v>130</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C131" s="4">
         <v>29</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>468</v>
+        <v>500</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>469</v>
+        <v>501</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>466</v>
+        <v>497</v>
       </c>
       <c r="G131" s="4">
         <v>0</v>
@@ -6904,37 +7052,37 @@
         <v>49</v>
       </c>
       <c r="J131" s="4" t="s">
-        <v>470</v>
+        <v>502</v>
       </c>
       <c r="K131" s="4" t="s">
-        <v>470</v>
+        <v>502</v>
       </c>
       <c r="L131" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="M131" s="4"/>
+        <v>502</v>
+      </c>
+      <c r="M131" s="4" t="s">
+        <v>503</v>
+      </c>
       <c r="N131" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="O131" s="4" t="s">
-        <v>83</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="O131" s="4"/>
     </row>
     <row r="132" ht="30.75">
       <c r="A132" s="4">
         <v>131</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C132" s="4">
         <v>30</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>471</v>
+        <v>504</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F132" s="4"/>
       <c r="G132" s="4"/>
@@ -6954,16 +7102,16 @@
         <v>132</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C133" s="4">
         <v>31</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>472</v>
+        <v>505</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F133" s="4"/>
       <c r="G133" s="4"/>
@@ -6983,70 +7131,70 @@
         <v>133</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C134" s="4">
         <v>32</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>473</v>
+        <v>506</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>474</v>
+        <v>507</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>475</v>
+        <v>508</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>410</v>
+        <v>433</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J134" s="4" t="s">
-        <v>476</v>
+        <v>509</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>477</v>
+        <v>510</v>
       </c>
       <c r="L134" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="M134" s="4"/>
+        <v>510</v>
+      </c>
+      <c r="M134" s="4" t="s">
+        <v>511</v>
+      </c>
       <c r="N134" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="O134" s="4" t="s">
-        <v>83</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="O134" s="4"/>
     </row>
     <row r="135" ht="125.25">
       <c r="A135" s="4">
         <v>134</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C135" s="4">
         <v>33</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>478</v>
+        <v>512</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>479</v>
+        <v>513</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>460</v>
+        <v>491</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>480</v>
+        <v>514</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>480</v>
+        <v>514</v>
       </c>
       <c r="I135" s="4" t="s">
         <v>42</v>
@@ -7059,7 +7207,7 @@
         <v>9</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>481</v>
+        <v>515</v>
       </c>
     </row>
     <row r="136" ht="84.75">
@@ -7067,16 +7215,16 @@
         <v>135</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="C136" s="4">
         <v>34</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>482</v>
+        <v>516</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>41</v>
@@ -7084,17 +7232,21 @@
       <c r="G136" s="4"/>
       <c r="H136" s="4"/>
       <c r="I136" s="4" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="J136" s="4"/>
       <c r="K136" s="4"/>
-      <c r="L136" s="4"/>
-      <c r="M136" s="4"/>
+      <c r="L136" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="M136" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="N136" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>483</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>

--- a/documents/STI2004-pinout-check.xlsx
+++ b/documents/STI2004-pinout-check.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="549">
   <si>
     <t>Status</t>
   </si>
@@ -244,7 +244,7 @@
     <t>IN_STARTER_SWITCH</t>
   </si>
   <si>
-    <t>M1.IN_SENS2_S8; R19.1</t>
+    <t>M1.IN_SENS2_S8; R30.1</t>
   </si>
   <si>
     <t>Cranking: 8-14</t>
@@ -265,7 +265,7 @@
     <t>IN_NEUTRAL_SWITCH</t>
   </si>
   <si>
-    <t>M1.IN_AUX2_S12</t>
+    <t>M1.IN_AUX2_S12; R44.1</t>
   </si>
   <si>
     <t>D10</t>
@@ -352,7 +352,7 @@
     <t>IN_AC_REQUEST</t>
   </si>
   <si>
-    <t>M1.IN_SENS3_S7; R20.1</t>
+    <t>M1.IN_SENS3_S7; R31.1</t>
   </si>
   <si>
     <t>D17</t>
@@ -397,6 +397,12 @@
     <t>&lt;1 &lt;-&gt; &gt;4</t>
   </si>
   <si>
+    <t>K_LINE</t>
+  </si>
+  <si>
+    <t>JP4.2_2; M10.LIN_V4; P8.Pin_1_1</t>
+  </si>
+  <si>
     <t>D21</t>
   </si>
   <si>
@@ -460,7 +466,10 @@
     <t>FUEL_PUMP_SIGNAL2</t>
   </si>
   <si>
-    <t>Net is named but reaches no module or rail</t>
+    <t>FP_STATUS</t>
+  </si>
+  <si>
+    <t>JP7.1_1; P12.Pin_1_1</t>
   </si>
   <si>
     <t>D29</t>
@@ -472,7 +481,13 @@
     <t>WI-112</t>
   </si>
   <si>
-    <t>Not in the FSM I/O table; see note; Red/white wire to data link connector pin 6 (WI-112); function not in the I/O table. Leave unconnected.</t>
+    <t>DLC6_D29</t>
+  </si>
+  <si>
+    <t>JP4.1_1; P13.Pin_1_1</t>
+  </si>
+  <si>
+    <t>Red/white wire to data link connector pin 6 (WI-112); function not in the I/O table. Leave unconnected.</t>
   </si>
   <si>
     <t>D30</t>
@@ -556,6 +571,12 @@
     <t>EN(STi)-22</t>
   </si>
   <si>
+    <t>IN_CRUISE_MAIN</t>
+  </si>
+  <si>
+    <t>M1.IN_D1_S4; R35.1</t>
+  </si>
+  <si>
     <t>C8</t>
   </si>
   <si>
@@ -571,7 +592,7 @@
     <t>IN_BRAKE_SW2</t>
   </si>
   <si>
-    <t>M1.IN_SENS4_S6; R21.1</t>
+    <t>M1.IN_SENS4_S6; R32.1</t>
   </si>
   <si>
     <t>C9</t>
@@ -589,7 +610,7 @@
     <t>IN_BRAKE_SW1</t>
   </si>
   <si>
-    <t>M1.IN_O2S2_S15; R23.1</t>
+    <t>M1.IN_O2S2_S15; R34.1</t>
   </si>
   <si>
     <t>C10</t>
@@ -598,12 +619,24 @@
     <t>RESUME/ACCEL switch</t>
   </si>
   <si>
+    <t>IN_CRUISE_RESUME</t>
+  </si>
+  <si>
+    <t>M1.IN_D3_S2; R36.1</t>
+  </si>
+  <si>
     <t>C11</t>
   </si>
   <si>
     <t>SET/COAST switch</t>
   </si>
   <si>
+    <t>IN_CRUISE_SET</t>
+  </si>
+  <si>
+    <t>M1.IN_D4_S1; R37.1</t>
+  </si>
+  <si>
     <t>C12</t>
   </si>
   <si>
@@ -742,7 +775,7 @@
     <t>IN_FUEL_LEVEL</t>
   </si>
   <si>
-    <t>M1.IN_AT1_S27</t>
+    <t>M1.IN_AT1_S27; R45.1</t>
   </si>
   <si>
     <t>C21</t>
@@ -880,6 +913,12 @@
     <t>Mass air flow sensor GND</t>
   </si>
   <si>
+    <t>GND_SENSOR</t>
+  </si>
+  <si>
+    <t>JP8.1_1; JP9.1_1</t>
+  </si>
+  <si>
     <t>C32</t>
   </si>
   <si>
@@ -985,7 +1024,7 @@
     <t>IN_CAM</t>
   </si>
   <si>
-    <t>M1.IN_CAM_S24</t>
+    <t>M1.IN_CAM_S24; R42.1</t>
   </si>
   <si>
     <t>B9</t>
@@ -1000,7 +1039,7 @@
     <t>IN_CAM_RH</t>
   </si>
   <si>
-    <t>M1.IN_AUX1_S13</t>
+    <t>M1.IN_AUX1_S13; R43.1</t>
   </si>
   <si>
     <t>B10</t>
@@ -1180,7 +1219,7 @@
     <t>FUEL_PUMP_SIGNAL1</t>
   </si>
   <si>
-    <t>M1.IGN5_W7</t>
+    <t>R39.2; R40.1; R41.1</t>
   </si>
   <si>
     <t>Waveform</t>
@@ -1267,7 +1306,7 @@
     <t>IN_CLUTCH</t>
   </si>
   <si>
-    <t>M1.IN_RES1_S17; R22.1</t>
+    <t>M1.IN_RES1_S17; R33.1</t>
   </si>
   <si>
     <t>A2</t>
@@ -1276,6 +1315,12 @@
     <t>Front A/F sensor heater signal 2</t>
   </si>
   <si>
+    <t>WBO_HEATER</t>
+  </si>
+  <si>
+    <t>M3.LSU_H+_E5; P5.Pin_1_1</t>
+  </si>
+  <si>
     <t>Joined with A3 in the harness to A/F heater B18 pin 1 (WI-113); heater +12 V comes from the main relay</t>
   </si>
   <si>
@@ -1366,12 +1411,24 @@
     <t>ON &lt;=1 / OFF 13-14</t>
   </si>
   <si>
+    <t>EVAP_A12</t>
+  </si>
+  <si>
+    <t>JP5.2_2</t>
+  </si>
+  <si>
     <t>A13</t>
   </si>
   <si>
     <t>Drain valve</t>
   </si>
   <si>
+    <t>EVAP_A13</t>
+  </si>
+  <si>
+    <t>JP6.2_2</t>
+  </si>
+  <si>
     <t>A14</t>
   </si>
   <si>
@@ -1393,12 +1450,24 @@
     <t>low-side output (lamp)</t>
   </si>
   <si>
+    <t>OUT_CRUISE_MAIN_LIGHT</t>
+  </si>
+  <si>
+    <t>Q17.D_2</t>
+  </si>
+  <si>
     <t>A16</t>
   </si>
   <si>
     <t>Cruise control set light</t>
   </si>
   <si>
+    <t>OUT_CRUISE_SET_LIGHT</t>
+  </si>
+  <si>
+    <t>Q18.D_2</t>
+  </si>
+  <si>
     <t>A17</t>
   </si>
   <si>
@@ -1450,7 +1519,13 @@
     <t>WI-111</t>
   </si>
   <si>
-    <t>Not in the FSM I/O table; see note; Blue (L) wire to REF. TO CHG-01 (charging system); function not in the I/O table, likely alternator signal. Not spare: do not ground or drive it. Measure on the car.</t>
+    <t>CHARGE_A22</t>
+  </si>
+  <si>
+    <t>P11.Pin_1_1</t>
+  </si>
+  <si>
+    <t>Blue (L) wire to REF. TO CHG-01 (charging system); function not in the I/O table, likely alternator signal. Not spare: do not ground or drive it. Measure on the car.</t>
   </si>
   <si>
     <t>A23</t>
@@ -1468,7 +1543,7 @@
     <t>OUT_TACH</t>
   </si>
   <si>
-    <t>Q16.D_2</t>
+    <t>Q16.D_2; R38.1</t>
   </si>
   <si>
     <t>A24</t>
@@ -1483,6 +1558,12 @@
     <t>Front A/F sensor shield</t>
   </si>
   <si>
+    <t>WBO_IP_J1</t>
+  </si>
+  <si>
+    <t>JP3.2_2</t>
+  </si>
+  <si>
     <t>A26</t>
   </si>
   <si>
@@ -1495,6 +1576,12 @@
     <t>2.4-2.7</t>
   </si>
   <si>
+    <t>WBO_VM_J1</t>
+  </si>
+  <si>
+    <t>JP2.2_2</t>
+  </si>
+  <si>
     <t>Denso 4-wire A/F sensor (plug B18 pin 4; WI-113); not a Bosch LSU</t>
   </si>
   <si>
@@ -1559,6 +1646,12 @@
   </si>
   <si>
     <t>2.8-3.2</t>
+  </si>
+  <si>
+    <t>WBO_UN_J1</t>
+  </si>
+  <si>
+    <t>JP1.2_2</t>
   </si>
   <si>
     <t>Denso 4-wire A/F sensor (plug B18 pin 3; WI-113); not a Bosch LSU</t>
@@ -1816,7 +1909,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -1838,7 +1931,7 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -1849,7 +1942,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -1860,7 +1953,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
@@ -2761,7 +2854,7 @@
       </c>
       <c r="O20" s="4"/>
     </row>
-    <row r="21" ht="57.75">
+    <row r="21" ht="71.25">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -2791,10 +2884,14 @@
       </c>
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
+      <c r="L21" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>128</v>
+      </c>
       <c r="N21" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O21" s="4"/>
     </row>
@@ -2809,7 +2906,7 @@
         <v>21</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>121</v>
@@ -2838,7 +2935,7 @@
         <v>22</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>121</v>
@@ -2849,7 +2946,7 @@
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -2869,7 +2966,7 @@
         <v>23</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>121</v>
@@ -2898,13 +2995,13 @@
         <v>24</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G25" s="4">
         <v>0</v>
@@ -2923,7 +3020,7 @@
         <v>9</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" ht="57.75">
@@ -2937,30 +3034,30 @@
         <v>25</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G26" s="4">
         <v>0</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="N26" s="4" t="s">
         <v>3</v>
@@ -2978,7 +3075,7 @@
         <v>26</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>121</v>
@@ -3007,7 +3104,7 @@
         <v>27</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>121</v>
@@ -3025,7 +3122,7 @@
       </c>
       <c r="O28" s="4"/>
     </row>
-    <row r="29" ht="84.75">
+    <row r="29" ht="57.75">
       <c r="A29" s="4">
         <v>28</v>
       </c>
@@ -3036,13 +3133,13 @@
         <v>28</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G29" s="5">
         <v>46308</v>
@@ -3055,20 +3152,20 @@
       </c>
       <c r="J29" s="4"/>
       <c r="K29" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="M29" s="4"/>
+        <v>150</v>
+      </c>
+      <c r="M29" s="4" t="s">
+        <v>151</v>
+      </c>
       <c r="N29" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="O29" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="30" ht="232.5">
+        <v>3</v>
+      </c>
+      <c r="O29" s="4"/>
+    </row>
+    <row r="30" ht="178.5">
       <c r="A30" s="4">
         <v>29</v>
       </c>
@@ -3079,26 +3176,30 @@
         <v>29</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
-      <c r="L30" s="4"/>
-      <c r="M30" s="4"/>
+      <c r="L30" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="M30" s="4" t="s">
+        <v>156</v>
+      </c>
       <c r="N30" s="4" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" ht="30.75">
@@ -3112,7 +3213,7 @@
         <v>30</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>121</v>
@@ -3141,13 +3242,13 @@
         <v>31</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G32" s="4">
         <v>0</v>
@@ -3156,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J32" s="4"/>
       <c r="K32" s="4" t="s">
@@ -3178,13 +3279,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C33" s="4">
         <v>1</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>121</v>
@@ -3207,13 +3308,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C34" s="4">
         <v>2</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>121</v>
@@ -3236,19 +3337,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C35" s="4">
         <v>3</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G35" s="5">
         <v>46308</v>
@@ -3261,13 +3362,13 @@
       </c>
       <c r="J35" s="4"/>
       <c r="K35" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="N35" s="4" t="s">
         <v>3</v>
@@ -3279,19 +3380,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C36" s="4">
         <v>4</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G36" s="5">
         <v>46308</v>
@@ -3304,13 +3405,13 @@
       </c>
       <c r="J36" s="4"/>
       <c r="K36" s="4" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="N36" s="4" t="s">
         <v>3</v>
@@ -3322,19 +3423,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C37" s="4">
         <v>5</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G37" s="5">
         <v>46308</v>
@@ -3347,13 +3448,13 @@
       </c>
       <c r="J37" s="4"/>
       <c r="K37" s="4" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="N37" s="4" t="s">
         <v>3</v>
@@ -3365,19 +3466,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C38" s="4">
         <v>6</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G38" s="5">
         <v>46308</v>
@@ -3390,13 +3491,13 @@
       </c>
       <c r="J38" s="4"/>
       <c r="K38" s="4" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="N38" s="4" t="s">
         <v>3</v>
@@ -3408,16 +3509,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C39" s="4">
         <v>7</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>73</v>
@@ -3429,14 +3530,18 @@
         <v>81</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="4"/>
+      <c r="L39" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="M39" s="4" t="s">
+        <v>186</v>
+      </c>
       <c r="N39" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O39" s="4"/>
     </row>
@@ -3445,36 +3550,36 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C40" s="4">
         <v>8</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>73</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
       <c r="L40" s="4" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="N40" s="4" t="s">
         <v>3</v>
@@ -3486,25 +3591,25 @@
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C41" s="4">
         <v>9</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>86</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>49</v>
@@ -3512,10 +3617,10 @@
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
       <c r="L41" s="4" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="M41" s="4" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="N41" s="4" t="s">
         <v>3</v>
@@ -3527,16 +3632,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C42" s="4">
         <v>10</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>73</v>
@@ -3548,14 +3653,18 @@
         <v>81</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="4"/>
+      <c r="L42" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="M42" s="4" t="s">
+        <v>202</v>
+      </c>
       <c r="N42" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O42" s="4"/>
     </row>
@@ -3564,16 +3673,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C43" s="4">
         <v>11</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>73</v>
@@ -3589,10 +3698,14 @@
       </c>
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
-      <c r="M43" s="4"/>
+      <c r="L43" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="M43" s="4" t="s">
+        <v>206</v>
+      </c>
       <c r="N43" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O43" s="4"/>
     </row>
@@ -3601,25 +3714,25 @@
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C44" s="4">
         <v>12</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>42</v>
@@ -3632,7 +3745,7 @@
         <v>9</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
     </row>
     <row r="45" ht="71.25">
@@ -3640,44 +3753,44 @@
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C45" s="4">
         <v>13</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J45" s="4"/>
       <c r="K45" s="4" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="N45" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="46" ht="71.25">
@@ -3685,44 +3798,44 @@
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C46" s="4">
         <v>14</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J46" s="4"/>
       <c r="K46" s="4" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="N46" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" ht="71.25">
@@ -3730,19 +3843,19 @@
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C47" s="4">
         <v>15</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="G47" s="4">
         <v>5</v>
@@ -3755,13 +3868,13 @@
       </c>
       <c r="J47" s="4"/>
       <c r="K47" s="4" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="N47" s="4" t="s">
         <v>3</v>
@@ -3773,19 +3886,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C48" s="4">
         <v>16</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="G48" s="4">
         <v>5</v>
@@ -3797,22 +3910,22 @@
         <v>74</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="N48" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
     </row>
     <row r="49" ht="57.75">
@@ -3820,40 +3933,40 @@
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C49" s="4">
         <v>17</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="N49" s="4" t="s">
         <v>3</v>
@@ -3865,40 +3978,40 @@
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C50" s="4">
         <v>18</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="N50" s="4" t="s">
         <v>3</v>
@@ -3910,13 +4023,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C51" s="4">
         <v>19</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>121</v>
@@ -3939,38 +4052,38 @@
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C52" s="4">
         <v>20</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J52" s="4"/>
       <c r="K52" s="4" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="N52" s="4" t="s">
         <v>3</v>
@@ -3982,25 +4095,25 @@
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C53" s="4">
         <v>21</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>42</v>
@@ -4019,25 +4132,25 @@
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C54" s="4">
         <v>22</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>42</v>
@@ -4045,10 +4158,10 @@
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
       <c r="L54" s="4" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="N54" s="4" t="s">
         <v>3</v>
@@ -4060,38 +4173,38 @@
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C55" s="4">
         <v>23</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="M55" s="4" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="N55" s="4" t="s">
         <v>3</v>
@@ -4103,13 +4216,13 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C56" s="4">
         <v>24</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>121</v>
@@ -4132,19 +4245,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C57" s="4">
         <v>25</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="G57" s="4">
         <v>2.8</v>
@@ -4157,13 +4270,13 @@
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="M57" s="4" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="N57" s="4" t="s">
         <v>3</v>
@@ -4175,40 +4288,40 @@
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C58" s="4">
         <v>26</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>74</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="M58" s="4" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="N58" s="4" t="s">
         <v>3</v>
@@ -4220,40 +4333,40 @@
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C59" s="4">
         <v>27</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="I59" s="4" t="s">
         <v>74</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="N59" s="4" t="s">
         <v>3</v>
@@ -4265,40 +4378,40 @@
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C60" s="4">
         <v>28</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="N60" s="4" t="s">
         <v>3</v>
@@ -4310,40 +4423,40 @@
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C61" s="4">
         <v>29</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="N61" s="4" t="s">
         <v>3</v>
@@ -4355,13 +4468,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C62" s="4">
         <v>30</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>121</v>
@@ -4384,16 +4497,16 @@
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C63" s="4">
         <v>31</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>48</v>
@@ -4405,17 +4518,17 @@
         <v>0</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4" t="s">
         <v>43</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>43</v>
+        <v>299</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>44</v>
+        <v>300</v>
       </c>
       <c r="N63" s="4" t="s">
         <v>3</v>
@@ -4427,19 +4540,19 @@
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C64" s="4">
         <v>32</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G64" s="4">
         <v>0</v>
@@ -4448,7 +4561,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J64" s="4"/>
       <c r="K64" s="4" t="s">
@@ -4470,19 +4583,19 @@
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C65" s="4">
         <v>33</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>290</v>
+        <v>303</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G65" s="4">
         <v>0</v>
@@ -4513,16 +4626,16 @@
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C66" s="4">
         <v>34</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>292</v>
+        <v>305</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>293</v>
+        <v>306</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>48</v>
@@ -4537,16 +4650,16 @@
         <v>49</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="K66" s="4" t="s">
         <v>43</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>43</v>
+        <v>299</v>
       </c>
       <c r="M66" s="4" t="s">
-        <v>44</v>
+        <v>300</v>
       </c>
       <c r="N66" s="4" t="s">
         <v>3</v>
@@ -4558,16 +4671,16 @@
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="C67" s="4">
         <v>35</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>48</v>
@@ -4579,23 +4692,23 @@
         <v>0</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J67" s="4"/>
       <c r="K67" s="4" t="s">
         <v>43</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>43</v>
+        <v>299</v>
       </c>
       <c r="M67" s="4" t="s">
-        <v>44</v>
+        <v>300</v>
       </c>
       <c r="N67" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
     </row>
     <row r="68" ht="44.25">
@@ -4603,16 +4716,16 @@
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C68" s="4">
         <v>1</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>299</v>
+        <v>312</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>41</v>
@@ -4646,36 +4759,36 @@
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C69" s="4">
         <v>2</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J69" s="4"/>
       <c r="K69" s="4"/>
       <c r="L69" s="4" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="M69" s="4" t="s">
-        <v>306</v>
+        <v>319</v>
       </c>
       <c r="N69" s="4" t="s">
         <v>3</v>
@@ -4687,13 +4800,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C70" s="4">
         <v>3</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>121</v>
@@ -4716,16 +4829,16 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C71" s="4">
         <v>4</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>41</v>
@@ -4759,19 +4872,19 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C72" s="4">
         <v>5</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="G72" s="5">
         <v>46308</v>
@@ -4783,13 +4896,13 @@
         <v>74</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="M72" s="4" t="s">
         <v>44</v>
@@ -4804,19 +4917,19 @@
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C73" s="4">
         <v>6</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>314</v>
+        <v>327</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="G73" s="5">
         <v>46308</v>
@@ -4828,13 +4941,13 @@
         <v>74</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="M73" s="4" t="s">
         <v>44</v>
@@ -4849,13 +4962,13 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C74" s="4">
         <v>7</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>121</v>
@@ -4878,40 +4991,40 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C75" s="4">
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>321</v>
+        <v>334</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>322</v>
+        <v>335</v>
       </c>
       <c r="M75" s="4" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="N75" s="4" t="s">
         <v>3</v>
@@ -4923,40 +5036,40 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C76" s="4">
         <v>9</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>326</v>
+        <v>339</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>327</v>
+        <v>340</v>
       </c>
       <c r="M76" s="4" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="N76" s="4" t="s">
         <v>3</v>
@@ -4968,40 +5081,40 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C77" s="4">
         <v>10</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>329</v>
+        <v>342</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="G77" s="4">
         <v>0</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>332</v>
+        <v>345</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>320</v>
+        <v>333</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>333</v>
+        <v>346</v>
       </c>
       <c r="M77" s="4" t="s">
-        <v>334</v>
+        <v>347</v>
       </c>
       <c r="N77" s="4" t="s">
         <v>3</v>
@@ -5013,13 +5126,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C78" s="4">
         <v>11</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>335</v>
+        <v>348</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>121</v>
@@ -5042,16 +5155,16 @@
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C79" s="4">
         <v>12</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>41</v>
@@ -5085,13 +5198,13 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C80" s="4">
         <v>13</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>121</v>
@@ -5114,13 +5227,13 @@
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C81" s="4">
         <v>14</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>339</v>
+        <v>352</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>121</v>
@@ -5143,19 +5256,19 @@
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C82" s="4">
         <v>15</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>340</v>
+        <v>353</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="G82" s="4">
         <v>0</v>
@@ -5164,23 +5277,23 @@
         <v>65</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="J82" s="4"/>
       <c r="K82" s="4" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>344</v>
+        <v>357</v>
       </c>
       <c r="M82" s="4" t="s">
-        <v>345</v>
+        <v>358</v>
       </c>
       <c r="N82" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>346</v>
+        <v>359</v>
       </c>
     </row>
     <row r="83" ht="57.75">
@@ -5188,19 +5301,19 @@
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C83" s="4">
         <v>16</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="G83" s="4">
         <v>0</v>
@@ -5213,13 +5326,13 @@
       </c>
       <c r="J83" s="4"/>
       <c r="K83" s="4" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="M83" s="4" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="N83" s="4" t="s">
         <v>3</v>
@@ -5231,19 +5344,19 @@
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C84" s="4">
         <v>17</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>342</v>
+        <v>355</v>
       </c>
       <c r="G84" s="4">
         <v>0</v>
@@ -5256,13 +5369,13 @@
       </c>
       <c r="J84" s="4"/>
       <c r="K84" s="4" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="M84" s="4" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="N84" s="4" t="s">
         <v>3</v>
@@ -5274,19 +5387,19 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C85" s="4">
         <v>18</v>
       </c>
       <c r="D85" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="F85" s="4" t="s">
         <v>355</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>342</v>
       </c>
       <c r="G85" s="4">
         <v>0</v>
@@ -5299,13 +5412,13 @@
       </c>
       <c r="J85" s="4"/>
       <c r="K85" s="4" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="M85" s="4" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="N85" s="4" t="s">
         <v>3</v>
@@ -5317,19 +5430,19 @@
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C86" s="4">
         <v>19</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>361</v>
+        <v>374</v>
       </c>
       <c r="G86" s="5">
         <v>46308</v>
@@ -5342,19 +5455,19 @@
       </c>
       <c r="J86" s="4"/>
       <c r="K86" s="4" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="M86" s="4" t="s">
-        <v>363</v>
+        <v>376</v>
       </c>
       <c r="N86" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>364</v>
+        <v>377</v>
       </c>
     </row>
     <row r="87" ht="30.75">
@@ -5362,13 +5475,13 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C87" s="4">
         <v>20</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>121</v>
@@ -5391,13 +5504,13 @@
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C88" s="4">
         <v>21</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>121</v>
@@ -5420,19 +5533,19 @@
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C89" s="4">
         <v>22</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>331</v>
+        <v>344</v>
       </c>
       <c r="G89" s="4">
         <v>0</v>
@@ -5441,19 +5554,19 @@
         <v>0</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="L89" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="M89" s="4" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="N89" s="4" t="s">
         <v>3</v>
@@ -5465,13 +5578,13 @@
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C90" s="4">
         <v>23</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>121</v>
@@ -5494,44 +5607,44 @@
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C91" s="4">
         <v>24</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>115</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="I91" s="4" t="s">
         <v>74</v>
       </c>
       <c r="J91" s="4"/>
       <c r="K91" s="4" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>376</v>
+        <v>389</v>
       </c>
       <c r="M91" s="4" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="N91" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>378</v>
+        <v>391</v>
       </c>
     </row>
     <row r="92" ht="57.75">
@@ -5539,38 +5652,38 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C92" s="4">
         <v>25</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>379</v>
+        <v>392</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>115</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>74</v>
       </c>
       <c r="J92" s="4"/>
       <c r="K92" s="4" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="M92" s="4" t="s">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="N92" s="4" t="s">
         <v>3</v>
@@ -5582,44 +5695,44 @@
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C93" s="4">
         <v>26</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>383</v>
+        <v>396</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>384</v>
+        <v>397</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="I93" s="4" t="s">
         <v>74</v>
       </c>
       <c r="J93" s="4"/>
       <c r="K93" s="4" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>387</v>
+        <v>400</v>
       </c>
       <c r="M93" s="4" t="s">
-        <v>388</v>
+        <v>401</v>
       </c>
       <c r="N93" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
     </row>
     <row r="94" ht="125.25">
@@ -5627,40 +5740,40 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C94" s="4">
         <v>27</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>390</v>
+        <v>403</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>391</v>
+        <v>404</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>393</v>
+        <v>406</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>394</v>
+        <v>407</v>
       </c>
       <c r="M94" s="4" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
       <c r="N94" s="4" t="s">
         <v>3</v>
@@ -5672,13 +5785,13 @@
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C95" s="4">
         <v>28</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>121</v>
@@ -5701,13 +5814,13 @@
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C96" s="4">
         <v>29</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>397</v>
+        <v>410</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>121</v>
@@ -5730,13 +5843,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C97" s="4">
         <v>30</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>121</v>
@@ -5759,19 +5872,19 @@
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C98" s="4">
         <v>31</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G98" s="4">
         <v>0</v>
@@ -5780,7 +5893,7 @@
         <v>0</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J98" s="4"/>
       <c r="K98" s="4" t="s">
@@ -5802,13 +5915,13 @@
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C99" s="4">
         <v>32</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>121</v>
@@ -5831,25 +5944,25 @@
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C100" s="4">
         <v>33</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>402</v>
+        <v>415</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>115</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>116</v>
@@ -5857,16 +5970,16 @@
       <c r="J100" s="4"/>
       <c r="K100" s="4"/>
       <c r="L100" s="4" t="s">
-        <v>403</v>
+        <v>416</v>
       </c>
       <c r="M100" s="4" t="s">
-        <v>404</v>
+        <v>417</v>
       </c>
       <c r="N100" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>405</v>
+        <v>418</v>
       </c>
     </row>
     <row r="101" ht="30.75">
@@ -5874,13 +5987,13 @@
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C101" s="4">
         <v>34</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>406</v>
+        <v>419</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>121</v>
@@ -5903,16 +6016,16 @@
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="C102" s="4">
         <v>35</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>407</v>
+        <v>420</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>408</v>
+        <v>421</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>115</v>
@@ -5928,19 +6041,19 @@
       </c>
       <c r="J102" s="4"/>
       <c r="K102" s="4" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>409</v>
+        <v>422</v>
       </c>
       <c r="M102" s="4" t="s">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="N102" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>411</v>
+        <v>424</v>
       </c>
     </row>
     <row r="103" ht="57.75">
@@ -5948,40 +6061,40 @@
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C103" s="4">
         <v>1</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>86</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="I103" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>416</v>
+        <v>429</v>
       </c>
       <c r="M103" s="4" t="s">
-        <v>417</v>
+        <v>430</v>
       </c>
       <c r="N103" s="4" t="s">
         <v>3</v>
@@ -5993,38 +6106,42 @@
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C104" s="4">
         <v>2</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>418</v>
+        <v>431</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>419</v>
+        <v>432</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J104" s="4"/>
       <c r="K104" s="4"/>
-      <c r="L104" s="4"/>
-      <c r="M104" s="4"/>
+      <c r="L104" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="M104" s="4" t="s">
+        <v>434</v>
+      </c>
       <c r="N104" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>420</v>
+        <v>435</v>
       </c>
     </row>
     <row r="105" ht="111.75">
@@ -6032,38 +6149,42 @@
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C105" s="4">
         <v>3</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>421</v>
+        <v>436</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>422</v>
+        <v>437</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
-      <c r="L105" s="4"/>
-      <c r="M105" s="4"/>
+      <c r="L105" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="M105" s="4" t="s">
+        <v>434</v>
+      </c>
       <c r="N105" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>423</v>
+        <v>438</v>
       </c>
     </row>
     <row r="106" ht="30.75">
@@ -6071,13 +6192,13 @@
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C106" s="4">
         <v>4</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>121</v>
@@ -6100,13 +6221,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C107" s="4">
         <v>5</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>121</v>
@@ -6129,16 +6250,16 @@
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C108" s="4">
         <v>6</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>426</v>
+        <v>441</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>427</v>
+        <v>442</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>41</v>
@@ -6172,16 +6293,16 @@
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C109" s="4">
         <v>7</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>428</v>
+        <v>443</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>429</v>
+        <v>444</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>41</v>
@@ -6215,25 +6336,25 @@
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C110" s="4">
         <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="I110" s="4" t="s">
         <v>74</v>
@@ -6241,10 +6362,10 @@
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
       <c r="L110" s="4" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="M110" s="4" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="N110" s="4" t="s">
         <v>3</v>
@@ -6256,25 +6377,25 @@
         <v>110</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C111" s="4">
         <v>9</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="I111" s="4" t="s">
         <v>74</v>
@@ -6282,10 +6403,10 @@
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
       <c r="L111" s="4" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="M111" s="4" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="N111" s="4" t="s">
         <v>3</v>
@@ -6297,25 +6418,25 @@
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C112" s="4">
         <v>10</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>441</v>
+        <v>456</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="I112" s="4" t="s">
         <v>74</v>
@@ -6323,10 +6444,10 @@
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
       <c r="L112" s="4" t="s">
-        <v>435</v>
+        <v>450</v>
       </c>
       <c r="M112" s="4" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="N112" s="4" t="s">
         <v>3</v>
@@ -6338,25 +6459,25 @@
         <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C113" s="4">
         <v>11</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>443</v>
+        <v>458</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>444</v>
+        <v>459</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="I113" s="4" t="s">
         <v>74</v>
@@ -6364,10 +6485,10 @@
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
       <c r="L113" s="4" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="M113" s="4" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="N113" s="4" t="s">
         <v>3</v>
@@ -6379,35 +6500,39 @@
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C114" s="4">
         <v>12</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>445</v>
+        <v>460</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>446</v>
+        <v>461</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="I114" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J114" s="4"/>
       <c r="K114" s="4"/>
-      <c r="L114" s="4"/>
-      <c r="M114" s="4"/>
+      <c r="L114" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="M114" s="4" t="s">
+        <v>466</v>
+      </c>
       <c r="N114" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O114" s="4"/>
     </row>
@@ -6416,35 +6541,39 @@
         <v>114</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C115" s="4">
         <v>13</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>450</v>
+        <v>467</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>451</v>
+        <v>468</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="I115" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J115" s="4"/>
       <c r="K115" s="4"/>
-      <c r="L115" s="4"/>
-      <c r="M115" s="4"/>
+      <c r="L115" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="M115" s="4" t="s">
+        <v>470</v>
+      </c>
       <c r="N115" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O115" s="4"/>
     </row>
@@ -6453,62 +6582,62 @@
         <v>115</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C116" s="4">
         <v>14</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="I116" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J116" s="4"/>
       <c r="K116" s="4" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="M116" s="4" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="N116" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O116" s="4"/>
     </row>
-    <row r="117" ht="44.25">
+    <row r="117" ht="57.75">
       <c r="A117" s="4">
         <v>116</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C117" s="4">
         <v>15</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="G117" s="4" t="s">
         <v>94</v>
@@ -6521,31 +6650,35 @@
       </c>
       <c r="J117" s="4"/>
       <c r="K117" s="4"/>
-      <c r="L117" s="4"/>
-      <c r="M117" s="4"/>
+      <c r="L117" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="M117" s="4" t="s">
+        <v>479</v>
+      </c>
       <c r="N117" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O117" s="4"/>
     </row>
-    <row r="118" ht="44.25">
+    <row r="118" ht="57.75">
       <c r="A118" s="4">
         <v>117</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C118" s="4">
         <v>16</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>460</v>
+        <v>481</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="G118" s="4" t="s">
         <v>94</v>
@@ -6558,10 +6691,14 @@
       </c>
       <c r="J118" s="4"/>
       <c r="K118" s="4"/>
-      <c r="L118" s="4"/>
-      <c r="M118" s="4"/>
+      <c r="L118" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="M118" s="4" t="s">
+        <v>483</v>
+      </c>
       <c r="N118" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O118" s="4"/>
     </row>
@@ -6570,25 +6707,25 @@
         <v>118</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C119" s="4">
         <v>17</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="I119" s="4" t="s">
         <v>42</v>
@@ -6596,16 +6733,16 @@
       <c r="J119" s="4"/>
       <c r="K119" s="4"/>
       <c r="L119" s="4" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
       <c r="M119" s="4" t="s">
-        <v>464</v>
+        <v>487</v>
       </c>
       <c r="N119" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>465</v>
+        <v>488</v>
       </c>
     </row>
     <row r="120" ht="71.25">
@@ -6613,19 +6750,19 @@
         <v>119</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C120" s="4">
         <v>18</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>466</v>
+        <v>489</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>467</v>
+        <v>490</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="G120" s="4" t="s">
         <v>80</v>
@@ -6637,13 +6774,13 @@
         <v>49</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>469</v>
+        <v>492</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>469</v>
+        <v>492</v>
       </c>
       <c r="L120" s="4" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="M120" s="4" t="s">
         <v>44</v>
@@ -6658,19 +6795,19 @@
         <v>120</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C121" s="4">
         <v>19</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>471</v>
+        <v>494</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>468</v>
+        <v>491</v>
       </c>
       <c r="G121" s="4" t="s">
         <v>80</v>
@@ -6682,13 +6819,13 @@
         <v>49</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="L121" s="4" t="s">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="M121" s="4" t="s">
         <v>44</v>
@@ -6703,13 +6840,13 @@
         <v>121</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C122" s="4">
         <v>20</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>473</v>
+        <v>496</v>
       </c>
       <c r="E122" s="4" t="s">
         <v>121</v>
@@ -6732,13 +6869,13 @@
         <v>122</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C123" s="4">
         <v>21</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>474</v>
+        <v>497</v>
       </c>
       <c r="E123" s="4" t="s">
         <v>121</v>
@@ -6756,37 +6893,41 @@
       </c>
       <c r="O123" s="4"/>
     </row>
-    <row r="124" ht="326.25">
+    <row r="124" ht="272.25">
       <c r="A124" s="4">
         <v>123</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C124" s="4">
         <v>22</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>475</v>
+        <v>498</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>476</v>
+        <v>499</v>
       </c>
       <c r="F124" s="4"/>
       <c r="G124" s="4"/>
       <c r="H124" s="4"/>
       <c r="I124" s="4" t="s">
-        <v>477</v>
+        <v>500</v>
       </c>
       <c r="J124" s="4"/>
       <c r="K124" s="4"/>
-      <c r="L124" s="4"/>
-      <c r="M124" s="4"/>
+      <c r="L124" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="M124" s="4" t="s">
+        <v>502</v>
+      </c>
       <c r="N124" s="4" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="O124" s="4" t="s">
-        <v>478</v>
+        <v>503</v>
       </c>
     </row>
     <row r="125" ht="57.75">
@@ -6794,46 +6935,46 @@
         <v>124</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C125" s="4">
         <v>23</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>479</v>
+        <v>504</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>480</v>
+        <v>505</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>481</v>
+        <v>506</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>482</v>
+        <v>507</v>
       </c>
       <c r="I125" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>483</v>
+        <v>508</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>483</v>
+        <v>508</v>
       </c>
       <c r="L125" s="4" t="s">
-        <v>483</v>
+        <v>508</v>
       </c>
       <c r="M125" s="4" t="s">
-        <v>484</v>
+        <v>509</v>
       </c>
       <c r="N125" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O125" s="4" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
     </row>
     <row r="126" ht="57.75">
@@ -6841,25 +6982,25 @@
         <v>125</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C126" s="4">
         <v>24</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>485</v>
+        <v>510</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>486</v>
+        <v>511</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>447</v>
+        <v>462</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>448</v>
+        <v>463</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>449</v>
+        <v>464</v>
       </c>
       <c r="I126" s="4" t="s">
         <v>42</v>
@@ -6878,19 +7019,19 @@
         <v>126</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C127" s="4">
         <v>25</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>487</v>
+        <v>512</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>488</v>
+        <v>513</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="G127" s="4">
         <v>0</v>
@@ -6903,10 +7044,14 @@
       </c>
       <c r="J127" s="4"/>
       <c r="K127" s="4"/>
-      <c r="L127" s="4"/>
-      <c r="M127" s="4"/>
+      <c r="L127" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="M127" s="4" t="s">
+        <v>515</v>
+      </c>
       <c r="N127" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O127" s="4"/>
     </row>
@@ -6915,38 +7060,42 @@
         <v>127</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C128" s="4">
         <v>26</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>489</v>
+        <v>516</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>490</v>
+        <v>517</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>491</v>
+        <v>518</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>492</v>
+        <v>519</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>492</v>
+        <v>519</v>
       </c>
       <c r="I128" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J128" s="4"/>
       <c r="K128" s="4"/>
-      <c r="L128" s="4"/>
-      <c r="M128" s="4"/>
+      <c r="L128" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="M128" s="4" t="s">
+        <v>521</v>
+      </c>
       <c r="N128" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>493</v>
+        <v>522</v>
       </c>
     </row>
     <row r="129" ht="30.75">
@@ -6954,13 +7103,13 @@
         <v>128</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C129" s="4">
         <v>27</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>494</v>
+        <v>523</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>121</v>
@@ -6983,19 +7132,19 @@
         <v>129</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C130" s="4">
         <v>28</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>495</v>
+        <v>524</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>496</v>
+        <v>525</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>497</v>
+        <v>526</v>
       </c>
       <c r="G130" s="4">
         <v>0</v>
@@ -7007,16 +7156,16 @@
         <v>49</v>
       </c>
       <c r="J130" s="4" t="s">
-        <v>498</v>
+        <v>527</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>498</v>
+        <v>527</v>
       </c>
       <c r="L130" s="4" t="s">
-        <v>498</v>
+        <v>527</v>
       </c>
       <c r="M130" s="4" t="s">
-        <v>499</v>
+        <v>528</v>
       </c>
       <c r="N130" s="4" t="s">
         <v>3</v>
@@ -7028,19 +7177,19 @@
         <v>130</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C131" s="4">
         <v>29</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>500</v>
+        <v>529</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>501</v>
+        <v>530</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>497</v>
+        <v>526</v>
       </c>
       <c r="G131" s="4">
         <v>0</v>
@@ -7052,16 +7201,16 @@
         <v>49</v>
       </c>
       <c r="J131" s="4" t="s">
-        <v>502</v>
+        <v>531</v>
       </c>
       <c r="K131" s="4" t="s">
-        <v>502</v>
+        <v>531</v>
       </c>
       <c r="L131" s="4" t="s">
-        <v>502</v>
+        <v>531</v>
       </c>
       <c r="M131" s="4" t="s">
-        <v>503</v>
+        <v>532</v>
       </c>
       <c r="N131" s="4" t="s">
         <v>3</v>
@@ -7073,13 +7222,13 @@
         <v>131</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C132" s="4">
         <v>30</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>504</v>
+        <v>533</v>
       </c>
       <c r="E132" s="4" t="s">
         <v>121</v>
@@ -7102,13 +7251,13 @@
         <v>132</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C133" s="4">
         <v>31</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>505</v>
+        <v>534</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>121</v>
@@ -7131,40 +7280,40 @@
         <v>133</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C134" s="4">
         <v>32</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>506</v>
+        <v>535</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>507</v>
+        <v>536</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>508</v>
+        <v>537</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>434</v>
+        <v>449</v>
       </c>
       <c r="I134" s="4" t="s">
         <v>74</v>
       </c>
       <c r="J134" s="4" t="s">
-        <v>509</v>
+        <v>538</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>510</v>
+        <v>539</v>
       </c>
       <c r="L134" s="4" t="s">
-        <v>510</v>
+        <v>539</v>
       </c>
       <c r="M134" s="4" t="s">
-        <v>511</v>
+        <v>540</v>
       </c>
       <c r="N134" s="4" t="s">
         <v>3</v>
@@ -7176,38 +7325,42 @@
         <v>134</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C135" s="4">
         <v>33</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>512</v>
+        <v>541</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>513</v>
+        <v>542</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>491</v>
+        <v>518</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>514</v>
+        <v>543</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>514</v>
+        <v>543</v>
       </c>
       <c r="I135" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J135" s="4"/>
       <c r="K135" s="4"/>
-      <c r="L135" s="4"/>
-      <c r="M135" s="4"/>
+      <c r="L135" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="M135" s="4" t="s">
+        <v>545</v>
+      </c>
       <c r="N135" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>515</v>
+        <v>546</v>
       </c>
     </row>
     <row r="136" ht="84.75">
@@ -7215,16 +7368,16 @@
         <v>135</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>412</v>
+        <v>425</v>
       </c>
       <c r="C136" s="4">
         <v>34</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>516</v>
+        <v>547</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>41</v>
@@ -7232,7 +7385,7 @@
       <c r="G136" s="4"/>
       <c r="H136" s="4"/>
       <c r="I136" s="4" t="s">
-        <v>343</v>
+        <v>356</v>
       </c>
       <c r="J136" s="4"/>
       <c r="K136" s="4"/>
@@ -7246,7 +7399,7 @@
         <v>3</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>517</v>
+        <v>548</v>
       </c>
     </row>
   </sheetData>

--- a/documents/STI2004-pinout-check.xlsx
+++ b/documents/STI2004-pinout-check.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="549">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="560">
   <si>
     <t>Status</t>
   </si>
@@ -217,7 +217,10 @@
     <t>Net-(F5-Pad1)</t>
   </si>
   <si>
-    <t>F5 -&gt; +12V_ETB -&gt; M2.12V_IN_N2, M2.12V_IN_S1</t>
+    <t>+12V_ETB</t>
+  </si>
+  <si>
+    <t>M2.12V_IN_N2; M2.12V_IN_S1</t>
   </si>
   <si>
     <t>D7</t>
@@ -301,18 +304,36 @@
     <t>ON 0 / OFF 10-13</t>
   </si>
   <si>
+    <t>IN_DEFOG</t>
+  </si>
+  <si>
+    <t>M11.IN_D1_V2; R49.1</t>
+  </si>
+  <si>
     <t>D12</t>
   </si>
   <si>
     <t>Small light switch</t>
   </si>
   <si>
+    <t>IN_SMALL_LIGHT</t>
+  </si>
+  <si>
+    <t>M11.IN_D2_V3; R50.1</t>
+  </si>
+  <si>
     <t>D13</t>
   </si>
   <si>
     <t>Blower fan switch</t>
   </si>
   <si>
+    <t>IN_BLOWER</t>
+  </si>
+  <si>
+    <t>M11.IN_D3_V4; R51.1</t>
+  </si>
+  <si>
     <t>Also shown to auto A/C module (WI-106)</t>
   </si>
   <si>
@@ -325,6 +346,12 @@
     <t>digital in (5 V pull-up)</t>
   </si>
   <si>
+    <t>IN_TEST_MODE</t>
+  </si>
+  <si>
+    <t>M11.IN_D4_V5</t>
+  </si>
+  <si>
     <t>When connected: 0</t>
   </si>
   <si>
@@ -422,6 +449,12 @@
   </si>
   <si>
     <t>digital in</t>
+  </si>
+  <si>
+    <t>IN_BLOWBY</t>
+  </si>
+  <si>
+    <t>M12.IN_D4_V5</t>
   </si>
   <si>
     <t>Disconnected (fault): 5</t>
@@ -1909,7 +1942,7 @@
         <v>3</v>
       </c>
       <c r="B2">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -1942,7 +1975,7 @@
         <v>9</v>
       </c>
       <c r="B5">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -2300,7 +2333,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" ht="84.75">
+    <row r="7" ht="71.25">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -2333,10 +2366,10 @@
         <v>66</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N7" s="4" t="s">
         <v>3</v>
@@ -2354,10 +2387,10 @@
         <v>7</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>41</v>
@@ -2373,7 +2406,7 @@
       </c>
       <c r="J8" s="4"/>
       <c r="K8" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>43</v>
@@ -2397,13 +2430,13 @@
         <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
@@ -2412,23 +2445,23 @@
         <v>0</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J9" s="4"/>
       <c r="K9" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N9" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" ht="44.25">
@@ -2442,32 +2475,32 @@
         <v>9</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N10" s="4" t="s">
         <v>3</v>
@@ -2485,34 +2518,34 @@
         <v>10</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G11" s="5">
         <v>46308</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I11" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N11" s="4" t="s">
         <v>3</v>
@@ -2530,29 +2563,33 @@
         <v>11</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I12" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
+      <c r="L12" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="M12" s="4" t="s">
+        <v>97</v>
+      </c>
       <c r="N12" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O12" s="4"/>
     </row>
@@ -2567,29 +2604,33 @@
         <v>12</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>94</v>
-      </c>
       <c r="H13" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I13" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
+      <c r="L13" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>101</v>
+      </c>
       <c r="N13" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O13" s="4"/>
     </row>
@@ -2604,32 +2645,36 @@
         <v>13</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I14" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
+      <c r="L14" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>105</v>
+      </c>
       <c r="N14" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" ht="44.25">
@@ -2643,13 +2688,13 @@
         <v>14</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="G15" s="4">
         <v>5</v>
@@ -2658,17 +2703,21 @@
         <v>5</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
+      <c r="L15" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>111</v>
+      </c>
       <c r="N15" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" ht="30.75">
@@ -2682,13 +2731,13 @@
         <v>15</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="G16" s="5">
         <v>46308</v>
@@ -2697,17 +2746,17 @@
         <v>65</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="N16" s="4" t="s">
         <v>3</v>
@@ -2725,30 +2774,30 @@
         <v>16</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="N17" s="4" t="s">
         <v>3</v>
@@ -2766,34 +2815,34 @@
         <v>17</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="4" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="N18" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" ht="30.75">
@@ -2807,10 +2856,10 @@
         <v>18</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
@@ -2836,10 +2885,10 @@
         <v>19</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
@@ -2865,19 +2914,19 @@
         <v>20</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="I21" s="4" t="s">
         <v>42</v>
@@ -2885,10 +2934,10 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
       <c r="L21" s="4" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="N21" s="4" t="s">
         <v>3</v>
@@ -2906,10 +2955,10 @@
         <v>21</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
@@ -2935,10 +2984,10 @@
         <v>22</v>
       </c>
       <c r="D23" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>121</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
@@ -2946,7 +2995,7 @@
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
@@ -2966,10 +3015,10 @@
         <v>23</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
@@ -2995,13 +3044,13 @@
         <v>24</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="G25" s="4">
         <v>0</v>
@@ -3014,13 +3063,17 @@
       </c>
       <c r="J25" s="4"/>
       <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
+      <c r="L25" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="N25" s="4" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" ht="57.75">
@@ -3034,30 +3087,30 @@
         <v>25</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="G26" s="4">
         <v>0</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
       <c r="L26" s="4" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="N26" s="4" t="s">
         <v>3</v>
@@ -3075,10 +3128,10 @@
         <v>26</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -3104,10 +3157,10 @@
         <v>27</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -3133,13 +3186,13 @@
         <v>28</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="G29" s="5">
         <v>46308</v>
@@ -3148,17 +3201,17 @@
         <v>65</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J29" s="4"/>
       <c r="K29" s="4" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="N29" s="4" t="s">
         <v>3</v>
@@ -3176,30 +3229,30 @@
         <v>29</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="J30" s="4"/>
       <c r="K30" s="4"/>
       <c r="L30" s="4" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="N30" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
     </row>
     <row r="31" ht="30.75">
@@ -3213,10 +3266,10 @@
         <v>30</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
@@ -3242,13 +3295,13 @@
         <v>31</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="G32" s="4">
         <v>0</v>
@@ -3257,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J32" s="4"/>
       <c r="K32" s="4" t="s">
@@ -3279,16 +3332,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C33" s="4">
         <v>1</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -3308,16 +3361,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C34" s="4">
         <v>2</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -3337,19 +3390,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C35" s="4">
         <v>3</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="G35" s="5">
         <v>46308</v>
@@ -3358,17 +3411,17 @@
         <v>46036</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J35" s="4"/>
       <c r="K35" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="N35" s="4" t="s">
         <v>3</v>
@@ -3380,19 +3433,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C36" s="4">
         <v>4</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="G36" s="5">
         <v>46308</v>
@@ -3401,17 +3454,17 @@
         <v>46036</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J36" s="4"/>
       <c r="K36" s="4" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="N36" s="4" t="s">
         <v>3</v>
@@ -3423,19 +3476,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C37" s="4">
         <v>5</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="G37" s="5">
         <v>46308</v>
@@ -3444,17 +3497,17 @@
         <v>46036</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J37" s="4"/>
       <c r="K37" s="4" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="N37" s="4" t="s">
         <v>3</v>
@@ -3466,19 +3519,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C38" s="4">
         <v>6</v>
       </c>
       <c r="D38" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F38" s="4" t="s">
         <v>178</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>167</v>
       </c>
       <c r="G38" s="5">
         <v>46308</v>
@@ -3487,17 +3540,17 @@
         <v>46036</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J38" s="4"/>
       <c r="K38" s="4" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="N38" s="4" t="s">
         <v>3</v>
@@ -3509,36 +3562,36 @@
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C39" s="4">
         <v>7</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="J39" s="4"/>
       <c r="K39" s="4"/>
       <c r="L39" s="4" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="M39" s="4" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="N39" s="4" t="s">
         <v>3</v>
@@ -3550,36 +3603,36 @@
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C40" s="4">
         <v>8</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
       <c r="L40" s="4" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="N40" s="4" t="s">
         <v>3</v>
@@ -3591,25 +3644,25 @@
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C41" s="4">
         <v>9</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="I41" s="4" t="s">
         <v>49</v>
@@ -3617,10 +3670,10 @@
       <c r="J41" s="4"/>
       <c r="K41" s="4"/>
       <c r="L41" s="4" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="M41" s="4" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="N41" s="4" t="s">
         <v>3</v>
@@ -3632,36 +3685,36 @@
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C42" s="4">
         <v>10</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="J42" s="4"/>
       <c r="K42" s="4"/>
       <c r="L42" s="4" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="N42" s="4" t="s">
         <v>3</v>
@@ -3673,25 +3726,25 @@
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C43" s="4">
         <v>11</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I43" s="4" t="s">
         <v>49</v>
@@ -3699,10 +3752,10 @@
       <c r="J43" s="4"/>
       <c r="K43" s="4"/>
       <c r="L43" s="4" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="N43" s="4" t="s">
         <v>3</v>
@@ -3714,25 +3767,25 @@
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C44" s="4">
         <v>12</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="I44" s="4" t="s">
         <v>42</v>
@@ -3745,7 +3798,7 @@
         <v>9</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
     </row>
     <row r="45" ht="71.25">
@@ -3753,44 +3806,44 @@
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C45" s="4">
         <v>13</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J45" s="4"/>
       <c r="K45" s="4" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="N45" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
     </row>
     <row r="46" ht="71.25">
@@ -3798,44 +3851,44 @@
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C46" s="4">
         <v>14</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J46" s="4"/>
       <c r="K46" s="4" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="N46" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
     </row>
     <row r="47" ht="71.25">
@@ -3843,19 +3896,19 @@
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C47" s="4">
         <v>15</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G47" s="4">
         <v>5</v>
@@ -3868,13 +3921,13 @@
       </c>
       <c r="J47" s="4"/>
       <c r="K47" s="4" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="N47" s="4" t="s">
         <v>3</v>
@@ -3886,19 +3939,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C48" s="4">
         <v>16</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="G48" s="4">
         <v>5</v>
@@ -3907,25 +3960,25 @@
         <v>5</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="N48" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
     </row>
     <row r="49" ht="57.75">
@@ -3933,40 +3986,40 @@
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C49" s="4">
         <v>17</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="N49" s="4" t="s">
         <v>3</v>
@@ -3978,40 +4031,40 @@
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C50" s="4">
         <v>18</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="N50" s="4" t="s">
         <v>3</v>
@@ -4023,16 +4076,16 @@
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C51" s="4">
         <v>19</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
@@ -4052,38 +4105,38 @@
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C52" s="4">
         <v>20</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J52" s="4"/>
       <c r="K52" s="4" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="N52" s="4" t="s">
         <v>3</v>
@@ -4095,25 +4148,25 @@
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C53" s="4">
         <v>21</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>42</v>
@@ -4132,25 +4185,25 @@
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C54" s="4">
         <v>22</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>42</v>
@@ -4158,10 +4211,10 @@
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
       <c r="L54" s="4" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="N54" s="4" t="s">
         <v>3</v>
@@ -4173,38 +4226,38 @@
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C55" s="4">
         <v>23</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="M55" s="4" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
       <c r="N55" s="4" t="s">
         <v>3</v>
@@ -4216,16 +4269,16 @@
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C56" s="4">
         <v>24</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
@@ -4245,19 +4298,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C57" s="4">
         <v>25</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="G57" s="4">
         <v>2.8</v>
@@ -4266,17 +4319,17 @@
         <v>2.8</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="M57" s="4" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="N57" s="4" t="s">
         <v>3</v>
@@ -4288,40 +4341,40 @@
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C58" s="4">
         <v>26</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="M58" s="4" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="N58" s="4" t="s">
         <v>3</v>
@@ -4333,40 +4386,40 @@
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C59" s="4">
         <v>27</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="N59" s="4" t="s">
         <v>3</v>
@@ -4378,40 +4431,40 @@
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C60" s="4">
         <v>28</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="N60" s="4" t="s">
         <v>3</v>
@@ -4423,40 +4476,40 @@
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C61" s="4">
         <v>29</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="N61" s="4" t="s">
         <v>3</v>
@@ -4468,16 +4521,16 @@
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C62" s="4">
         <v>30</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F62" s="4"/>
       <c r="G62" s="4"/>
@@ -4497,16 +4550,16 @@
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C63" s="4">
         <v>31</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>48</v>
@@ -4518,17 +4571,17 @@
         <v>0</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4" t="s">
         <v>43</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="N63" s="4" t="s">
         <v>3</v>
@@ -4540,19 +4593,19 @@
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C64" s="4">
         <v>32</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="G64" s="4">
         <v>0</v>
@@ -4561,7 +4614,7 @@
         <v>0</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J64" s="4"/>
       <c r="K64" s="4" t="s">
@@ -4583,19 +4636,19 @@
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C65" s="4">
         <v>33</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="G65" s="4">
         <v>0</v>
@@ -4604,7 +4657,7 @@
         <v>0</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J65" s="4"/>
       <c r="K65" s="4" t="s">
@@ -4626,16 +4679,16 @@
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C66" s="4">
         <v>34</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>48</v>
@@ -4650,16 +4703,16 @@
         <v>49</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="K66" s="4" t="s">
         <v>43</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="M66" s="4" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="N66" s="4" t="s">
         <v>3</v>
@@ -4671,16 +4724,16 @@
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="C67" s="4">
         <v>35</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>48</v>
@@ -4692,23 +4745,23 @@
         <v>0</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J67" s="4"/>
       <c r="K67" s="4" t="s">
         <v>43</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="M67" s="4" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="N67" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
     </row>
     <row r="68" ht="44.25">
@@ -4716,16 +4769,16 @@
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C68" s="4">
         <v>1</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>41</v>
@@ -4759,36 +4812,36 @@
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C69" s="4">
         <v>2</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J69" s="4"/>
       <c r="K69" s="4"/>
       <c r="L69" s="4" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="M69" s="4" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="N69" s="4" t="s">
         <v>3</v>
@@ -4800,16 +4853,16 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C70" s="4">
         <v>3</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
@@ -4829,16 +4882,16 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C71" s="4">
         <v>4</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>41</v>
@@ -4872,19 +4925,19 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C72" s="4">
         <v>5</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="G72" s="5">
         <v>46308</v>
@@ -4893,16 +4946,16 @@
         <v>65</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="M72" s="4" t="s">
         <v>44</v>
@@ -4917,19 +4970,19 @@
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C73" s="4">
         <v>6</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="G73" s="5">
         <v>46308</v>
@@ -4938,16 +4991,16 @@
         <v>65</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="M73" s="4" t="s">
         <v>44</v>
@@ -4962,16 +5015,16 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C74" s="4">
         <v>7</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="4"/>
@@ -4991,40 +5044,40 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C75" s="4">
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="M75" s="4" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="N75" s="4" t="s">
         <v>3</v>
@@ -5036,40 +5089,40 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C76" s="4">
         <v>9</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="M76" s="4" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="N76" s="4" t="s">
         <v>3</v>
@@ -5081,40 +5134,40 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C77" s="4">
         <v>10</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="G77" s="4">
         <v>0</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="M77" s="4" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="N77" s="4" t="s">
         <v>3</v>
@@ -5126,16 +5179,16 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C78" s="4">
         <v>11</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
@@ -5155,16 +5208,16 @@
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C79" s="4">
         <v>12</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>41</v>
@@ -5198,16 +5251,16 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C80" s="4">
         <v>13</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
@@ -5227,16 +5280,16 @@
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C81" s="4">
         <v>14</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
@@ -5256,19 +5309,19 @@
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C82" s="4">
         <v>15</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="G82" s="4">
         <v>0</v>
@@ -5277,23 +5330,23 @@
         <v>65</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="J82" s="4"/>
       <c r="K82" s="4" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="M82" s="4" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="N82" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
     </row>
     <row r="83" ht="57.75">
@@ -5301,19 +5354,19 @@
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C83" s="4">
         <v>16</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="G83" s="4">
         <v>0</v>
@@ -5322,17 +5375,17 @@
         <v>65</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J83" s="4"/>
       <c r="K83" s="4" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="M83" s="4" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="N83" s="4" t="s">
         <v>3</v>
@@ -5344,19 +5397,19 @@
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C84" s="4">
         <v>17</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="G84" s="4">
         <v>0</v>
@@ -5365,17 +5418,17 @@
         <v>65</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J84" s="4"/>
       <c r="K84" s="4" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="M84" s="4" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="N84" s="4" t="s">
         <v>3</v>
@@ -5387,19 +5440,19 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C85" s="4">
         <v>18</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="G85" s="4">
         <v>0</v>
@@ -5408,17 +5461,17 @@
         <v>65</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J85" s="4"/>
       <c r="K85" s="4" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="M85" s="4" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="N85" s="4" t="s">
         <v>3</v>
@@ -5430,19 +5483,19 @@
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C86" s="4">
         <v>19</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="G86" s="5">
         <v>46308</v>
@@ -5451,23 +5504,23 @@
         <v>65</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J86" s="4"/>
       <c r="K86" s="4" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="M86" s="4" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="N86" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
     </row>
     <row r="87" ht="30.75">
@@ -5475,16 +5528,16 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C87" s="4">
         <v>20</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="4"/>
@@ -5504,16 +5557,16 @@
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C88" s="4">
         <v>21</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
@@ -5533,19 +5586,19 @@
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C89" s="4">
         <v>22</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="G89" s="4">
         <v>0</v>
@@ -5554,19 +5607,19 @@
         <v>0</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="L89" s="4" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="M89" s="4" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="N89" s="4" t="s">
         <v>3</v>
@@ -5578,16 +5631,16 @@
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C90" s="4">
         <v>23</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="4"/>
@@ -5607,44 +5660,44 @@
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C91" s="4">
         <v>24</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J91" s="4"/>
       <c r="K91" s="4" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="M91" s="4" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="N91" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
     </row>
     <row r="92" ht="57.75">
@@ -5652,38 +5705,38 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C92" s="4">
         <v>25</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J92" s="4"/>
       <c r="K92" s="4" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="M92" s="4" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="N92" s="4" t="s">
         <v>3</v>
@@ -5695,44 +5748,44 @@
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C93" s="4">
         <v>26</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J93" s="4"/>
       <c r="K93" s="4" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="M93" s="4" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="N93" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
     </row>
     <row r="94" ht="125.25">
@@ -5740,40 +5793,40 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C94" s="4">
         <v>27</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="M94" s="4" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="N94" s="4" t="s">
         <v>3</v>
@@ -5785,16 +5838,16 @@
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C95" s="4">
         <v>28</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
@@ -5814,16 +5867,16 @@
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C96" s="4">
         <v>29</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F96" s="4"/>
       <c r="G96" s="4"/>
@@ -5843,16 +5896,16 @@
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C97" s="4">
         <v>30</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F97" s="4"/>
       <c r="G97" s="4"/>
@@ -5872,19 +5925,19 @@
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C98" s="4">
         <v>31</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="G98" s="4">
         <v>0</v>
@@ -5893,7 +5946,7 @@
         <v>0</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J98" s="4"/>
       <c r="K98" s="4" t="s">
@@ -5915,16 +5968,16 @@
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C99" s="4">
         <v>32</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
@@ -5944,42 +5997,42 @@
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C100" s="4">
         <v>33</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="J100" s="4"/>
       <c r="K100" s="4"/>
       <c r="L100" s="4" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="M100" s="4" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="N100" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
     </row>
     <row r="101" ht="30.75">
@@ -5987,16 +6040,16 @@
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C101" s="4">
         <v>34</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
@@ -6016,44 +6069,44 @@
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="C102" s="4">
         <v>35</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I102" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J102" s="4"/>
       <c r="K102" s="4" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="M102" s="4" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="N102" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
     </row>
     <row r="103" ht="57.75">
@@ -6061,40 +6114,40 @@
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C103" s="4">
         <v>1</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="I103" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="M103" s="4" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="N103" s="4" t="s">
         <v>3</v>
@@ -6106,42 +6159,42 @@
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C104" s="4">
         <v>2</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J104" s="4"/>
       <c r="K104" s="4"/>
       <c r="L104" s="4" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="M104" s="4" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="N104" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
     </row>
     <row r="105" ht="111.75">
@@ -6149,42 +6202,42 @@
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C105" s="4">
         <v>3</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
       <c r="L105" s="4" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="M105" s="4" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="N105" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
     </row>
     <row r="106" ht="30.75">
@@ -6192,16 +6245,16 @@
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C106" s="4">
         <v>4</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F106" s="4"/>
       <c r="G106" s="4"/>
@@ -6221,16 +6274,16 @@
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C107" s="4">
         <v>5</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F107" s="4"/>
       <c r="G107" s="4"/>
@@ -6250,16 +6303,16 @@
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C108" s="4">
         <v>6</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>41</v>
@@ -6293,16 +6346,16 @@
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C109" s="4">
         <v>7</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>41</v>
@@ -6336,36 +6389,36 @@
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C110" s="4">
         <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="I110" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
       <c r="L110" s="4" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="M110" s="4" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="N110" s="4" t="s">
         <v>3</v>
@@ -6377,36 +6430,36 @@
         <v>110</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C111" s="4">
         <v>9</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
       <c r="L111" s="4" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="M111" s="4" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="N111" s="4" t="s">
         <v>3</v>
@@ -6418,36 +6471,36 @@
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C112" s="4">
         <v>10</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
       <c r="L112" s="4" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="M112" s="4" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="N112" s="4" t="s">
         <v>3</v>
@@ -6459,36 +6512,36 @@
         <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C113" s="4">
         <v>11</v>
       </c>
       <c r="D113" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="E113" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="F113" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="E113" s="4" t="s">
+      <c r="G113" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="F113" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="G113" s="4" t="s">
-        <v>448</v>
-      </c>
       <c r="H113" s="4" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
       <c r="L113" s="4" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="M113" s="4" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="N113" s="4" t="s">
         <v>3</v>
@@ -6500,25 +6553,25 @@
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C114" s="4">
         <v>12</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="I114" s="4" t="s">
         <v>42</v>
@@ -6526,10 +6579,10 @@
       <c r="J114" s="4"/>
       <c r="K114" s="4"/>
       <c r="L114" s="4" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="M114" s="4" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="N114" s="4" t="s">
         <v>3</v>
@@ -6541,25 +6594,25 @@
         <v>114</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C115" s="4">
         <v>13</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="I115" s="4" t="s">
         <v>42</v>
@@ -6567,10 +6620,10 @@
       <c r="J115" s="4"/>
       <c r="K115" s="4"/>
       <c r="L115" s="4" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="M115" s="4" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="N115" s="4" t="s">
         <v>3</v>
@@ -6582,38 +6635,38 @@
         <v>115</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C116" s="4">
         <v>14</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="I116" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J116" s="4"/>
       <c r="K116" s="4" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="M116" s="4" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="N116" s="4" t="s">
         <v>3</v>
@@ -6625,25 +6678,25 @@
         <v>116</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C117" s="4">
         <v>15</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I117" s="4" t="s">
         <v>49</v>
@@ -6651,10 +6704,10 @@
       <c r="J117" s="4"/>
       <c r="K117" s="4"/>
       <c r="L117" s="4" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="M117" s="4" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="N117" s="4" t="s">
         <v>3</v>
@@ -6666,25 +6719,25 @@
         <v>117</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C118" s="4">
         <v>16</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I118" s="4" t="s">
         <v>49</v>
@@ -6692,10 +6745,10 @@
       <c r="J118" s="4"/>
       <c r="K118" s="4"/>
       <c r="L118" s="4" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="M118" s="4" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="N118" s="4" t="s">
         <v>3</v>
@@ -6707,25 +6760,25 @@
         <v>118</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C119" s="4">
         <v>17</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="I119" s="4" t="s">
         <v>42</v>
@@ -6733,16 +6786,16 @@
       <c r="J119" s="4"/>
       <c r="K119" s="4"/>
       <c r="L119" s="4" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="M119" s="4" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="N119" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
     </row>
     <row r="120" ht="71.25">
@@ -6750,37 +6803,37 @@
         <v>119</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C120" s="4">
         <v>18</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I120" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="L120" s="4" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="M120" s="4" t="s">
         <v>44</v>
@@ -6795,37 +6848,37 @@
         <v>120</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C121" s="4">
         <v>19</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I121" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="L121" s="4" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="M121" s="4" t="s">
         <v>44</v>
@@ -6840,16 +6893,16 @@
         <v>121</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C122" s="4">
         <v>20</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F122" s="4"/>
       <c r="G122" s="4"/>
@@ -6869,16 +6922,16 @@
         <v>122</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C123" s="4">
         <v>21</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F123" s="4"/>
       <c r="G123" s="4"/>
@@ -6898,36 +6951,36 @@
         <v>123</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C124" s="4">
         <v>22</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="F124" s="4"/>
       <c r="G124" s="4"/>
       <c r="H124" s="4"/>
       <c r="I124" s="4" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="J124" s="4"/>
       <c r="K124" s="4"/>
       <c r="L124" s="4" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="M124" s="4" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="N124" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O124" s="4" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
     </row>
     <row r="125" ht="57.75">
@@ -6935,46 +6988,46 @@
         <v>124</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C125" s="4">
         <v>23</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="I125" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="L125" s="4" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="M125" s="4" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="N125" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O125" s="4" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
     </row>
     <row r="126" ht="57.75">
@@ -6982,25 +7035,25 @@
         <v>125</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C126" s="4">
         <v>24</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="I126" s="4" t="s">
         <v>42</v>
@@ -7019,19 +7072,19 @@
         <v>126</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C127" s="4">
         <v>25</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="G127" s="4">
         <v>0</v>
@@ -7045,10 +7098,10 @@
       <c r="J127" s="4"/>
       <c r="K127" s="4"/>
       <c r="L127" s="4" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="M127" s="4" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="N127" s="4" t="s">
         <v>3</v>
@@ -7060,25 +7113,25 @@
         <v>127</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C128" s="4">
         <v>26</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="I128" s="4" t="s">
         <v>42</v>
@@ -7086,16 +7139,16 @@
       <c r="J128" s="4"/>
       <c r="K128" s="4"/>
       <c r="L128" s="4" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="M128" s="4" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="N128" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
     </row>
     <row r="129" ht="30.75">
@@ -7103,16 +7156,16 @@
         <v>128</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C129" s="4">
         <v>27</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F129" s="4"/>
       <c r="G129" s="4"/>
@@ -7132,19 +7185,19 @@
         <v>129</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C130" s="4">
         <v>28</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="G130" s="4">
         <v>0</v>
@@ -7156,16 +7209,16 @@
         <v>49</v>
       </c>
       <c r="J130" s="4" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="L130" s="4" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="M130" s="4" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="N130" s="4" t="s">
         <v>3</v>
@@ -7177,19 +7230,19 @@
         <v>130</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C131" s="4">
         <v>29</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="G131" s="4">
         <v>0</v>
@@ -7201,16 +7254,16 @@
         <v>49</v>
       </c>
       <c r="J131" s="4" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="K131" s="4" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="L131" s="4" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="M131" s="4" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="N131" s="4" t="s">
         <v>3</v>
@@ -7222,16 +7275,16 @@
         <v>131</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C132" s="4">
         <v>30</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F132" s="4"/>
       <c r="G132" s="4"/>
@@ -7251,16 +7304,16 @@
         <v>132</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C133" s="4">
         <v>31</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F133" s="4"/>
       <c r="G133" s="4"/>
@@ -7280,40 +7333,40 @@
         <v>133</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C134" s="4">
         <v>32</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J134" s="4" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="L134" s="4" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="M134" s="4" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="N134" s="4" t="s">
         <v>3</v>
@@ -7325,25 +7378,25 @@
         <v>134</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C135" s="4">
         <v>33</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
       <c r="I135" s="4" t="s">
         <v>42</v>
@@ -7351,16 +7404,16 @@
       <c r="J135" s="4"/>
       <c r="K135" s="4"/>
       <c r="L135" s="4" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="M135" s="4" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="N135" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
     </row>
     <row r="136" ht="84.75">
@@ -7368,16 +7421,16 @@
         <v>135</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
       <c r="C136" s="4">
         <v>34</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="F136" s="4" t="s">
         <v>41</v>
@@ -7385,7 +7438,7 @@
       <c r="G136" s="4"/>
       <c r="H136" s="4"/>
       <c r="I136" s="4" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="J136" s="4"/>
       <c r="K136" s="4"/>
@@ -7399,7 +7452,7 @@
         <v>3</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>

--- a/documents/STI2004-pinout-check.xlsx
+++ b/documents/STI2004-pinout-check.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="561">
   <si>
     <t>Status</t>
   </si>
@@ -367,7 +367,7 @@
     <t>+12V_IGN</t>
   </si>
   <si>
-    <t>M14.IN_VIGN_V2</t>
+    <t>M14.IN_VIGN_V2; M8.IN_VIGN_V2</t>
   </si>
   <si>
     <t>D16</t>
@@ -733,22 +733,25 @@
     <t>APS_PS_5V</t>
   </si>
   <si>
+    <t>JP11.1_1; M8.5VP_V4</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>Sensor power supply</t>
+  </si>
+  <si>
+    <t>5v OUT SENSOR_PS_5V</t>
+  </si>
+  <si>
+    <t>SENSOR_PS_5V</t>
+  </si>
+  <si>
     <t>+5VAS</t>
   </si>
   <si>
-    <t>M14.5VP_V4</t>
-  </si>
-  <si>
-    <t>C16</t>
-  </si>
-  <si>
-    <t>Sensor power supply</t>
-  </si>
-  <si>
-    <t>5v OUT SENSOR_PS_5V</t>
-  </si>
-  <si>
-    <t>SENSOR_PS_5V</t>
+    <t>F7 -&gt; AUX_5V -&gt; J3.Pin_3_3; JP11.2_2; M14.5VP_V4</t>
   </si>
   <si>
     <t>Feeds throttle TPS; MAP; TGV sensors</t>
@@ -949,7 +952,7 @@
     <t>GND_SENSOR</t>
   </si>
   <si>
-    <t>JP8.1_1; JP9.1_1</t>
+    <t>J3.Pin_4_4; JP8.1_1; JP9.1_1</t>
   </si>
   <si>
     <t>C32</t>
@@ -1177,7 +1180,7 @@
     <t>+12V_BACK_UP</t>
   </si>
   <si>
-    <t>M14.V12_PERM_V1</t>
+    <t>M14.V12_PERM_V1; M8.V12_PERM_V1</t>
   </si>
   <si>
     <t>Ignition OFF: 10-13</t>
@@ -2720,7 +2723,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="16" ht="30.75">
+    <row r="16" ht="71.25">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -3924,17 +3927,17 @@
         <v>238</v>
       </c>
       <c r="L47" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="M47" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="M47" s="4" t="s">
-        <v>240</v>
-      </c>
       <c r="N47" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O47" s="4"/>
     </row>
-    <row r="48" ht="71.25">
+    <row r="48" ht="98.25">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -3945,10 +3948,10 @@
         <v>16</v>
       </c>
       <c r="D48" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E48" s="4" t="s">
         <v>241</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>242</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>237</v>
@@ -3963,22 +3966,22 @@
         <v>75</v>
       </c>
       <c r="J48" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="K48" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="K48" s="4" t="s">
+      <c r="L48" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="L48" s="4" t="s">
-        <v>239</v>
-      </c>
       <c r="M48" s="4" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="N48" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="49" ht="57.75">
@@ -3992,34 +3995,34 @@
         <v>17</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I49" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N49" s="4" t="s">
         <v>3</v>
@@ -4037,34 +4040,34 @@
         <v>18</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I50" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="N50" s="4" t="s">
         <v>3</v>
@@ -4082,7 +4085,7 @@
         <v>19</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>130</v>
@@ -4111,32 +4114,32 @@
         <v>20</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I52" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J52" s="4"/>
       <c r="K52" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N52" s="4" t="s">
         <v>3</v>
@@ -4154,19 +4157,19 @@
         <v>21</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="I53" s="4" t="s">
         <v>42</v>
@@ -4191,19 +4194,19 @@
         <v>22</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="I54" s="4" t="s">
         <v>42</v>
@@ -4211,10 +4214,10 @@
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
       <c r="L54" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N54" s="4" t="s">
         <v>3</v>
@@ -4232,32 +4235,32 @@
         <v>23</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I55" s="4" t="s">
         <v>152</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M55" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N55" s="4" t="s">
         <v>3</v>
@@ -4275,7 +4278,7 @@
         <v>24</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>130</v>
@@ -4304,13 +4307,13 @@
         <v>25</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G57" s="4">
         <v>2.8</v>
@@ -4323,13 +4326,13 @@
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M57" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N57" s="4" t="s">
         <v>3</v>
@@ -4347,34 +4350,34 @@
         <v>26</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>75</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="M58" s="4" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N58" s="4" t="s">
         <v>3</v>
@@ -4392,34 +4395,34 @@
         <v>27</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="I59" s="4" t="s">
         <v>75</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N59" s="4" t="s">
         <v>3</v>
@@ -4437,34 +4440,34 @@
         <v>28</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I60" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N60" s="4" t="s">
         <v>3</v>
@@ -4482,34 +4485,34 @@
         <v>29</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N61" s="4" t="s">
         <v>3</v>
@@ -4527,7 +4530,7 @@
         <v>30</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>130</v>
@@ -4556,10 +4559,10 @@
         <v>31</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>48</v>
@@ -4578,10 +4581,10 @@
         <v>43</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N63" s="4" t="s">
         <v>3</v>
@@ -4599,10 +4602,10 @@
         <v>32</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>172</v>
@@ -4642,10 +4645,10 @@
         <v>33</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>172</v>
@@ -4685,10 +4688,10 @@
         <v>34</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>48</v>
@@ -4703,16 +4706,16 @@
         <v>49</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K66" s="4" t="s">
         <v>43</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M66" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N66" s="4" t="s">
         <v>3</v>
@@ -4730,10 +4733,10 @@
         <v>35</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>48</v>
@@ -4752,16 +4755,16 @@
         <v>43</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="M67" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="N67" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="68" ht="44.25">
@@ -4769,16 +4772,16 @@
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C68" s="4">
         <v>1</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>41</v>
@@ -4812,25 +4815,25 @@
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C69" s="4">
         <v>2</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I69" s="4" t="s">
         <v>152</v>
@@ -4838,10 +4841,10 @@
       <c r="J69" s="4"/>
       <c r="K69" s="4"/>
       <c r="L69" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M69" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N69" s="4" t="s">
         <v>3</v>
@@ -4853,13 +4856,13 @@
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C70" s="4">
         <v>3</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>130</v>
@@ -4882,16 +4885,16 @@
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C71" s="4">
         <v>4</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>41</v>
@@ -4925,19 +4928,19 @@
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C72" s="4">
         <v>5</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G72" s="5">
         <v>46308</v>
@@ -4949,13 +4952,13 @@
         <v>75</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M72" s="4" t="s">
         <v>44</v>
@@ -4970,19 +4973,19 @@
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C73" s="4">
         <v>6</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="G73" s="5">
         <v>46308</v>
@@ -4994,13 +4997,13 @@
         <v>75</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M73" s="4" t="s">
         <v>44</v>
@@ -5015,13 +5018,13 @@
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C74" s="4">
         <v>7</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>130</v>
@@ -5044,40 +5047,40 @@
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C75" s="4">
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G75" s="4" t="s">
         <v>151</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I75" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="M75" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="N75" s="4" t="s">
         <v>3</v>
@@ -5089,40 +5092,40 @@
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C76" s="4">
         <v>9</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="G76" s="4" t="s">
         <v>151</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="I76" s="4" t="s">
         <v>49</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M76" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N76" s="4" t="s">
         <v>3</v>
@@ -5134,40 +5137,40 @@
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C77" s="4">
         <v>10</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G77" s="4">
         <v>0</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="I77" s="4" t="s">
         <v>152</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M77" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N77" s="4" t="s">
         <v>3</v>
@@ -5179,13 +5182,13 @@
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C78" s="4">
         <v>11</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>130</v>
@@ -5208,16 +5211,16 @@
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C79" s="4">
         <v>12</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>41</v>
@@ -5251,13 +5254,13 @@
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C80" s="4">
         <v>13</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>130</v>
@@ -5280,13 +5283,13 @@
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C81" s="4">
         <v>14</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>130</v>
@@ -5309,19 +5312,19 @@
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C82" s="4">
         <v>15</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G82" s="4">
         <v>0</v>
@@ -5330,23 +5333,23 @@
         <v>65</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J82" s="4"/>
       <c r="K82" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M82" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N82" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="83" ht="57.75">
@@ -5354,19 +5357,19 @@
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C83" s="4">
         <v>16</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G83" s="4">
         <v>0</v>
@@ -5379,13 +5382,13 @@
       </c>
       <c r="J83" s="4"/>
       <c r="K83" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="M83" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="N83" s="4" t="s">
         <v>3</v>
@@ -5397,19 +5400,19 @@
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C84" s="4">
         <v>17</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G84" s="4">
         <v>0</v>
@@ -5422,13 +5425,13 @@
       </c>
       <c r="J84" s="4"/>
       <c r="K84" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M84" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N84" s="4" t="s">
         <v>3</v>
@@ -5440,19 +5443,19 @@
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C85" s="4">
         <v>18</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G85" s="4">
         <v>0</v>
@@ -5465,37 +5468,37 @@
       </c>
       <c r="J85" s="4"/>
       <c r="K85" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M85" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N85" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O85" s="4"/>
     </row>
-    <row r="86" ht="44.25">
+    <row r="86" ht="71.25">
       <c r="A86" s="4">
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C86" s="4">
         <v>19</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G86" s="5">
         <v>46308</v>
@@ -5508,19 +5511,19 @@
       </c>
       <c r="J86" s="4"/>
       <c r="K86" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M86" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N86" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="87" ht="30.75">
@@ -5528,13 +5531,13 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C87" s="4">
         <v>20</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>130</v>
@@ -5557,13 +5560,13 @@
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C88" s="4">
         <v>21</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>130</v>
@@ -5586,19 +5589,19 @@
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C89" s="4">
         <v>22</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G89" s="4">
         <v>0</v>
@@ -5610,7 +5613,7 @@
         <v>152</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K89" s="4" t="s">
         <v>140</v>
@@ -5619,7 +5622,7 @@
         <v>140</v>
       </c>
       <c r="M89" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N89" s="4" t="s">
         <v>3</v>
@@ -5631,13 +5634,13 @@
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C90" s="4">
         <v>23</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>130</v>
@@ -5660,44 +5663,44 @@
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C91" s="4">
         <v>24</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>124</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I91" s="4" t="s">
         <v>75</v>
       </c>
       <c r="J91" s="4"/>
       <c r="K91" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M91" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N91" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="92" ht="57.75">
@@ -5705,38 +5708,38 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C92" s="4">
         <v>25</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>124</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I92" s="4" t="s">
         <v>75</v>
       </c>
       <c r="J92" s="4"/>
       <c r="K92" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M92" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N92" s="4" t="s">
         <v>3</v>
@@ -5748,44 +5751,44 @@
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C93" s="4">
         <v>26</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I93" s="4" t="s">
         <v>75</v>
       </c>
       <c r="J93" s="4"/>
       <c r="K93" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="M93" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="N93" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="94" ht="125.25">
@@ -5793,40 +5796,40 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C94" s="4">
         <v>27</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="I94" s="4" t="s">
         <v>152</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M94" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N94" s="4" t="s">
         <v>3</v>
@@ -5838,13 +5841,13 @@
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C95" s="4">
         <v>28</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E95" s="4" t="s">
         <v>130</v>
@@ -5867,13 +5870,13 @@
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C96" s="4">
         <v>29</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E96" s="4" t="s">
         <v>130</v>
@@ -5896,13 +5899,13 @@
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C97" s="4">
         <v>30</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>130</v>
@@ -5925,16 +5928,16 @@
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C98" s="4">
         <v>31</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F98" s="4" t="s">
         <v>172</v>
@@ -5968,13 +5971,13 @@
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C99" s="4">
         <v>32</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E99" s="4" t="s">
         <v>130</v>
@@ -5997,25 +6000,25 @@
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C100" s="4">
         <v>33</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F100" s="4" t="s">
         <v>124</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="I100" s="4" t="s">
         <v>125</v>
@@ -6023,16 +6026,16 @@
       <c r="J100" s="4"/>
       <c r="K100" s="4"/>
       <c r="L100" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M100" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N100" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="101" ht="30.75">
@@ -6040,13 +6043,13 @@
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C101" s="4">
         <v>34</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E101" s="4" t="s">
         <v>130</v>
@@ -6069,16 +6072,16 @@
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C102" s="4">
         <v>35</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F102" s="4" t="s">
         <v>124</v>
@@ -6094,19 +6097,19 @@
       </c>
       <c r="J102" s="4"/>
       <c r="K102" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M102" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N102" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="103" ht="57.75">
@@ -6114,16 +6117,16 @@
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C103" s="4">
         <v>1</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F103" s="4" t="s">
         <v>87</v>
@@ -6138,16 +6141,16 @@
         <v>49</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M103" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N103" s="4" t="s">
         <v>3</v>
@@ -6159,25 +6162,25 @@
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C104" s="4">
         <v>2</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I104" s="4" t="s">
         <v>152</v>
@@ -6185,16 +6188,16 @@
       <c r="J104" s="4"/>
       <c r="K104" s="4"/>
       <c r="L104" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M104" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N104" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="105" ht="111.75">
@@ -6202,25 +6205,25 @@
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C105" s="4">
         <v>3</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I105" s="4" t="s">
         <v>152</v>
@@ -6228,16 +6231,16 @@
       <c r="J105" s="4"/>
       <c r="K105" s="4"/>
       <c r="L105" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M105" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N105" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="106" ht="30.75">
@@ -6245,13 +6248,13 @@
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C106" s="4">
         <v>4</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>130</v>
@@ -6274,13 +6277,13 @@
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C107" s="4">
         <v>5</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>130</v>
@@ -6303,16 +6306,16 @@
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C108" s="4">
         <v>6</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F108" s="4" t="s">
         <v>41</v>
@@ -6346,16 +6349,16 @@
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C109" s="4">
         <v>7</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="F109" s="4" t="s">
         <v>41</v>
@@ -6389,25 +6392,25 @@
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C110" s="4">
         <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I110" s="4" t="s">
         <v>75</v>
@@ -6415,10 +6418,10 @@
       <c r="J110" s="4"/>
       <c r="K110" s="4"/>
       <c r="L110" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M110" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N110" s="4" t="s">
         <v>3</v>
@@ -6430,25 +6433,25 @@
         <v>110</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C111" s="4">
         <v>9</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I111" s="4" t="s">
         <v>75</v>
@@ -6456,10 +6459,10 @@
       <c r="J111" s="4"/>
       <c r="K111" s="4"/>
       <c r="L111" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M111" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N111" s="4" t="s">
         <v>3</v>
@@ -6471,25 +6474,25 @@
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C112" s="4">
         <v>10</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I112" s="4" t="s">
         <v>75</v>
@@ -6497,10 +6500,10 @@
       <c r="J112" s="4"/>
       <c r="K112" s="4"/>
       <c r="L112" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M112" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N112" s="4" t="s">
         <v>3</v>
@@ -6512,25 +6515,25 @@
         <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C113" s="4">
         <v>11</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I113" s="4" t="s">
         <v>75</v>
@@ -6538,10 +6541,10 @@
       <c r="J113" s="4"/>
       <c r="K113" s="4"/>
       <c r="L113" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M113" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N113" s="4" t="s">
         <v>3</v>
@@ -6553,25 +6556,25 @@
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C114" s="4">
         <v>12</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I114" s="4" t="s">
         <v>42</v>
@@ -6579,10 +6582,10 @@
       <c r="J114" s="4"/>
       <c r="K114" s="4"/>
       <c r="L114" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M114" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N114" s="4" t="s">
         <v>3</v>
@@ -6594,25 +6597,25 @@
         <v>114</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C115" s="4">
         <v>13</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I115" s="4" t="s">
         <v>42</v>
@@ -6620,10 +6623,10 @@
       <c r="J115" s="4"/>
       <c r="K115" s="4"/>
       <c r="L115" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="M115" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="N115" s="4" t="s">
         <v>3</v>
@@ -6635,38 +6638,38 @@
         <v>115</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C116" s="4">
         <v>14</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I116" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J116" s="4"/>
       <c r="K116" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M116" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N116" s="4" t="s">
         <v>3</v>
@@ -6678,19 +6681,19 @@
         <v>116</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C117" s="4">
         <v>15</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G117" s="4" t="s">
         <v>95</v>
@@ -6704,10 +6707,10 @@
       <c r="J117" s="4"/>
       <c r="K117" s="4"/>
       <c r="L117" s="4" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M117" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N117" s="4" t="s">
         <v>3</v>
@@ -6719,19 +6722,19 @@
         <v>117</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C118" s="4">
         <v>16</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G118" s="4" t="s">
         <v>95</v>
@@ -6745,10 +6748,10 @@
       <c r="J118" s="4"/>
       <c r="K118" s="4"/>
       <c r="L118" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M118" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N118" s="4" t="s">
         <v>3</v>
@@ -6760,25 +6763,25 @@
         <v>118</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C119" s="4">
         <v>17</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I119" s="4" t="s">
         <v>42</v>
@@ -6786,16 +6789,16 @@
       <c r="J119" s="4"/>
       <c r="K119" s="4"/>
       <c r="L119" s="4" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M119" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N119" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="120" ht="71.25">
@@ -6803,19 +6806,19 @@
         <v>119</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C120" s="4">
         <v>18</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G120" s="4" t="s">
         <v>81</v>
@@ -6827,13 +6830,13 @@
         <v>49</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L120" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M120" s="4" t="s">
         <v>44</v>
@@ -6848,19 +6851,19 @@
         <v>120</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C121" s="4">
         <v>19</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="G121" s="4" t="s">
         <v>81</v>
@@ -6872,13 +6875,13 @@
         <v>49</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="L121" s="4" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M121" s="4" t="s">
         <v>44</v>
@@ -6893,13 +6896,13 @@
         <v>121</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C122" s="4">
         <v>20</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="E122" s="4" t="s">
         <v>130</v>
@@ -6922,13 +6925,13 @@
         <v>122</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C123" s="4">
         <v>21</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="E123" s="4" t="s">
         <v>130</v>
@@ -6951,36 +6954,36 @@
         <v>123</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C124" s="4">
         <v>22</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F124" s="4"/>
       <c r="G124" s="4"/>
       <c r="H124" s="4"/>
       <c r="I124" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="J124" s="4"/>
       <c r="K124" s="4"/>
       <c r="L124" s="4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M124" s="4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N124" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O124" s="4" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="125" ht="57.75">
@@ -6988,46 +6991,46 @@
         <v>124</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C125" s="4">
         <v>23</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="I125" s="4" t="s">
         <v>42</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L125" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M125" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N125" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O125" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="126" ht="57.75">
@@ -7035,25 +7038,25 @@
         <v>125</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C126" s="4">
         <v>24</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="I126" s="4" t="s">
         <v>42</v>
@@ -7072,16 +7075,16 @@
         <v>126</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C127" s="4">
         <v>25</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F127" s="4" t="s">
         <v>172</v>
@@ -7098,10 +7101,10 @@
       <c r="J127" s="4"/>
       <c r="K127" s="4"/>
       <c r="L127" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M127" s="4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N127" s="4" t="s">
         <v>3</v>
@@ -7113,25 +7116,25 @@
         <v>127</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C128" s="4">
         <v>26</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="I128" s="4" t="s">
         <v>42</v>
@@ -7139,16 +7142,16 @@
       <c r="J128" s="4"/>
       <c r="K128" s="4"/>
       <c r="L128" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M128" s="4" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N128" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="129" ht="30.75">
@@ -7156,13 +7159,13 @@
         <v>128</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C129" s="4">
         <v>27</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>130</v>
@@ -7185,19 +7188,19 @@
         <v>129</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C130" s="4">
         <v>28</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G130" s="4">
         <v>0</v>
@@ -7209,16 +7212,16 @@
         <v>49</v>
       </c>
       <c r="J130" s="4" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="L130" s="4" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M130" s="4" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N130" s="4" t="s">
         <v>3</v>
@@ -7230,19 +7233,19 @@
         <v>130</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C131" s="4">
         <v>29</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G131" s="4">
         <v>0</v>
@@ -7254,16 +7257,16 @@
         <v>49</v>
       </c>
       <c r="J131" s="4" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="K131" s="4" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="L131" s="4" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="M131" s="4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N131" s="4" t="s">
         <v>3</v>
@@ -7275,13 +7278,13 @@
         <v>131</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C132" s="4">
         <v>30</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E132" s="4" t="s">
         <v>130</v>
@@ -7304,13 +7307,13 @@
         <v>132</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C133" s="4">
         <v>31</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>130</v>
@@ -7333,40 +7336,40 @@
         <v>133</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C134" s="4">
         <v>32</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="I134" s="4" t="s">
         <v>75</v>
       </c>
       <c r="J134" s="4" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="L134" s="4" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M134" s="4" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N134" s="4" t="s">
         <v>3</v>
@@ -7378,25 +7381,25 @@
         <v>134</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C135" s="4">
         <v>33</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="I135" s="4" t="s">
         <v>42</v>
@@ -7404,16 +7407,16 @@
       <c r="J135" s="4"/>
       <c r="K135" s="4"/>
       <c r="L135" s="4" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="M135" s="4" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="N135" s="4" t="s">
         <v>3</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="136" ht="84.75">
@@ -7421,13 +7424,13 @@
         <v>135</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C136" s="4">
         <v>34</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E136" s="4" t="s">
         <v>164</v>
@@ -7438,7 +7441,7 @@
       <c r="G136" s="4"/>
       <c r="H136" s="4"/>
       <c r="I136" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J136" s="4"/>
       <c r="K136" s="4"/>
@@ -7452,7 +7455,7 @@
         <v>3</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
   </sheetData>

--- a/documents/STI2004-pinout-check.xlsx
+++ b/documents/STI2004-pinout-check.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1222" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1154" uniqueCount="553">
   <si>
     <t>Status</t>
   </si>
@@ -82,7 +82,7 @@
     <t>Schematics</t>
   </si>
   <si>
-    <t>master, rev-b-wiring</t>
+    <t>current</t>
   </si>
   <si>
     <t>Status judged on the last one</t>
@@ -118,13 +118,10 @@
     <t>Your sheet</t>
   </si>
   <si>
-    <t>Net: master</t>
-  </si>
-  <si>
-    <t>Net: rev-b-wiring</t>
-  </si>
-  <si>
-    <t>Reaches (rev-b-wiring)</t>
+    <t>Net: current</t>
+  </si>
+  <si>
+    <t>Reaches (current)</t>
   </si>
   <si>
     <t>Notes</t>
@@ -214,9 +211,6 @@
     <t>13-14</t>
   </si>
   <si>
-    <t>Net-(F5-Pad1)</t>
-  </si>
-  <si>
     <t>+12V_ETB</t>
   </si>
   <si>
@@ -229,9 +223,6 @@
     <t>GND (injectors)</t>
   </si>
   <si>
-    <t>GND_INJECTORS</t>
-  </si>
-  <si>
     <t>D8</t>
   </si>
   <si>
@@ -286,9 +277,6 @@
     <t>IN_PS_PRESSURE_SWIITCH | DIGITAL 12-0 OFF ON</t>
   </si>
   <si>
-    <t>IN_PS_PRESSURE_SWIITCH</t>
-  </si>
-  <si>
     <t>IN_PS_PRESSURE_SWITCH</t>
   </si>
   <si>
@@ -307,7 +295,7 @@
     <t>IN_DEFOG</t>
   </si>
   <si>
-    <t>M11.IN_D1_V2; R49.1</t>
+    <t>M11.IN_D1_V2; R51.1</t>
   </si>
   <si>
     <t>D12</t>
@@ -319,7 +307,7 @@
     <t>IN_SMALL_LIGHT</t>
   </si>
   <si>
-    <t>M11.IN_D2_V3; R50.1</t>
+    <t>M11.IN_D2_V3; R52.1</t>
   </si>
   <si>
     <t>D13</t>
@@ -331,7 +319,7 @@
     <t>IN_BLOWER</t>
   </si>
   <si>
-    <t>M11.IN_D3_V4; R51.1</t>
+    <t>M11.IN_D3_V4; R53.1</t>
   </si>
   <si>
     <t>Also shown to auto A/C module (WI-106)</t>
@@ -436,769 +424,757 @@
     <t>D22</t>
   </si>
   <si>
+    <t>D23</t>
+  </si>
+  <si>
+    <t>D24</t>
+  </si>
+  <si>
+    <t>Blow-by leak diagnosis signal</t>
+  </si>
+  <si>
+    <t>digital in</t>
+  </si>
+  <si>
+    <t>IN_BLOWBY</t>
+  </si>
+  <si>
+    <t>M12.IN_D4_V5</t>
+  </si>
+  <si>
+    <t>Disconnected (fault): 5</t>
+  </si>
+  <si>
+    <t>D25</t>
+  </si>
+  <si>
+    <t>Rear oxygen sensor signal</t>
+  </si>
+  <si>
+    <t>analog in (narrowband O2)</t>
+  </si>
+  <si>
+    <t>0-0.9</t>
+  </si>
+  <si>
+    <t>EN(STi)-18</t>
+  </si>
+  <si>
+    <t>IN_O2S</t>
+  </si>
+  <si>
+    <t>M1.IN_O2S_S16</t>
+  </si>
+  <si>
+    <t>D26</t>
+  </si>
+  <si>
+    <t>D27</t>
+  </si>
+  <si>
+    <t>D28</t>
+  </si>
+  <si>
+    <t>Fuel pump control unit signal 2</t>
+  </si>
+  <si>
+    <t>12 V to FPCU</t>
+  </si>
+  <si>
+    <t>FP_STATUS</t>
+  </si>
+  <si>
+    <t>JP7.1_1; P12.Pin_1_1</t>
+  </si>
+  <si>
+    <t>D29</t>
+  </si>
+  <si>
+    <t>(not in I/O table)</t>
+  </si>
+  <si>
+    <t>WI-112</t>
+  </si>
+  <si>
+    <t>DLC6_D29</t>
+  </si>
+  <si>
+    <t>JP4.1_1; P13.Pin_1_1</t>
+  </si>
+  <si>
+    <t>Red/white wire to data link connector pin 6 (WI-112); function not in the I/O table. Leave unconnected.</t>
+  </si>
+  <si>
+    <t>D30</t>
+  </si>
+  <si>
+    <t>D31</t>
+  </si>
+  <si>
+    <t>Rear oxygen sensor shield</t>
+  </si>
+  <si>
+    <t>shield</t>
+  </si>
+  <si>
+    <t>B136</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>Fuel injector #4</t>
+  </si>
+  <si>
+    <t>injector low-side</t>
+  </si>
+  <si>
+    <t>OUT_INJ4</t>
+  </si>
+  <si>
+    <t>Q4.D_2</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>Fuel injector #3</t>
+  </si>
+  <si>
+    <t>OUT_INJ3</t>
+  </si>
+  <si>
+    <t>Q3.D_2</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>Fuel injector #2</t>
+  </si>
+  <si>
+    <t>OUT_INJ2</t>
+  </si>
+  <si>
+    <t>Q2.D_2</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>Fuel injector #1</t>
+  </si>
+  <si>
+    <t>OUT_INJ1</t>
+  </si>
+  <si>
+    <t>Q1.D_2</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>Cruise main switch</t>
+  </si>
+  <si>
+    <t>EN(STi)-22</t>
+  </si>
+  <si>
+    <t>IN_CRUISE_MAIN</t>
+  </si>
+  <si>
+    <t>M1.IN_D1_S4; R35.1</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
+    <t>Brake switch 2</t>
+  </si>
+  <si>
+    <t>pressed 10-13 / released 0</t>
+  </si>
+  <si>
+    <t>pressed 13-14 / released 0</t>
+  </si>
+  <si>
+    <t>IN_BRAKE_SW2</t>
+  </si>
+  <si>
+    <t>M1.IN_SENS4_S6; R32.1</t>
+  </si>
+  <si>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>Brake switch 1</t>
+  </si>
+  <si>
+    <t>pressed 0 / released 10-13</t>
+  </si>
+  <si>
+    <t>pressed 0 / released 13-14</t>
+  </si>
+  <si>
+    <t>IN_BRAKE_SW1</t>
+  </si>
+  <si>
+    <t>M1.IN_O2S2_S15; R34.1</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>RESUME/ACCEL switch</t>
+  </si>
+  <si>
+    <t>IN_CRUISE_RESUME</t>
+  </si>
+  <si>
+    <t>M1.IN_D3_S2; R36.1</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>SET/COAST switch</t>
+  </si>
+  <si>
+    <t>IN_CRUISE_SET</t>
+  </si>
+  <si>
+    <t>M1.IN_D4_S1; R37.1</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>Fuel temperature sensor signal</t>
+  </si>
+  <si>
+    <t>analog in (thermistor)</t>
+  </si>
+  <si>
+    <t>2.5-3.8</t>
+  </si>
+  <si>
+    <t>At 25 C</t>
+  </si>
+  <si>
+    <t>C13</t>
+  </si>
+  <si>
+    <t>Intake air temperature sensor signal</t>
+  </si>
+  <si>
+    <t>0.3-4.6</t>
+  </si>
+  <si>
+    <t>IN_IAT</t>
+  </si>
+  <si>
+    <t>M1.IN_IAT_S26</t>
+  </si>
+  <si>
+    <t>In the MAF housing</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>Engine coolant temperature sensor signal</t>
+  </si>
+  <si>
+    <t>1.0-1.4</t>
+  </si>
+  <si>
+    <t>IN_ECT</t>
+  </si>
+  <si>
+    <t>M1.IN_CLT_S28</t>
+  </si>
+  <si>
+    <t>After warm-up</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>Accelerator position sensor power supply</t>
+  </si>
+  <si>
+    <t>5 V sensor supply out</t>
+  </si>
+  <si>
+    <t>APS_PS_5V</t>
+  </si>
+  <si>
+    <t>JP12.1_1; M8.5VP_V4</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>Sensor power supply</t>
+  </si>
+  <si>
+    <t>5v OUT SENSOR_PS_5V</t>
+  </si>
+  <si>
+    <t>+5VAS</t>
+  </si>
+  <si>
+    <t>F7 -&gt; AUX_5V -&gt; J3.Pin_3_3; JP12.2_2; M14.5VP_V4</t>
+  </si>
+  <si>
+    <t>Feeds throttle TPS; MAP; TGV sensors</t>
+  </si>
+  <si>
+    <t>C17</t>
+  </si>
+  <si>
+    <t>Accelerator position sensor main</t>
+  </si>
+  <si>
+    <t>analog in</t>
+  </si>
+  <si>
+    <t>closed 1 / open 3.5</t>
+  </si>
+  <si>
+    <t>IN_APS_MAIN</t>
+  </si>
+  <si>
+    <t>IN_PPS_MAIN</t>
+  </si>
+  <si>
+    <t>M1.IN_PPS_S31</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>Electric throttle main (TPS1)</t>
+  </si>
+  <si>
+    <t>0.64-0.72 / open 3.96</t>
+  </si>
+  <si>
+    <t>0.64-0.72</t>
+  </si>
+  <si>
+    <t>IN_TPS_MAIN</t>
+  </si>
+  <si>
+    <t>M1.IN_TPS_S30</t>
+  </si>
+  <si>
+    <t>C19</t>
+  </si>
+  <si>
+    <t>C20</t>
+  </si>
+  <si>
+    <t>Fuel level sensor</t>
+  </si>
+  <si>
+    <t>0.12-4.75</t>
+  </si>
+  <si>
+    <t>IN_FUEL_LEVEL</t>
+  </si>
+  <si>
+    <t>M1.IN_AT1_S27; R45.1</t>
+  </si>
+  <si>
+    <t>C21</t>
+  </si>
+  <si>
+    <t>Fuel tank pressure sensor signal</t>
+  </si>
+  <si>
+    <t>2.3-2.7</t>
+  </si>
+  <si>
+    <t>C22</t>
+  </si>
+  <si>
+    <t>Manifold absolute pressure sensor signal</t>
+  </si>
+  <si>
+    <t>1.7-2.4</t>
+  </si>
+  <si>
+    <t>1.1-1.6</t>
+  </si>
+  <si>
+    <t>IN_MAP</t>
+  </si>
+  <si>
+    <t>M1.IN_MAP1_S21</t>
+  </si>
+  <si>
+    <t>C23</t>
+  </si>
+  <si>
+    <t>Mass air flow sensor signal</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>0.3-4.5</t>
+  </si>
+  <si>
+    <t>IN_MAF</t>
+  </si>
+  <si>
+    <t>M1.IN_SENS1_S9</t>
+  </si>
+  <si>
+    <t>C24</t>
+  </si>
+  <si>
+    <t>C25</t>
+  </si>
+  <si>
+    <t>Knock sensor signal</t>
+  </si>
+  <si>
+    <t>knock in</t>
+  </si>
+  <si>
+    <t>IN_KNOCK_RAW</t>
+  </si>
+  <si>
+    <t>M13.IN_KNOCK_W1</t>
+  </si>
+  <si>
+    <t>C26</t>
+  </si>
+  <si>
+    <t>Tumble generator valve position sensor LH</t>
+  </si>
+  <si>
+    <t>closed 3.8-4.9 / open 0.2-0.9</t>
+  </si>
+  <si>
+    <t>same</t>
+  </si>
+  <si>
+    <t>IN_TUMBLE_SENSOR_LH</t>
+  </si>
+  <si>
+    <t>M1.IN_MAP2_S20</t>
+  </si>
+  <si>
+    <t>C27</t>
+  </si>
+  <si>
+    <t>Tumble generator valve position sensor RH</t>
+  </si>
+  <si>
+    <t>IN_TUMBLE_SENSOR_RH</t>
+  </si>
+  <si>
+    <t>M1.IN_MAP3_S19</t>
+  </si>
+  <si>
+    <t>C28</t>
+  </si>
+  <si>
+    <t>Accelerator position sensor sub</t>
+  </si>
+  <si>
+    <t>IN_APS_SUB</t>
+  </si>
+  <si>
+    <t>IN_PPS_SUB</t>
+  </si>
+  <si>
+    <t>M1.IN_PPS2_S33</t>
+  </si>
+  <si>
+    <t>C29</t>
+  </si>
+  <si>
+    <t>Electric throttle sub (TPS2)</t>
+  </si>
+  <si>
+    <t>1.51-1.58 / open 4.17</t>
+  </si>
+  <si>
+    <t>1.51-1.58</t>
+  </si>
+  <si>
+    <t>IN_TPS_SUB</t>
+  </si>
+  <si>
+    <t>M1.IN_TPS2_S32</t>
+  </si>
+  <si>
+    <t>C30</t>
+  </si>
+  <si>
+    <t>C31</t>
+  </si>
+  <si>
+    <t>Mass air flow sensor GND</t>
+  </si>
+  <si>
+    <t>GND_SENSOR</t>
+  </si>
+  <si>
+    <t>J3.Pin_4_4; JP8.1_1; JP9.1_1</t>
+  </si>
+  <si>
+    <t>C32</t>
+  </si>
+  <si>
+    <t>Mass air flow sensor shield</t>
+  </si>
+  <si>
+    <t>C33</t>
+  </si>
+  <si>
+    <t>Knock sensor shield</t>
+  </si>
+  <si>
+    <t>C34</t>
+  </si>
+  <si>
+    <t>Accelerator position sensor GND (sensor)</t>
+  </si>
+  <si>
+    <t>APS_GND</t>
+  </si>
+  <si>
+    <t>C35</t>
+  </si>
+  <si>
+    <t>GND (sensor)</t>
+  </si>
+  <si>
+    <t>Return for ECT; rear O2; TGV; MAP; fuel tank pressure</t>
+  </si>
+  <si>
+    <t>B135</t>
+  </si>
+  <si>
+    <t>B1</t>
+  </si>
+  <si>
+    <t>GND (power supply)</t>
+  </si>
+  <si>
+    <t>B2</t>
+  </si>
+  <si>
+    <t>Rear oxygen sensor heater signal</t>
+  </si>
+  <si>
+    <t>heater low-side</t>
+  </si>
+  <si>
+    <t>0-1.0</t>
+  </si>
+  <si>
+    <t>OUT_O2_HEATER_REAR</t>
+  </si>
+  <si>
+    <t>Q14.D_2</t>
+  </si>
+  <si>
+    <t>B3</t>
+  </si>
+  <si>
+    <t>B4</t>
+  </si>
+  <si>
+    <t>B5</t>
+  </si>
+  <si>
+    <t>Control unit power supply</t>
+  </si>
+  <si>
+    <t>12 V in (main relay)</t>
+  </si>
+  <si>
+    <t>12V IN</t>
+  </si>
+  <si>
+    <t>+12V_RAW</t>
+  </si>
+  <si>
+    <t>B6</t>
+  </si>
+  <si>
+    <t>B7</t>
+  </si>
+  <si>
+    <t>B8</t>
+  </si>
+  <si>
+    <t>Camshaft position sensor (LH)</t>
+  </si>
+  <si>
+    <t>cam sensor in</t>
+  </si>
+  <si>
+    <t>ON 0 / OFF 4.7-5.3</t>
+  </si>
+  <si>
+    <t>Sensor output waveform</t>
+  </si>
+  <si>
+    <t>IN_CAM</t>
+  </si>
+  <si>
+    <t>M1.IN_CAM_S24; R42.1</t>
+  </si>
+  <si>
+    <t>B9</t>
+  </si>
+  <si>
+    <t>Camshaft position sensor (RH)</t>
+  </si>
+  <si>
+    <t>IN_CAM_RH</t>
+  </si>
+  <si>
+    <t>M1.IN_AUX1_S13; R43.1</t>
+  </si>
+  <si>
+    <t>B10</t>
+  </si>
+  <si>
+    <t>Crankshaft position sensor signal (+)</t>
+  </si>
+  <si>
+    <t>VR in</t>
+  </si>
+  <si>
+    <t>-7 to +7</t>
+  </si>
+  <si>
+    <t>IN_CRANK+</t>
+  </si>
+  <si>
+    <t>M5.VR+_W2</t>
+  </si>
+  <si>
+    <t>B11</t>
+  </si>
+  <si>
+    <t>B12</t>
+  </si>
+  <si>
+    <t>GND (ignition system)</t>
+  </si>
+  <si>
+    <t>B13</t>
+  </si>
+  <si>
+    <t>B14</t>
+  </si>
+  <si>
+    <t>B15</t>
+  </si>
+  <si>
+    <t>Ignition control #4</t>
+  </si>
+  <si>
+    <t>igniter output</t>
+  </si>
+  <si>
+    <t>WI-107</t>
+  </si>
+  <si>
+    <t>Net-(F1-Pad1)</t>
+  </si>
+  <si>
+    <t>F1 -&gt; OUT_IGN4 -&gt; M1.IGN4_W8</t>
+  </si>
+  <si>
+    <t>I/O table (EN(STi)-19) prints B135 16 for both #3 and #4; wiring diagram shows B15 to coil 4</t>
+  </si>
+  <si>
+    <t>B16</t>
+  </si>
+  <si>
+    <t>Ignition control #3</t>
+  </si>
+  <si>
+    <t>Net-(F2-Pad1)</t>
+  </si>
+  <si>
+    <t>F2 -&gt; OUT_IGN3 -&gt; M1.IGN3_W9</t>
+  </si>
+  <si>
+    <t>B17</t>
+  </si>
+  <si>
+    <t>Ignition control #2</t>
+  </si>
+  <si>
+    <t>Net-(F3-Pad1)</t>
+  </si>
+  <si>
+    <t>F3 -&gt; OUT_IGN2 -&gt; M1.IGN2_W10</t>
+  </si>
+  <si>
+    <t>B18</t>
+  </si>
+  <si>
+    <t>Ignition control #1</t>
+  </si>
+  <si>
+    <t>Net-(F4-Pad1)</t>
+  </si>
+  <si>
+    <t>F4 -&gt; OUT_IGN1 -&gt; M1.IGN1_W11</t>
+  </si>
+  <si>
+    <t>B19</t>
+  </si>
+  <si>
+    <t>Back-up power supply</t>
+  </si>
+  <si>
+    <t>12 V permanent in</t>
+  </si>
+  <si>
+    <t>+12V_BACK_UP</t>
+  </si>
+  <si>
+    <t>M14.V12_PERM_V1; M8.V12_PERM_V1</t>
+  </si>
+  <si>
+    <t>Ignition OFF: 10-13</t>
+  </si>
+  <si>
+    <t>B20</t>
+  </si>
+  <si>
+    <t>B21</t>
+  </si>
+  <si>
+    <t>B22</t>
+  </si>
+  <si>
+    <t>Crankshaft position sensor signal (-)</t>
+  </si>
+  <si>
+    <t>A/C relay control</t>
+  </si>
+  <si>
     <t>IN_CRANK-</t>
-  </si>
-  <si>
-    <t>D23</t>
-  </si>
-  <si>
-    <t>D24</t>
-  </si>
-  <si>
-    <t>Blow-by leak diagnosis signal</t>
-  </si>
-  <si>
-    <t>digital in</t>
-  </si>
-  <si>
-    <t>IN_BLOWBY</t>
-  </si>
-  <si>
-    <t>M12.IN_D4_V5</t>
-  </si>
-  <si>
-    <t>Disconnected (fault): 5</t>
-  </si>
-  <si>
-    <t>D25</t>
-  </si>
-  <si>
-    <t>Rear oxygen sensor signal</t>
-  </si>
-  <si>
-    <t>analog in (narrowband O2)</t>
-  </si>
-  <si>
-    <t>0-0.9</t>
-  </si>
-  <si>
-    <t>EN(STi)-18</t>
-  </si>
-  <si>
-    <t>IN_O2S</t>
-  </si>
-  <si>
-    <t>M1.IN_O2S_S16</t>
-  </si>
-  <si>
-    <t>D26</t>
-  </si>
-  <si>
-    <t>D27</t>
-  </si>
-  <si>
-    <t>D28</t>
-  </si>
-  <si>
-    <t>Fuel pump control unit signal 2</t>
-  </si>
-  <si>
-    <t>12 V to FPCU</t>
-  </si>
-  <si>
-    <t>FUEL_PUMP_SIGNAL2</t>
-  </si>
-  <si>
-    <t>FP_STATUS</t>
-  </si>
-  <si>
-    <t>JP7.1_1; P12.Pin_1_1</t>
-  </si>
-  <si>
-    <t>D29</t>
-  </si>
-  <si>
-    <t>(not in I/O table)</t>
-  </si>
-  <si>
-    <t>WI-112</t>
-  </si>
-  <si>
-    <t>DLC6_D29</t>
-  </si>
-  <si>
-    <t>JP4.1_1; P13.Pin_1_1</t>
-  </si>
-  <si>
-    <t>Red/white wire to data link connector pin 6 (WI-112); function not in the I/O table. Leave unconnected.</t>
-  </si>
-  <si>
-    <t>D30</t>
-  </si>
-  <si>
-    <t>D31</t>
-  </si>
-  <si>
-    <t>Rear oxygen sensor shield</t>
-  </si>
-  <si>
-    <t>shield</t>
-  </si>
-  <si>
-    <t>B136</t>
-  </si>
-  <si>
-    <t>C1</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>C3</t>
-  </si>
-  <si>
-    <t>Fuel injector #4</t>
-  </si>
-  <si>
-    <t>injector low-side</t>
-  </si>
-  <si>
-    <t>OUT_INJ4</t>
-  </si>
-  <si>
-    <t>Q4.D_2</t>
-  </si>
-  <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>Fuel injector #3</t>
-  </si>
-  <si>
-    <t>OUT_INJ3</t>
-  </si>
-  <si>
-    <t>Q3.D_2</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>Fuel injector #2</t>
-  </si>
-  <si>
-    <t>OUT_INJ2</t>
-  </si>
-  <si>
-    <t>Q2.D_2</t>
-  </si>
-  <si>
-    <t>C6</t>
-  </si>
-  <si>
-    <t>Fuel injector #1</t>
-  </si>
-  <si>
-    <t>OUT_INJ1</t>
-  </si>
-  <si>
-    <t>Q1.D_2</t>
-  </si>
-  <si>
-    <t>C7</t>
-  </si>
-  <si>
-    <t>Cruise main switch</t>
-  </si>
-  <si>
-    <t>EN(STi)-22</t>
-  </si>
-  <si>
-    <t>IN_CRUISE_MAIN</t>
-  </si>
-  <si>
-    <t>M1.IN_D1_S4; R35.1</t>
-  </si>
-  <si>
-    <t>C8</t>
-  </si>
-  <si>
-    <t>Brake switch 2</t>
-  </si>
-  <si>
-    <t>pressed 10-13 / released 0</t>
-  </si>
-  <si>
-    <t>pressed 13-14 / released 0</t>
-  </si>
-  <si>
-    <t>IN_BRAKE_SW2</t>
-  </si>
-  <si>
-    <t>M1.IN_SENS4_S6; R32.1</t>
-  </si>
-  <si>
-    <t>C9</t>
-  </si>
-  <si>
-    <t>Brake switch 1</t>
-  </si>
-  <si>
-    <t>pressed 0 / released 10-13</t>
-  </si>
-  <si>
-    <t>pressed 0 / released 13-14</t>
-  </si>
-  <si>
-    <t>IN_BRAKE_SW1</t>
-  </si>
-  <si>
-    <t>M1.IN_O2S2_S15; R34.1</t>
-  </si>
-  <si>
-    <t>C10</t>
-  </si>
-  <si>
-    <t>RESUME/ACCEL switch</t>
-  </si>
-  <si>
-    <t>IN_CRUISE_RESUME</t>
-  </si>
-  <si>
-    <t>M1.IN_D3_S2; R36.1</t>
-  </si>
-  <si>
-    <t>C11</t>
-  </si>
-  <si>
-    <t>SET/COAST switch</t>
-  </si>
-  <si>
-    <t>IN_CRUISE_SET</t>
-  </si>
-  <si>
-    <t>M1.IN_D4_S1; R37.1</t>
-  </si>
-  <si>
-    <t>C12</t>
-  </si>
-  <si>
-    <t>Fuel temperature sensor signal</t>
-  </si>
-  <si>
-    <t>analog in (thermistor)</t>
-  </si>
-  <si>
-    <t>2.5-3.8</t>
-  </si>
-  <si>
-    <t>At 25 C</t>
-  </si>
-  <si>
-    <t>C13</t>
-  </si>
-  <si>
-    <t>Intake air temperature sensor signal</t>
-  </si>
-  <si>
-    <t>0.3-4.6</t>
-  </si>
-  <si>
-    <t>IN_IAT</t>
-  </si>
-  <si>
-    <t>M1.IN_IAT_S26</t>
-  </si>
-  <si>
-    <t>In the MAF housing</t>
-  </si>
-  <si>
-    <t>C14</t>
-  </si>
-  <si>
-    <t>Engine coolant temperature sensor signal</t>
-  </si>
-  <si>
-    <t>1.0-1.4</t>
-  </si>
-  <si>
-    <t>IN_ECT</t>
-  </si>
-  <si>
-    <t>M1.IN_CLT_S28</t>
-  </si>
-  <si>
-    <t>After warm-up</t>
-  </si>
-  <si>
-    <t>C15</t>
-  </si>
-  <si>
-    <t>Accelerator position sensor power supply</t>
-  </si>
-  <si>
-    <t>5 V sensor supply out</t>
-  </si>
-  <si>
-    <t>APS_PS_5V</t>
-  </si>
-  <si>
-    <t>JP11.1_1; M8.5VP_V4</t>
-  </si>
-  <si>
-    <t>C16</t>
-  </si>
-  <si>
-    <t>Sensor power supply</t>
-  </si>
-  <si>
-    <t>5v OUT SENSOR_PS_5V</t>
-  </si>
-  <si>
-    <t>SENSOR_PS_5V</t>
-  </si>
-  <si>
-    <t>+5VAS</t>
-  </si>
-  <si>
-    <t>F7 -&gt; AUX_5V -&gt; J3.Pin_3_3; JP11.2_2; M14.5VP_V4</t>
-  </si>
-  <si>
-    <t>Feeds throttle TPS; MAP; TGV sensors</t>
-  </si>
-  <si>
-    <t>C17</t>
-  </si>
-  <si>
-    <t>Accelerator position sensor main</t>
-  </si>
-  <si>
-    <t>analog in</t>
-  </si>
-  <si>
-    <t>closed 1 / open 3.5</t>
-  </si>
-  <si>
-    <t>IN_APS_MAIN</t>
-  </si>
-  <si>
-    <t>IN_PPS_MAIN</t>
-  </si>
-  <si>
-    <t>M1.IN_PPS_S31</t>
-  </si>
-  <si>
-    <t>C18</t>
-  </si>
-  <si>
-    <t>Electric throttle main (TPS1)</t>
-  </si>
-  <si>
-    <t>0.64-0.72 / open 3.96</t>
-  </si>
-  <si>
-    <t>0.64-0.72</t>
-  </si>
-  <si>
-    <t>IN_TPS_MAIN</t>
-  </si>
-  <si>
-    <t>M1.IN_TPS_S30</t>
-  </si>
-  <si>
-    <t>C19</t>
-  </si>
-  <si>
-    <t>C20</t>
-  </si>
-  <si>
-    <t>Fuel level sensor</t>
-  </si>
-  <si>
-    <t>0.12-4.75</t>
-  </si>
-  <si>
-    <t>IN_FUEL_LEVEL</t>
-  </si>
-  <si>
-    <t>M1.IN_AT1_S27; R45.1</t>
-  </si>
-  <si>
-    <t>C21</t>
-  </si>
-  <si>
-    <t>Fuel tank pressure sensor signal</t>
-  </si>
-  <si>
-    <t>2.3-2.7</t>
-  </si>
-  <si>
-    <t>C22</t>
-  </si>
-  <si>
-    <t>Manifold absolute pressure sensor signal</t>
-  </si>
-  <si>
-    <t>1.7-2.4</t>
-  </si>
-  <si>
-    <t>1.1-1.6</t>
-  </si>
-  <si>
-    <t>IN_MAP</t>
-  </si>
-  <si>
-    <t>M1.IN_MAP1_S21</t>
-  </si>
-  <si>
-    <t>C23</t>
-  </si>
-  <si>
-    <t>Mass air flow sensor signal</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>0.3-4.5</t>
-  </si>
-  <si>
-    <t>IN_MAF</t>
-  </si>
-  <si>
-    <t>M1.IN_SENS1_S9</t>
-  </si>
-  <si>
-    <t>C24</t>
-  </si>
-  <si>
-    <t>C25</t>
-  </si>
-  <si>
-    <t>Knock sensor signal</t>
-  </si>
-  <si>
-    <t>knock in</t>
-  </si>
-  <si>
-    <t>IN_KNOCK_RAW</t>
-  </si>
-  <si>
-    <t>M13.IN_KNOCK_W1</t>
-  </si>
-  <si>
-    <t>C26</t>
-  </si>
-  <si>
-    <t>Tumble generator valve position sensor LH</t>
-  </si>
-  <si>
-    <t>closed 3.8-4.9 / open 0.2-0.9</t>
-  </si>
-  <si>
-    <t>same</t>
-  </si>
-  <si>
-    <t>IN_TUMBLE_SENSOR_LH</t>
-  </si>
-  <si>
-    <t>M1.IN_MAP2_S20</t>
-  </si>
-  <si>
-    <t>C27</t>
-  </si>
-  <si>
-    <t>Tumble generator valve position sensor RH</t>
-  </si>
-  <si>
-    <t>IN_TUMBLE_SENSOR_RH</t>
-  </si>
-  <si>
-    <t>M1.IN_MAP3_S19</t>
-  </si>
-  <si>
-    <t>C28</t>
-  </si>
-  <si>
-    <t>Accelerator position sensor sub</t>
-  </si>
-  <si>
-    <t>IN_APS_SUB</t>
-  </si>
-  <si>
-    <t>IN_PPS_SUB</t>
-  </si>
-  <si>
-    <t>M1.IN_PPS2_S33</t>
-  </si>
-  <si>
-    <t>C29</t>
-  </si>
-  <si>
-    <t>Electric throttle sub (TPS2)</t>
-  </si>
-  <si>
-    <t>1.51-1.58 / open 4.17</t>
-  </si>
-  <si>
-    <t>1.51-1.58</t>
-  </si>
-  <si>
-    <t>IN_TPS_SUB</t>
-  </si>
-  <si>
-    <t>M1.IN_TPS2_S32</t>
-  </si>
-  <si>
-    <t>C30</t>
-  </si>
-  <si>
-    <t>C31</t>
-  </si>
-  <si>
-    <t>Mass air flow sensor GND</t>
-  </si>
-  <si>
-    <t>GND_SENSOR</t>
-  </si>
-  <si>
-    <t>J3.Pin_4_4; JP8.1_1; JP9.1_1</t>
-  </si>
-  <si>
-    <t>C32</t>
-  </si>
-  <si>
-    <t>Mass air flow sensor shield</t>
-  </si>
-  <si>
-    <t>C33</t>
-  </si>
-  <si>
-    <t>Knock sensor shield</t>
-  </si>
-  <si>
-    <t>C34</t>
-  </si>
-  <si>
-    <t>Accelerator position sensor GND (sensor)</t>
-  </si>
-  <si>
-    <t>APS_GND</t>
-  </si>
-  <si>
-    <t>C35</t>
-  </si>
-  <si>
-    <t>GND (sensor)</t>
-  </si>
-  <si>
-    <t>Return for ECT; rear O2; TGV; MAP; fuel tank pressure</t>
-  </si>
-  <si>
-    <t>B135</t>
-  </si>
-  <si>
-    <t>B1</t>
-  </si>
-  <si>
-    <t>GND (power supply)</t>
-  </si>
-  <si>
-    <t>B2</t>
-  </si>
-  <si>
-    <t>Rear oxygen sensor heater signal</t>
-  </si>
-  <si>
-    <t>heater low-side</t>
-  </si>
-  <si>
-    <t>0-1.0</t>
-  </si>
-  <si>
-    <t>OUT_O2_HEATER_REAR</t>
-  </si>
-  <si>
-    <t>Q14.D_2</t>
-  </si>
-  <si>
-    <t>B3</t>
-  </si>
-  <si>
-    <t>B4</t>
-  </si>
-  <si>
-    <t>B5</t>
-  </si>
-  <si>
-    <t>Control unit power supply</t>
-  </si>
-  <si>
-    <t>12 V in (main relay)</t>
-  </si>
-  <si>
-    <t>12V IN</t>
-  </si>
-  <si>
-    <t>+12V_RAW</t>
-  </si>
-  <si>
-    <t>B6</t>
-  </si>
-  <si>
-    <t>B7</t>
-  </si>
-  <si>
-    <t>B8</t>
-  </si>
-  <si>
-    <t>Camshaft position sensor (LH)</t>
-  </si>
-  <si>
-    <t>cam sensor in</t>
-  </si>
-  <si>
-    <t>ON 0 / OFF 4.7-5.3</t>
-  </si>
-  <si>
-    <t>Sensor output waveform</t>
-  </si>
-  <si>
-    <t>IN_CAM_HALL_CAM_LH</t>
-  </si>
-  <si>
-    <t>IN_CAM</t>
-  </si>
-  <si>
-    <t>M1.IN_CAM_S24; R42.1</t>
-  </si>
-  <si>
-    <t>B9</t>
-  </si>
-  <si>
-    <t>Camshaft position sensor (RH)</t>
-  </si>
-  <si>
-    <t>IN_CAM_HALL_CAM_RH</t>
-  </si>
-  <si>
-    <t>IN_CAM_RH</t>
-  </si>
-  <si>
-    <t>M1.IN_AUX1_S13; R43.1</t>
-  </si>
-  <si>
-    <t>B10</t>
-  </si>
-  <si>
-    <t>Crankshaft position sensor signal (+)</t>
-  </si>
-  <si>
-    <t>VR in</t>
-  </si>
-  <si>
-    <t>-7 to +7</t>
-  </si>
-  <si>
-    <t>IN_CRANK+</t>
-  </si>
-  <si>
-    <t>M5.VR+_W2</t>
-  </si>
-  <si>
-    <t>B11</t>
-  </si>
-  <si>
-    <t>B12</t>
-  </si>
-  <si>
-    <t>GND (ignition system)</t>
-  </si>
-  <si>
-    <t>B13</t>
-  </si>
-  <si>
-    <t>B14</t>
-  </si>
-  <si>
-    <t>B15</t>
-  </si>
-  <si>
-    <t>Ignition control #4</t>
-  </si>
-  <si>
-    <t>igniter output</t>
-  </si>
-  <si>
-    <t>WI-107</t>
-  </si>
-  <si>
-    <t>Net-(F1-Pad1)</t>
-  </si>
-  <si>
-    <t>F1 -&gt; OUT_IGN4 -&gt; M1.IGN4_W8</t>
-  </si>
-  <si>
-    <t>I/O table (EN(STi)-19) prints B135 16 for both #3 and #4; wiring diagram shows B15 to coil 4</t>
-  </si>
-  <si>
-    <t>B16</t>
-  </si>
-  <si>
-    <t>Ignition control #3</t>
-  </si>
-  <si>
-    <t>Net-(F2-Pad1)</t>
-  </si>
-  <si>
-    <t>F2 -&gt; OUT_IGN3 -&gt; M1.IGN3_W9</t>
-  </si>
-  <si>
-    <t>B17</t>
-  </si>
-  <si>
-    <t>Ignition control #2</t>
-  </si>
-  <si>
-    <t>Net-(F3-Pad1)</t>
-  </si>
-  <si>
-    <t>F3 -&gt; OUT_IGN2 -&gt; M1.IGN2_W10</t>
-  </si>
-  <si>
-    <t>B18</t>
-  </si>
-  <si>
-    <t>Ignition control #1</t>
-  </si>
-  <si>
-    <t>Net-(F4-Pad1)</t>
-  </si>
-  <si>
-    <t>F4 -&gt; OUT_IGN1 -&gt; M1.IGN1_W11</t>
-  </si>
-  <si>
-    <t>B19</t>
-  </si>
-  <si>
-    <t>Back-up power supply</t>
-  </si>
-  <si>
-    <t>12 V permanent in</t>
-  </si>
-  <si>
-    <t>+12V_BACK_UP</t>
-  </si>
-  <si>
-    <t>M14.V12_PERM_V1; M8.V12_PERM_V1</t>
-  </si>
-  <si>
-    <t>Ignition OFF: 10-13</t>
-  </si>
-  <si>
-    <t>B20</t>
-  </si>
-  <si>
-    <t>B21</t>
-  </si>
-  <si>
-    <t>B22</t>
-  </si>
-  <si>
-    <t>Crankshaft position sensor signal (-)</t>
-  </si>
-  <si>
-    <t>A/C relay control</t>
   </si>
   <si>
     <t>M5.VR-_W1</t>
@@ -2047,7 +2023,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O136"/>
+  <dimension ref="A1:N136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -2058,10 +2034,10 @@
     <col min="6" max="6" width="22.7109375" customWidth="1"/>
     <col min="7" max="8" width="16.7109375" customWidth="1"/>
     <col min="9" max="9" width="11.7109375" customWidth="1"/>
-    <col min="10" max="12" width="26.7109375" customWidth="1"/>
-    <col min="13" max="13" width="34.7109375" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" customWidth="1"/>
-    <col min="15" max="15" width="44.7109375" customWidth="1"/>
+    <col min="10" max="11" width="26.7109375" customWidth="1"/>
+    <col min="12" max="12" width="34.7109375" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" customWidth="1"/>
+    <col min="14" max="14" width="44.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="44.25">
@@ -2102,13 +2078,10 @@
         <v>35</v>
       </c>
       <c r="M1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2" ht="44.25">
@@ -2116,19 +2089,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C2" s="4">
         <v>1</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="G2" s="4">
         <v>0</v>
@@ -2137,41 +2110,38 @@
         <v>0</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J2" s="4"/>
       <c r="K2" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L2" s="4" t="s">
         <v>43</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O2" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N2" s="4"/>
     </row>
     <row r="3" ht="44.25">
       <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C3" s="4">
         <v>2</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="G3" s="4">
         <v>0</v>
@@ -2180,41 +2150,38 @@
         <v>0</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J3" s="4"/>
       <c r="K3" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L3" s="4" t="s">
         <v>43</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O3" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N3" s="4"/>
     </row>
     <row r="4" ht="98.25">
       <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C4" s="4">
         <v>3</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>47</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>48</v>
       </c>
       <c r="G4" s="4">
         <v>0</v>
@@ -2223,23 +2190,20 @@
         <v>0</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>43</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" ht="44.25">
@@ -2247,46 +2211,43 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C5" s="4">
         <v>4</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="K5" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>55</v>
       </c>
       <c r="M5" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="6" ht="57.75">
@@ -2294,46 +2255,43 @@
         <v>5</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" s="4">
         <v>5</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="F6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>60</v>
-      </c>
       <c r="K6" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>60</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="N6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" ht="71.25">
@@ -2341,62 +2299,59 @@
         <v>6</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C7" s="4">
         <v>6</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="F7" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="G7" s="5">
         <v>46308</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J7" s="4"/>
       <c r="K7" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="L7" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="L7" s="4" t="s">
-        <v>67</v>
-      </c>
       <c r="M7" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O7" s="4"/>
-    </row>
-    <row r="8" ht="44.25">
+        <v>3</v>
+      </c>
+      <c r="N7" s="4"/>
+    </row>
+    <row r="8" ht="30.75">
       <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" s="4">
         <v>7</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" s="4">
         <v>0</v>
@@ -2405,41 +2360,38 @@
         <v>0</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J8" s="4"/>
       <c r="K8" s="4" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>43</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N8" s="4"/>
     </row>
     <row r="9" ht="44.25">
       <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C9" s="4">
         <v>8</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G9" s="4">
         <v>0</v>
@@ -2448,23 +2400,20 @@
         <v>0</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J9" s="4"/>
       <c r="K9" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" ht="44.25">
@@ -2472,212 +2421,203 @@
         <v>9</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="4">
         <v>9</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E10" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>82</v>
-      </c>
       <c r="I10" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J10" s="4"/>
       <c r="K10" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N10" s="4"/>
     </row>
     <row r="11" ht="98.25">
       <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C11" s="4">
         <v>10</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G11" s="5">
         <v>46308</v>
       </c>
       <c r="H11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="L11" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="I11" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>91</v>
-      </c>
       <c r="M11" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O11" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N11" s="4"/>
     </row>
     <row r="12" ht="44.25">
       <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C12" s="4">
         <v>11</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="L12" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4" t="s">
-        <v>96</v>
-      </c>
       <c r="M12" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O12" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N12" s="4"/>
     </row>
     <row r="13" ht="44.25">
       <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C13" s="4">
         <v>12</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
+      <c r="K13" s="4" t="s">
+        <v>96</v>
+      </c>
       <c r="L13" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O13" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N13" s="4"/>
     </row>
     <row r="14" ht="71.25">
       <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" s="4">
         <v>13</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="15" ht="44.25">
@@ -2685,19 +2625,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" s="4">
         <v>14</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G15" s="4">
         <v>5</v>
@@ -2706,21 +2646,20 @@
         <v>5</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
+      <c r="K15" s="4" t="s">
+        <v>106</v>
+      </c>
       <c r="L15" s="4" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>111</v>
+        <v>3</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O15" s="4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" ht="71.25">
@@ -2728,124 +2667,117 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C16" s="4">
         <v>15</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G16" s="5">
         <v>46308</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J16" s="4"/>
       <c r="K16" s="4" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="N16" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O16" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N16" s="4"/>
     </row>
     <row r="17" ht="44.25">
       <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" s="4">
         <v>16</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
+      <c r="K17" s="4" t="s">
+        <v>116</v>
+      </c>
       <c r="L17" s="4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="N17" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O17" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N17" s="4"/>
     </row>
     <row r="18" ht="125.25">
       <c r="A18" s="4">
         <v>17</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" s="4">
         <v>17</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G18" s="4"/>
       <c r="H18" s="4"/>
       <c r="I18" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="J18" s="4"/>
       <c r="K18" s="4" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>127</v>
+        <v>3</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" s="4" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" ht="30.75">
@@ -2853,16 +2785,16 @@
         <v>18</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C19" s="4">
         <v>18</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
@@ -2871,27 +2803,26 @@
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4" t="s">
+      <c r="M19" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O19" s="4"/>
+      <c r="N19" s="4"/>
     </row>
     <row r="20" ht="30.75">
       <c r="A20" s="4">
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C20" s="4">
         <v>19</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
@@ -2900,68 +2831,66 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4" t="s">
+      <c r="M20" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O20" s="4"/>
+      <c r="N20" s="4"/>
     </row>
     <row r="21" ht="71.25">
       <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21" s="4">
         <v>20</v>
       </c>
       <c r="D21" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="L21" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4" t="s">
-        <v>136</v>
-      </c>
       <c r="M21" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="N21" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N21" s="4"/>
     </row>
     <row r="22" ht="30.75">
       <c r="A22" s="4">
         <v>21</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C22" s="4">
         <v>21</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
@@ -2970,58 +2899,54 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4" t="s">
+      <c r="M22" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O22" s="4"/>
+      <c r="N22" s="4"/>
     </row>
     <row r="23" ht="30.75">
       <c r="A23" s="4">
         <v>22</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="4">
         <v>22</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="4"/>
-      <c r="K23" s="4" t="s">
-        <v>140</v>
-      </c>
+      <c r="K23" s="4"/>
       <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4" t="s">
+      <c r="M23" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O23" s="4"/>
+      <c r="N23" s="4"/>
     </row>
     <row r="24" ht="30.75">
       <c r="A24" s="4">
         <v>23</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C24" s="4">
         <v>23</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
@@ -3030,30 +2955,29 @@
       <c r="J24" s="4"/>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4" t="s">
+      <c r="M24" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O24" s="4"/>
+      <c r="N24" s="4"/>
     </row>
     <row r="25" ht="57.75">
       <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C25" s="4">
         <v>24</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G25" s="4">
         <v>0</v>
@@ -3062,21 +2986,20 @@
         <v>0</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
+      <c r="K25" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="L25" s="4" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>146</v>
+        <v>3</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O25" s="4" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" ht="57.75">
@@ -3084,57 +3007,56 @@
         <v>25</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C26" s="4">
         <v>25</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G26" s="4">
         <v>0</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
+      <c r="K26" s="4" t="s">
+        <v>148</v>
+      </c>
       <c r="L26" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O26" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N26" s="4"/>
     </row>
     <row r="27" ht="30.75">
       <c r="A27" s="4">
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C27" s="4">
         <v>26</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -3143,27 +3065,26 @@
       <c r="J27" s="4"/>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4" t="s">
+      <c r="M27" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O27" s="4"/>
+      <c r="N27" s="4"/>
     </row>
     <row r="28" ht="30.75">
       <c r="A28" s="4">
         <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C28" s="4">
         <v>27</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -3172,90 +3093,85 @@
       <c r="J28" s="4"/>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4" t="s">
+      <c r="M28" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O28" s="4"/>
+      <c r="N28" s="4"/>
     </row>
     <row r="29" ht="57.75">
       <c r="A29" s="4">
         <v>28</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C29" s="4">
         <v>28</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G29" s="5">
         <v>46308</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J29" s="4"/>
       <c r="K29" s="4" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="N29" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O29" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N29" s="4"/>
     </row>
     <row r="30" ht="178.5">
       <c r="A30" s="4">
         <v>29</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C30" s="4">
         <v>29</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
+      <c r="K30" s="4" t="s">
+        <v>160</v>
+      </c>
       <c r="L30" s="4" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>167</v>
+        <v>3</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O30" s="4" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" ht="30.75">
@@ -3263,16 +3179,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C31" s="4">
         <v>30</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
@@ -3281,30 +3197,29 @@
       <c r="J31" s="4"/>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4" t="s">
+      <c r="M31" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O31" s="4"/>
+      <c r="N31" s="4"/>
     </row>
     <row r="32" ht="57.75">
       <c r="A32" s="4">
         <v>31</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C32" s="4">
         <v>31</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G32" s="4">
         <v>0</v>
@@ -3313,38 +3228,35 @@
         <v>0</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J32" s="4"/>
       <c r="K32" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L32" s="4" t="s">
         <v>43</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N32" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O32" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N32" s="4"/>
     </row>
     <row r="33" ht="30.75">
       <c r="A33" s="4">
         <v>32</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C33" s="4">
         <v>1</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
@@ -3353,27 +3265,26 @@
       <c r="J33" s="4"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4" t="s">
+      <c r="M33" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O33" s="4"/>
+      <c r="N33" s="4"/>
     </row>
     <row r="34" ht="30.75">
       <c r="A34" s="4">
         <v>33</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C34" s="4">
         <v>2</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F34" s="4"/>
       <c r="G34" s="4"/>
@@ -3382,30 +3293,29 @@
       <c r="J34" s="4"/>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4" t="s">
+      <c r="M34" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O34" s="4"/>
+      <c r="N34" s="4"/>
     </row>
     <row r="35" ht="30.75">
       <c r="A35" s="4">
         <v>34</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C35" s="4">
         <v>3</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G35" s="5">
         <v>46308</v>
@@ -3414,41 +3324,38 @@
         <v>46036</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J35" s="4"/>
       <c r="K35" s="4" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="N35" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O35" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N35" s="4"/>
     </row>
     <row r="36" ht="30.75">
       <c r="A36" s="4">
         <v>35</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C36" s="4">
         <v>4</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G36" s="5">
         <v>46308</v>
@@ -3457,41 +3364,38 @@
         <v>46036</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J36" s="4"/>
       <c r="K36" s="4" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="N36" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O36" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N36" s="4"/>
     </row>
     <row r="37" ht="30.75">
       <c r="A37" s="4">
         <v>36</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C37" s="4">
         <v>5</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G37" s="5">
         <v>46308</v>
@@ -3500,41 +3404,38 @@
         <v>46036</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J37" s="4"/>
       <c r="K37" s="4" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="N37" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O37" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N37" s="4"/>
     </row>
     <row r="38" ht="30.75">
       <c r="A38" s="4">
         <v>37</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C38" s="4">
         <v>6</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="G38" s="5">
         <v>46308</v>
@@ -3543,265 +3444,256 @@
         <v>46036</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J38" s="4"/>
       <c r="K38" s="4" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="N38" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O38" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N38" s="4"/>
     </row>
     <row r="39" ht="44.25">
       <c r="A39" s="4">
         <v>38</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C39" s="4">
         <v>7</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
+      <c r="K39" s="4" t="s">
+        <v>190</v>
+      </c>
       <c r="L39" s="4" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="M39" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="N39" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O39" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N39" s="4"/>
     </row>
     <row r="40" ht="57.75">
       <c r="A40" s="4">
         <v>39</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C40" s="4">
         <v>8</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
+      <c r="K40" s="4" t="s">
+        <v>196</v>
+      </c>
       <c r="L40" s="4" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="N40" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O40" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N40" s="4"/>
     </row>
     <row r="41" ht="57.75">
       <c r="A41" s="4">
         <v>40</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C41" s="4">
         <v>9</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
+      <c r="K41" s="4" t="s">
+        <v>202</v>
+      </c>
       <c r="L41" s="4" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="M41" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="N41" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O41" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N41" s="4"/>
     </row>
     <row r="42" ht="44.25">
       <c r="A42" s="4">
         <v>41</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C42" s="4">
         <v>10</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
+      <c r="K42" s="4" t="s">
+        <v>206</v>
+      </c>
       <c r="L42" s="4" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="N42" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O42" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N42" s="4"/>
     </row>
     <row r="43" ht="44.25">
       <c r="A43" s="4">
         <v>42</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C43" s="4">
         <v>11</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
+      <c r="K43" s="4" t="s">
+        <v>210</v>
+      </c>
       <c r="L43" s="4" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="N43" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O43" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N43" s="4"/>
     </row>
     <row r="44" ht="57.75">
       <c r="A44" s="4">
         <v>43</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C44" s="4">
         <v>12</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
-      <c r="M44" s="4"/>
+      <c r="M44" s="4" t="s">
+        <v>9</v>
+      </c>
       <c r="N44" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="O44" s="4" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="45" ht="71.25">
@@ -3809,44 +3701,41 @@
         <v>44</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C45" s="4">
         <v>13</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J45" s="4"/>
       <c r="K45" s="4" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>227</v>
+        <v>3</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O45" s="4" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="46" ht="71.25">
@@ -3854,44 +3743,41 @@
         <v>45</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C46" s="4">
         <v>14</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J46" s="4"/>
       <c r="K46" s="4" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>233</v>
+        <v>3</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O46" s="4" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="47" ht="71.25">
@@ -3899,19 +3785,19 @@
         <v>46</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C47" s="4">
         <v>15</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="G47" s="4">
         <v>5</v>
@@ -3920,41 +3806,38 @@
         <v>5</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J47" s="4"/>
       <c r="K47" s="4" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="N47" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O47" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N47" s="4"/>
     </row>
     <row r="48" ht="98.25">
       <c r="A48" s="4">
         <v>47</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C48" s="4">
         <v>16</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="G48" s="4">
         <v>5</v>
@@ -3963,25 +3846,22 @@
         <v>5</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>245</v>
+        <v>3</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O48" s="4" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
     </row>
     <row r="49" ht="57.75">
@@ -3989,106 +3869,100 @@
         <v>48</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C49" s="4">
         <v>17</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="N49" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O49" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N49" s="4"/>
     </row>
     <row r="50" ht="57.75">
       <c r="A50" s="4">
         <v>49</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C50" s="4">
         <v>18</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="F50" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="G50" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="G50" s="4" t="s">
-        <v>256</v>
-      </c>
       <c r="H50" s="4" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="N50" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O50" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N50" s="4"/>
     </row>
     <row r="51" ht="30.75">
       <c r="A51" s="4">
         <v>50</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C51" s="4">
         <v>19</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
@@ -4097,191 +3971,182 @@
       <c r="J51" s="4"/>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4" t="s">
+      <c r="M51" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O51" s="4"/>
+      <c r="N51" s="4"/>
     </row>
     <row r="52" ht="44.25">
       <c r="A52" s="4">
         <v>51</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C52" s="4">
         <v>20</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J52" s="4"/>
       <c r="K52" s="4" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="N52" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O52" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N52" s="4"/>
     </row>
     <row r="53" ht="57.75">
       <c r="A53" s="4">
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C53" s="4">
         <v>21</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J53" s="4"/>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4" t="s">
+      <c r="M53" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="O53" s="4"/>
+      <c r="N53" s="4"/>
     </row>
     <row r="54" ht="71.25">
       <c r="A54" s="4">
         <v>53</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C54" s="4">
         <v>22</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
+      <c r="K54" s="4" t="s">
+        <v>266</v>
+      </c>
       <c r="L54" s="4" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="N54" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O54" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N54" s="4"/>
     </row>
     <row r="55" ht="57.75">
       <c r="A55" s="4">
         <v>54</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C55" s="4">
         <v>23</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J55" s="4"/>
       <c r="K55" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="L55" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="L55" s="4" t="s">
-        <v>279</v>
-      </c>
       <c r="M55" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="N55" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O55" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N55" s="4"/>
     </row>
     <row r="56" ht="30.75">
       <c r="A56" s="4">
         <v>55</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C56" s="4">
         <v>24</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
@@ -4290,30 +4155,29 @@
       <c r="J56" s="4"/>
       <c r="K56" s="4"/>
       <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4" t="s">
+      <c r="M56" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O56" s="4"/>
+      <c r="N56" s="4"/>
     </row>
     <row r="57" ht="44.25">
       <c r="A57" s="4">
         <v>56</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C57" s="4">
         <v>25</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="G57" s="4">
         <v>2.8</v>
@@ -4322,218 +4186,203 @@
         <v>2.8</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J57" s="4"/>
       <c r="K57" s="4" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="M57" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="N57" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O57" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N57" s="4"/>
     </row>
     <row r="58" ht="71.25">
       <c r="A58" s="4">
         <v>57</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C58" s="4">
         <v>26</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="M58" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="N58" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O58" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N58" s="4"/>
     </row>
     <row r="59" ht="71.25">
       <c r="A59" s="4">
         <v>58</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C59" s="4">
         <v>27</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="G59" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="I59" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="L59" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="H59" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="I59" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="J59" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="K59" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="L59" s="4" t="s">
-        <v>295</v>
-      </c>
       <c r="M59" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="N59" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O59" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N59" s="4"/>
     </row>
     <row r="60" ht="57.75">
       <c r="A60" s="4">
         <v>59</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C60" s="4">
         <v>28</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="M60" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="N60" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O60" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N60" s="4"/>
     </row>
     <row r="61" ht="57.75">
       <c r="A61" s="4">
         <v>60</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C61" s="4">
         <v>29</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="M61" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="N61" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O61" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N61" s="4"/>
     </row>
     <row r="62" ht="30.75">
       <c r="A62" s="4">
         <v>61</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C62" s="4">
         <v>30</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F62" s="4"/>
       <c r="G62" s="4"/>
@@ -4542,30 +4391,29 @@
       <c r="J62" s="4"/>
       <c r="K62" s="4"/>
       <c r="L62" s="4"/>
-      <c r="M62" s="4"/>
-      <c r="N62" s="4" t="s">
+      <c r="M62" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O62" s="4"/>
+      <c r="N62" s="4"/>
     </row>
     <row r="63" ht="57.75">
       <c r="A63" s="4">
         <v>62</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C63" s="4">
         <v>31</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G63" s="4">
         <v>0</v>
@@ -4574,41 +4422,38 @@
         <v>0</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J63" s="4"/>
       <c r="K63" s="4" t="s">
-        <v>43</v>
+        <v>304</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="N63" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O63" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N63" s="4"/>
     </row>
     <row r="64" ht="57.75">
       <c r="A64" s="4">
         <v>63</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C64" s="4">
         <v>32</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G64" s="4">
         <v>0</v>
@@ -4617,41 +4462,38 @@
         <v>0</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J64" s="4"/>
       <c r="K64" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L64" s="4" t="s">
         <v>43</v>
       </c>
       <c r="M64" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N64" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O64" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N64" s="4"/>
     </row>
     <row r="65" ht="44.25">
       <c r="A65" s="4">
         <v>64</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C65" s="4">
         <v>33</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G65" s="4">
         <v>0</v>
@@ -4660,41 +4502,38 @@
         <v>0</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J65" s="4"/>
       <c r="K65" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L65" s="4" t="s">
         <v>43</v>
       </c>
       <c r="M65" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N65" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O65" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N65" s="4"/>
     </row>
     <row r="66" ht="71.25">
       <c r="A66" s="4">
         <v>65</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C66" s="4">
         <v>34</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G66" s="4">
         <v>0</v>
@@ -4703,43 +4542,40 @@
         <v>0</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>43</v>
+        <v>304</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="M66" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="N66" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O66" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N66" s="4"/>
     </row>
     <row r="67" ht="98.25">
       <c r="A67" s="4">
         <v>66</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C67" s="4">
         <v>35</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G67" s="4">
         <v>0</v>
@@ -4748,23 +4584,20 @@
         <v>0</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J67" s="4"/>
       <c r="K67" s="4" t="s">
-        <v>43</v>
+        <v>304</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="M67" s="4" t="s">
-        <v>312</v>
+        <v>3</v>
       </c>
       <c r="N67" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O67" s="4" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="68" ht="44.25">
@@ -4772,19 +4605,19 @@
         <v>67</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C68" s="4">
         <v>1</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G68" s="4">
         <v>0</v>
@@ -4793,79 +4626,75 @@
         <v>0</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J68" s="4"/>
       <c r="K68" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L68" s="4" t="s">
         <v>43</v>
       </c>
       <c r="M68" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N68" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O68" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N68" s="4"/>
     </row>
     <row r="69" ht="57.75">
       <c r="A69" s="4">
         <v>68</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C69" s="4">
         <v>2</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
+      <c r="K69" s="4" t="s">
+        <v>323</v>
+      </c>
       <c r="L69" s="4" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="M69" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="N69" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O69" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N69" s="4"/>
     </row>
     <row r="70" ht="30.75">
       <c r="A70" s="4">
         <v>69</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C70" s="4">
         <v>3</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
@@ -4874,30 +4703,29 @@
       <c r="J70" s="4"/>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
-      <c r="M70" s="4"/>
-      <c r="N70" s="4" t="s">
+      <c r="M70" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O70" s="4"/>
+      <c r="N70" s="4"/>
     </row>
     <row r="71" ht="44.25">
       <c r="A71" s="4">
         <v>70</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C71" s="4">
         <v>4</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G71" s="4">
         <v>0</v>
@@ -4906,128 +4734,119 @@
         <v>0</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J71" s="4"/>
       <c r="K71" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L71" s="4" t="s">
         <v>43</v>
       </c>
       <c r="M71" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N71" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O71" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N71" s="4"/>
     </row>
     <row r="72" ht="44.25">
       <c r="A72" s="4">
         <v>71</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C72" s="4">
         <v>5</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="G72" s="5">
         <v>46308</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>338</v>
+        <v>43</v>
       </c>
       <c r="M72" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N72" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O72" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N72" s="4"/>
     </row>
     <row r="73" ht="44.25">
       <c r="A73" s="4">
         <v>72</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C73" s="4">
         <v>6</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="G73" s="5">
         <v>46308</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>338</v>
+        <v>43</v>
       </c>
       <c r="M73" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N73" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O73" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N73" s="4"/>
     </row>
     <row r="74" ht="30.75">
       <c r="A74" s="4">
         <v>73</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C74" s="4">
         <v>7</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F74" s="4"/>
       <c r="G74" s="4"/>
@@ -5036,162 +4855,152 @@
       <c r="J74" s="4"/>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
-      <c r="N74" s="4" t="s">
+      <c r="M74" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O74" s="4"/>
+      <c r="N74" s="4"/>
     </row>
     <row r="75" ht="57.75">
       <c r="A75" s="4">
         <v>74</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C75" s="4">
         <v>8</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="M75" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="N75" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O75" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N75" s="4"/>
     </row>
     <row r="76" ht="57.75">
       <c r="A76" s="4">
         <v>75</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C76" s="4">
         <v>9</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="F76" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="K76" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="G76" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="H76" s="4" t="s">
+      <c r="L76" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="I76" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="J76" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="K76" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="L76" s="4" t="s">
-        <v>352</v>
-      </c>
       <c r="M76" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="N76" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O76" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N76" s="4"/>
     </row>
     <row r="77" ht="71.25">
       <c r="A77" s="4">
         <v>76</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C77" s="4">
         <v>10</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="G77" s="4">
         <v>0</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="M77" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="N77" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O77" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N77" s="4"/>
     </row>
     <row r="78" ht="30.75">
       <c r="A78" s="4">
         <v>77</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C78" s="4">
         <v>11</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F78" s="4"/>
       <c r="G78" s="4"/>
@@ -5200,30 +5009,29 @@
       <c r="J78" s="4"/>
       <c r="K78" s="4"/>
       <c r="L78" s="4"/>
-      <c r="M78" s="4"/>
-      <c r="N78" s="4" t="s">
+      <c r="M78" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O78" s="4"/>
+      <c r="N78" s="4"/>
     </row>
     <row r="79" ht="44.25">
       <c r="A79" s="4">
         <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C79" s="4">
         <v>12</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G79" s="4">
         <v>0</v>
@@ -5232,38 +5040,35 @@
         <v>0</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J79" s="4"/>
       <c r="K79" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L79" s="4" t="s">
         <v>43</v>
       </c>
       <c r="M79" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N79" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O79" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N79" s="4"/>
     </row>
     <row r="80" ht="30.75">
       <c r="A80" s="4">
         <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C80" s="4">
         <v>13</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F80" s="4"/>
       <c r="G80" s="4"/>
@@ -5272,27 +5077,26 @@
       <c r="J80" s="4"/>
       <c r="K80" s="4"/>
       <c r="L80" s="4"/>
-      <c r="M80" s="4"/>
-      <c r="N80" s="4" t="s">
+      <c r="M80" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O80" s="4"/>
+      <c r="N80" s="4"/>
     </row>
     <row r="81" ht="30.75">
       <c r="A81" s="4">
         <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C81" s="4">
         <v>14</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F81" s="4"/>
       <c r="G81" s="4"/>
@@ -5301,55 +5105,51 @@
       <c r="J81" s="4"/>
       <c r="K81" s="4"/>
       <c r="L81" s="4"/>
-      <c r="M81" s="4"/>
-      <c r="N81" s="4" t="s">
+      <c r="M81" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O81" s="4"/>
+      <c r="N81" s="4"/>
     </row>
     <row r="82" ht="165">
       <c r="A82" s="4">
         <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C82" s="4">
         <v>15</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="G82" s="4">
         <v>0</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="J82" s="4"/>
       <c r="K82" s="4" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="M82" s="4" t="s">
-        <v>370</v>
+        <v>3</v>
       </c>
       <c r="N82" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O82" s="4" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
     </row>
     <row r="83" ht="57.75">
@@ -5357,173 +5157,161 @@
         <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C83" s="4">
         <v>16</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="G83" s="4">
         <v>0</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J83" s="4"/>
       <c r="K83" s="4" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="M83" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="N83" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N83" s="4"/>
     </row>
     <row r="84" ht="57.75">
       <c r="A84" s="4">
         <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C84" s="4">
         <v>17</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="G84" s="4">
         <v>0</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J84" s="4"/>
       <c r="K84" s="4" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="M84" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="N84" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O84" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N84" s="4"/>
     </row>
     <row r="85" ht="57.75">
       <c r="A85" s="4">
         <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C85" s="4">
         <v>18</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="G85" s="4">
         <v>0</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J85" s="4"/>
       <c r="K85" s="4" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="M85" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="N85" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O85" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N85" s="4"/>
     </row>
     <row r="86" ht="71.25">
       <c r="A86" s="4">
         <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C86" s="4">
         <v>19</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="G86" s="5">
         <v>46308</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J86" s="4"/>
       <c r="K86" s="4" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="M86" s="4" t="s">
-        <v>388</v>
+        <v>3</v>
       </c>
       <c r="N86" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O86" s="4" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
     </row>
     <row r="87" ht="30.75">
@@ -5531,16 +5319,16 @@
         <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C87" s="4">
         <v>20</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F87" s="4"/>
       <c r="G87" s="4"/>
@@ -5549,27 +5337,26 @@
       <c r="J87" s="4"/>
       <c r="K87" s="4"/>
       <c r="L87" s="4"/>
-      <c r="M87" s="4"/>
-      <c r="N87" s="4" t="s">
+      <c r="M87" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O87" s="4"/>
+      <c r="N87" s="4"/>
     </row>
     <row r="88" ht="30.75">
       <c r="A88" s="4">
         <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C88" s="4">
         <v>21</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F88" s="4"/>
       <c r="G88" s="4"/>
@@ -5578,30 +5365,29 @@
       <c r="J88" s="4"/>
       <c r="K88" s="4"/>
       <c r="L88" s="4"/>
-      <c r="M88" s="4"/>
-      <c r="N88" s="4" t="s">
+      <c r="M88" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O88" s="4"/>
+      <c r="N88" s="4"/>
     </row>
     <row r="89" ht="71.25">
       <c r="A89" s="4">
         <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C89" s="4">
         <v>22</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="G89" s="4">
         <v>0</v>
@@ -5610,40 +5396,37 @@
         <v>0</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>140</v>
+        <v>386</v>
       </c>
       <c r="L89" s="4" t="s">
-        <v>140</v>
+        <v>387</v>
       </c>
       <c r="M89" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="N89" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N89" s="4"/>
     </row>
     <row r="90" ht="30.75">
       <c r="A90" s="4">
         <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C90" s="4">
         <v>23</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F90" s="4"/>
       <c r="G90" s="4"/>
@@ -5652,55 +5435,51 @@
       <c r="J90" s="4"/>
       <c r="K90" s="4"/>
       <c r="L90" s="4"/>
-      <c r="M90" s="4"/>
-      <c r="N90" s="4" t="s">
+      <c r="M90" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O90" s="4"/>
+      <c r="N90" s="4"/>
     </row>
     <row r="91" ht="57.75">
       <c r="A91" s="4">
         <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C91" s="4">
         <v>24</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J91" s="4"/>
       <c r="K91" s="4" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="M91" s="4" t="s">
-        <v>402</v>
+        <v>3</v>
       </c>
       <c r="N91" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="4" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
     </row>
     <row r="92" ht="57.75">
@@ -5708,87 +5487,81 @@
         <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C92" s="4">
         <v>25</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J92" s="4"/>
       <c r="K92" s="4" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="M92" s="4" t="s">
-        <v>407</v>
-      </c>
-      <c r="N92" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O92" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N92" s="4"/>
     </row>
     <row r="93" ht="57.75">
       <c r="A93" s="4">
         <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C93" s="4">
         <v>26</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J93" s="4"/>
       <c r="K93" s="4" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="M93" s="4" t="s">
-        <v>413</v>
+        <v>3</v>
       </c>
       <c r="N93" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O93" s="4" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
     </row>
     <row r="94" ht="125.25">
@@ -5796,61 +5569,58 @@
         <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C94" s="4">
         <v>27</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="G94" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="I94" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="K94" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="H94" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="I94" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="J94" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="K94" s="4" t="s">
-        <v>419</v>
-      </c>
       <c r="L94" s="4" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="M94" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="N94" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O94" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N94" s="4"/>
     </row>
     <row r="95" ht="30.75">
       <c r="A95" s="4">
         <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C95" s="4">
         <v>28</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F95" s="4"/>
       <c r="G95" s="4"/>
@@ -5859,27 +5629,26 @@
       <c r="J95" s="4"/>
       <c r="K95" s="4"/>
       <c r="L95" s="4"/>
-      <c r="M95" s="4"/>
-      <c r="N95" s="4" t="s">
+      <c r="M95" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O95" s="4"/>
+      <c r="N95" s="4"/>
     </row>
     <row r="96" ht="30.75">
       <c r="A96" s="4">
         <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C96" s="4">
         <v>29</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F96" s="4"/>
       <c r="G96" s="4"/>
@@ -5888,27 +5657,26 @@
       <c r="J96" s="4"/>
       <c r="K96" s="4"/>
       <c r="L96" s="4"/>
-      <c r="M96" s="4"/>
-      <c r="N96" s="4" t="s">
+      <c r="M96" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O96" s="4"/>
+      <c r="N96" s="4"/>
     </row>
     <row r="97" ht="30.75">
       <c r="A97" s="4">
         <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C97" s="4">
         <v>30</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F97" s="4"/>
       <c r="G97" s="4"/>
@@ -5917,30 +5685,29 @@
       <c r="J97" s="4"/>
       <c r="K97" s="4"/>
       <c r="L97" s="4"/>
-      <c r="M97" s="4"/>
-      <c r="N97" s="4" t="s">
+      <c r="M97" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O97" s="4"/>
+      <c r="N97" s="4"/>
     </row>
     <row r="98" ht="57.75">
       <c r="A98" s="4">
         <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C98" s="4">
         <v>31</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G98" s="4">
         <v>0</v>
@@ -5949,38 +5716,35 @@
         <v>0</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J98" s="4"/>
       <c r="K98" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L98" s="4" t="s">
         <v>43</v>
       </c>
       <c r="M98" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N98" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O98" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N98" s="4"/>
     </row>
     <row r="99" ht="30.75">
       <c r="A99" s="4">
         <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C99" s="4">
         <v>32</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F99" s="4"/>
       <c r="G99" s="4"/>
@@ -5989,53 +5753,51 @@
       <c r="J99" s="4"/>
       <c r="K99" s="4"/>
       <c r="L99" s="4"/>
-      <c r="M99" s="4"/>
-      <c r="N99" s="4" t="s">
+      <c r="M99" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O99" s="4"/>
+      <c r="N99" s="4"/>
     </row>
     <row r="100" ht="151.5">
       <c r="A100" s="4">
         <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C100" s="4">
         <v>33</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="J100" s="4"/>
-      <c r="K100" s="4"/>
+      <c r="K100" s="4" t="s">
+        <v>420</v>
+      </c>
       <c r="L100" s="4" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="M100" s="4" t="s">
-        <v>429</v>
+        <v>3</v>
       </c>
       <c r="N100" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="4" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
     </row>
     <row r="101" ht="30.75">
@@ -6043,16 +5805,16 @@
         <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C101" s="4">
         <v>34</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F101" s="4"/>
       <c r="G101" s="4"/>
@@ -6061,55 +5823,51 @@
       <c r="J101" s="4"/>
       <c r="K101" s="4"/>
       <c r="L101" s="4"/>
-      <c r="M101" s="4"/>
-      <c r="N101" s="4" t="s">
+      <c r="M101" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O101" s="4"/>
+      <c r="N101" s="4"/>
     </row>
     <row r="102" ht="71.25">
       <c r="A102" s="4">
         <v>101</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="C102" s="4">
         <v>35</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J102" s="4"/>
       <c r="K102" s="4" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="M102" s="4" t="s">
-        <v>435</v>
+        <v>3</v>
       </c>
       <c r="N102" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="4" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
     </row>
     <row r="103" ht="57.75">
@@ -6117,87 +5875,83 @@
         <v>102</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C103" s="4">
         <v>1</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="M103" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="N103" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O103" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N103" s="4"/>
     </row>
     <row r="104" ht="178.5">
       <c r="A104" s="4">
         <v>103</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C104" s="4">
         <v>2</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J104" s="4"/>
-      <c r="K104" s="4"/>
+      <c r="K104" s="4" t="s">
+        <v>437</v>
+      </c>
       <c r="L104" s="4" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="M104" s="4" t="s">
-        <v>446</v>
+        <v>3</v>
       </c>
       <c r="N104" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O104" s="4" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
     </row>
     <row r="105" ht="111.75">
@@ -6205,42 +5959,41 @@
         <v>104</v>
       </c>
       <c r="B105" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C105" s="4">
+        <v>3</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="E105" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="F105" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="G105" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="I105" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="J105" s="4"/>
+      <c r="K105" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="C105" s="4">
-        <v>3</v>
-      </c>
-      <c r="D105" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="E105" s="4" t="s">
-        <v>449</v>
-      </c>
-      <c r="F105" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="G105" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="H105" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="I105" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="J105" s="4"/>
-      <c r="K105" s="4"/>
       <c r="L105" s="4" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="M105" s="4" t="s">
-        <v>446</v>
+        <v>3</v>
       </c>
       <c r="N105" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O105" s="4" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
     </row>
     <row r="106" ht="30.75">
@@ -6248,16 +6001,16 @@
         <v>105</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C106" s="4">
         <v>4</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F106" s="4"/>
       <c r="G106" s="4"/>
@@ -6266,27 +6019,26 @@
       <c r="J106" s="4"/>
       <c r="K106" s="4"/>
       <c r="L106" s="4"/>
-      <c r="M106" s="4"/>
-      <c r="N106" s="4" t="s">
+      <c r="M106" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O106" s="4"/>
+      <c r="N106" s="4"/>
     </row>
     <row r="107" ht="30.75">
       <c r="A107" s="4">
         <v>106</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C107" s="4">
         <v>5</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F107" s="4"/>
       <c r="G107" s="4"/>
@@ -6295,30 +6047,29 @@
       <c r="J107" s="4"/>
       <c r="K107" s="4"/>
       <c r="L107" s="4"/>
-      <c r="M107" s="4"/>
-      <c r="N107" s="4" t="s">
+      <c r="M107" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O107" s="4"/>
+      <c r="N107" s="4"/>
     </row>
     <row r="108" ht="57.75">
       <c r="A108" s="4">
         <v>107</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C108" s="4">
         <v>6</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G108" s="4">
         <v>0</v>
@@ -6327,41 +6078,38 @@
         <v>0</v>
       </c>
       <c r="I108" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J108" s="4"/>
       <c r="K108" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L108" s="4" t="s">
         <v>43</v>
       </c>
       <c r="M108" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N108" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O108" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N108" s="4"/>
     </row>
     <row r="109" ht="57.75">
       <c r="A109" s="4">
         <v>108</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C109" s="4">
         <v>7</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G109" s="4">
         <v>0</v>
@@ -6370,435 +6118,420 @@
         <v>0</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J109" s="4"/>
       <c r="K109" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L109" s="4" t="s">
         <v>43</v>
       </c>
       <c r="M109" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N109" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O109" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N109" s="4"/>
     </row>
     <row r="110" ht="71.25">
       <c r="A110" s="4">
         <v>109</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C110" s="4">
         <v>8</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="I110" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J110" s="4"/>
-      <c r="K110" s="4"/>
+      <c r="K110" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="L110" s="4" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="M110" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="N110" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O110" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N110" s="4"/>
     </row>
     <row r="111" ht="57.75">
       <c r="A111" s="4">
         <v>110</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C111" s="4">
         <v>9</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="F111" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="G111" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="I111" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J111" s="4"/>
+      <c r="K111" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="L111" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="G111" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="H111" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="I111" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="J111" s="4"/>
-      <c r="K111" s="4"/>
-      <c r="L111" s="4" t="s">
-        <v>466</v>
-      </c>
       <c r="M111" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="N111" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O111" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N111" s="4"/>
     </row>
     <row r="112" ht="71.25">
       <c r="A112" s="4">
         <v>111</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C112" s="4">
         <v>10</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J112" s="4"/>
-      <c r="K112" s="4"/>
+      <c r="K112" s="4" t="s">
+        <v>454</v>
+      </c>
       <c r="L112" s="4" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="M112" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="N112" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O112" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N112" s="4"/>
     </row>
     <row r="113" ht="57.75">
       <c r="A113" s="4">
         <v>112</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C113" s="4">
         <v>11</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="F113" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="G113" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="I113" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="J113" s="4"/>
+      <c r="K113" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="L113" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="G113" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="H113" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="I113" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="J113" s="4"/>
-      <c r="K113" s="4"/>
-      <c r="L113" s="4" t="s">
-        <v>466</v>
-      </c>
       <c r="M113" s="4" t="s">
-        <v>467</v>
-      </c>
-      <c r="N113" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O113" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N113" s="4"/>
     </row>
     <row r="114" ht="71.25">
       <c r="A114" s="4">
         <v>113</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C114" s="4">
         <v>12</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="I114" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J114" s="4"/>
-      <c r="K114" s="4"/>
+      <c r="K114" s="4" t="s">
+        <v>469</v>
+      </c>
       <c r="L114" s="4" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="M114" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="N114" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O114" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N114" s="4"/>
     </row>
     <row r="115" ht="44.25">
       <c r="A115" s="4">
         <v>114</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C115" s="4">
         <v>13</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="F115" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="G115" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="I115" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="J115" s="4"/>
+      <c r="K115" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="L115" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="G115" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="I115" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="J115" s="4"/>
-      <c r="K115" s="4"/>
-      <c r="L115" s="4" t="s">
-        <v>481</v>
-      </c>
       <c r="M115" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="N115" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O115" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N115" s="4"/>
     </row>
     <row r="116" ht="57.75">
       <c r="A116" s="4">
         <v>115</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C116" s="4">
         <v>14</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="I116" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J116" s="4"/>
       <c r="K116" s="4" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="M116" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="N116" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O116" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N116" s="4"/>
     </row>
     <row r="117" ht="57.75">
       <c r="A117" s="4">
         <v>116</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C117" s="4">
         <v>15</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I117" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J117" s="4"/>
-      <c r="K117" s="4"/>
+      <c r="K117" s="4" t="s">
+        <v>482</v>
+      </c>
       <c r="L117" s="4" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="M117" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="N117" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O117" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N117" s="4"/>
     </row>
     <row r="118" ht="57.75">
       <c r="A118" s="4">
         <v>117</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C118" s="4">
         <v>16</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="I118" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J118" s="4"/>
-      <c r="K118" s="4"/>
+      <c r="K118" s="4" t="s">
+        <v>486</v>
+      </c>
       <c r="L118" s="4" t="s">
-        <v>494</v>
+        <v>487</v>
       </c>
       <c r="M118" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="N118" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O118" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N118" s="4"/>
     </row>
     <row r="119" ht="57.75">
       <c r="A119" s="4">
         <v>118</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C119" s="4">
         <v>17</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="I119" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J119" s="4"/>
-      <c r="K119" s="4"/>
+      <c r="K119" s="4" t="s">
+        <v>490</v>
+      </c>
       <c r="L119" s="4" t="s">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="M119" s="4" t="s">
-        <v>499</v>
+        <v>3</v>
       </c>
       <c r="N119" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O119" s="4" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
     </row>
     <row r="120" ht="71.25">
@@ -6806,106 +6539,100 @@
         <v>119</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C120" s="4">
         <v>18</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H120" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I120" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>504</v>
+        <v>331</v>
       </c>
       <c r="L120" s="4" t="s">
-        <v>338</v>
+        <v>43</v>
       </c>
       <c r="M120" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N120" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O120" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N120" s="4"/>
     </row>
     <row r="121" ht="71.25">
       <c r="A121" s="4">
         <v>120</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C121" s="4">
         <v>19</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="I121" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>507</v>
+        <v>331</v>
       </c>
       <c r="L121" s="4" t="s">
-        <v>338</v>
+        <v>43</v>
       </c>
       <c r="M121" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="N121" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O121" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N121" s="4"/>
     </row>
     <row r="122" ht="30.75">
       <c r="A122" s="4">
         <v>121</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C122" s="4">
         <v>20</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F122" s="4"/>
       <c r="G122" s="4"/>
@@ -6914,27 +6641,26 @@
       <c r="J122" s="4"/>
       <c r="K122" s="4"/>
       <c r="L122" s="4"/>
-      <c r="M122" s="4"/>
-      <c r="N122" s="4" t="s">
+      <c r="M122" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O122" s="4"/>
+      <c r="N122" s="4"/>
     </row>
     <row r="123" ht="30.75">
       <c r="A123" s="4">
         <v>122</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C123" s="4">
         <v>21</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F123" s="4"/>
       <c r="G123" s="4"/>
@@ -6943,47 +6669,45 @@
       <c r="J123" s="4"/>
       <c r="K123" s="4"/>
       <c r="L123" s="4"/>
-      <c r="M123" s="4"/>
-      <c r="N123" s="4" t="s">
+      <c r="M123" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O123" s="4"/>
+      <c r="N123" s="4"/>
     </row>
     <row r="124" ht="272.25">
       <c r="A124" s="4">
         <v>123</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C124" s="4">
         <v>22</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="F124" s="4"/>
       <c r="G124" s="4"/>
       <c r="H124" s="4"/>
       <c r="I124" s="4" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="J124" s="4"/>
-      <c r="K124" s="4"/>
+      <c r="K124" s="4" t="s">
+        <v>505</v>
+      </c>
       <c r="L124" s="4" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="M124" s="4" t="s">
-        <v>514</v>
+        <v>3</v>
       </c>
       <c r="N124" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O124" s="4" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
     </row>
     <row r="125" ht="57.75">
@@ -6991,46 +6715,43 @@
         <v>124</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C125" s="4">
         <v>23</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="I125" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="L125" s="4" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="M125" s="4" t="s">
-        <v>521</v>
+        <v>3</v>
       </c>
       <c r="N125" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O125" s="4" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
     </row>
     <row r="126" ht="57.75">
@@ -7038,56 +6759,55 @@
         <v>125</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C126" s="4">
         <v>24</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="I126" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J126" s="4"/>
       <c r="K126" s="4"/>
       <c r="L126" s="4"/>
-      <c r="M126" s="4"/>
-      <c r="N126" s="4" t="s">
+      <c r="M126" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="O126" s="4"/>
+      <c r="N126" s="4"/>
     </row>
     <row r="127" ht="44.25">
       <c r="A127" s="4">
         <v>126</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C127" s="4">
         <v>25</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="G127" s="4">
         <v>0</v>
@@ -7096,62 +6816,60 @@
         <v>0</v>
       </c>
       <c r="I127" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J127" s="4"/>
-      <c r="K127" s="4"/>
+      <c r="K127" s="4" t="s">
+        <v>518</v>
+      </c>
       <c r="L127" s="4" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="M127" s="4" t="s">
-        <v>527</v>
-      </c>
-      <c r="N127" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O127" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N127" s="4"/>
     </row>
     <row r="128" ht="125.25">
       <c r="A128" s="4">
         <v>127</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C128" s="4">
         <v>26</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="I128" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J128" s="4"/>
-      <c r="K128" s="4"/>
+      <c r="K128" s="4" t="s">
+        <v>524</v>
+      </c>
       <c r="L128" s="4" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="M128" s="4" t="s">
-        <v>533</v>
+        <v>3</v>
       </c>
       <c r="N128" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O128" s="4" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
     </row>
     <row r="129" ht="30.75">
@@ -7159,16 +6877,16 @@
         <v>128</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C129" s="4">
         <v>27</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F129" s="4"/>
       <c r="G129" s="4"/>
@@ -7177,30 +6895,29 @@
       <c r="J129" s="4"/>
       <c r="K129" s="4"/>
       <c r="L129" s="4"/>
-      <c r="M129" s="4"/>
-      <c r="N129" s="4" t="s">
+      <c r="M129" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O129" s="4"/>
+      <c r="N129" s="4"/>
     </row>
     <row r="130" ht="71.25">
       <c r="A130" s="4">
         <v>129</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C130" s="4">
         <v>28</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="G130" s="4">
         <v>0</v>
@@ -7209,43 +6926,40 @@
         <v>0</v>
       </c>
       <c r="I130" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J130" s="4" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="L130" s="4" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="M130" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="N130" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O130" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N130" s="4"/>
     </row>
     <row r="131" ht="71.25">
       <c r="A131" s="4">
         <v>130</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C131" s="4">
         <v>29</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="G131" s="4">
         <v>0</v>
@@ -7254,40 +6968,37 @@
         <v>0</v>
       </c>
       <c r="I131" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J131" s="4" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="K131" s="4" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="L131" s="4" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="M131" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="N131" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O131" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N131" s="4"/>
     </row>
     <row r="132" ht="30.75">
       <c r="A132" s="4">
         <v>131</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C132" s="4">
         <v>30</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F132" s="4"/>
       <c r="G132" s="4"/>
@@ -7296,27 +7007,26 @@
       <c r="J132" s="4"/>
       <c r="K132" s="4"/>
       <c r="L132" s="4"/>
-      <c r="M132" s="4"/>
-      <c r="N132" s="4" t="s">
+      <c r="M132" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O132" s="4"/>
+      <c r="N132" s="4"/>
     </row>
     <row r="133" ht="30.75">
       <c r="A133" s="4">
         <v>132</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C133" s="4">
         <v>31</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F133" s="4"/>
       <c r="G133" s="4"/>
@@ -7325,98 +7035,93 @@
       <c r="J133" s="4"/>
       <c r="K133" s="4"/>
       <c r="L133" s="4"/>
-      <c r="M133" s="4"/>
-      <c r="N133" s="4" t="s">
+      <c r="M133" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O133" s="4"/>
+      <c r="N133" s="4"/>
     </row>
     <row r="134" ht="84.75">
       <c r="A134" s="4">
         <v>133</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C134" s="4">
         <v>32</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="H134" s="4" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="J134" s="4" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="L134" s="4" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="M134" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="N134" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O134" s="4"/>
+        <v>3</v>
+      </c>
+      <c r="N134" s="4"/>
     </row>
     <row r="135" ht="125.25">
       <c r="A135" s="4">
         <v>134</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C135" s="4">
         <v>33</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="H135" s="4" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="I135" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J135" s="4"/>
-      <c r="K135" s="4"/>
+      <c r="K135" s="4" t="s">
+        <v>548</v>
+      </c>
       <c r="L135" s="4" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="M135" s="4" t="s">
-        <v>557</v>
+        <v>3</v>
       </c>
       <c r="N135" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O135" s="4" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
     </row>
     <row r="136" ht="84.75">
@@ -7424,65 +7129,64 @@
         <v>135</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="C136" s="4">
         <v>34</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G136" s="4"/>
       <c r="H136" s="4"/>
       <c r="I136" s="4" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="J136" s="4"/>
-      <c r="K136" s="4"/>
+      <c r="K136" s="4" t="s">
+        <v>42</v>
+      </c>
       <c r="L136" s="4" t="s">
         <v>43</v>
       </c>
       <c r="M136" s="4" t="s">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="N136" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="O136" s="4" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O136"/>
-  <conditionalFormatting sqref="N2:N136">
+  <autoFilter ref="A1:N136"/>
+  <conditionalFormatting sqref="M2:M136">
     <cfRule type="beginsWith" dxfId="0" priority="1" operator="beginsWith" text="OK">
-      <formula>LEFT(N2,LEN("OK"))="OK"</formula>
+      <formula>LEFT(M2,LEN("OK"))="OK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N136">
+  <conditionalFormatting sqref="M2:M136">
     <cfRule type="beginsWith" dxfId="1" priority="2" operator="beginsWith" text="CHECK">
-      <formula>LEFT(N2,LEN("CHECK"))="CHECK"</formula>
+      <formula>LEFT(M2,LEN("CHECK"))="CHECK"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N136">
+  <conditionalFormatting sqref="M2:M136">
     <cfRule type="beginsWith" dxfId="1" priority="3" operator="beginsWith" text="LABEL ONLY">
-      <formula>LEFT(N2,LEN("LABEL ONLY"))="LABEL ONLY"</formula>
+      <formula>LEFT(M2,LEN("LABEL ONLY"))="LABEL ONLY"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N136">
+  <conditionalFormatting sqref="M2:M136">
     <cfRule type="beginsWith" dxfId="2" priority="4" operator="beginsWith" text="MISMATCH">
-      <formula>LEFT(N2,LEN("MISMATCH"))="MISMATCH"</formula>
+      <formula>LEFT(M2,LEN("MISMATCH"))="MISMATCH"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N136">
+  <conditionalFormatting sqref="M2:M136">
     <cfRule type="beginsWith" dxfId="2" priority="5" operator="beginsWith" text="NOT WIRED">
-      <formula>LEFT(N2,LEN("NOT WIRED"))="NOT WIRED"</formula>
+      <formula>LEFT(M2,LEN("NOT WIRED"))="NOT WIRED"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>

--- a/documents/STI2004-pinout-check.xlsx
+++ b/documents/STI2004-pinout-check.xlsx
@@ -415,7 +415,7 @@
     <t>K_LINE</t>
   </si>
   <si>
-    <t>JP4.2_2; M10.LIN_V4; P8.Pin_1_1</t>
+    <t>JP4.2; M10.LIN_V4; P8.1_1</t>
   </si>
   <si>
     <t>D21</t>
@@ -484,7 +484,7 @@
     <t>FP_STATUS</t>
   </si>
   <si>
-    <t>JP7.1_1; P12.Pin_1_1</t>
+    <t>JP7.1; P12.1_1</t>
   </si>
   <si>
     <t>D29</t>
@@ -499,7 +499,7 @@
     <t>DLC6_D29</t>
   </si>
   <si>
-    <t>JP4.1_1; P13.Pin_1_1</t>
+    <t>JP4.1; P13.1_1</t>
   </si>
   <si>
     <t>Red/white wire to data link connector pin 6 (WI-112); function not in the I/O table. Leave unconnected.</t>
@@ -715,7 +715,7 @@
     <t>APS_PS_5V</t>
   </si>
   <si>
-    <t>JP12.1_1; M8.5VP_V4</t>
+    <t>JP12.1; M8.5VP_V4</t>
   </si>
   <si>
     <t>C16</t>
@@ -730,7 +730,7 @@
     <t>+5VAS</t>
   </si>
   <si>
-    <t>F7 -&gt; AUX_5V -&gt; J3.Pin_3_3; JP12.2_2; M14.5VP_V4</t>
+    <t>F7 -&gt; AUX_5V -&gt; J3.Pin_3_3; JP12.2; M14.5VP_V4</t>
   </si>
   <si>
     <t>Feeds throttle TPS; MAP; TGV sensors</t>
@@ -931,7 +931,7 @@
     <t>GND_SENSOR</t>
   </si>
   <si>
-    <t>J3.Pin_4_4; JP8.1_1; JP9.1_1</t>
+    <t>J3.Pin_4_4; JP8.1; JP9.1</t>
   </si>
   <si>
     <t>C32</t>
@@ -1330,7 +1330,7 @@
     <t>WBO_HEATER</t>
   </si>
   <si>
-    <t>M3.LSU_H+_E5; P5.Pin_1_1</t>
+    <t>M3.LSU_H+_E5; P5.1_1</t>
   </si>
   <si>
     <t>Joined with A3 in the harness to A/F heater B18 pin 1 (WI-113); heater +12 V comes from the main relay</t>
@@ -1426,7 +1426,7 @@
     <t>EVAP_A12</t>
   </si>
   <si>
-    <t>JP5.2_2</t>
+    <t>JP5.2</t>
   </si>
   <si>
     <t>A13</t>
@@ -1438,7 +1438,7 @@
     <t>EVAP_A13</t>
   </si>
   <si>
-    <t>JP6.2_2</t>
+    <t>JP6.2</t>
   </si>
   <si>
     <t>A14</t>
@@ -1534,7 +1534,7 @@
     <t>CHARGE_A22</t>
   </si>
   <si>
-    <t>P11.Pin_1_1</t>
+    <t>P11.1_1</t>
   </si>
   <si>
     <t>Blue (L) wire to REF. TO CHG-01 (charging system); function not in the I/O table, likely alternator signal. Not spare: do not ground or drive it. Measure on the car.</t>
@@ -1573,7 +1573,7 @@
     <t>WBO_IP_J1</t>
   </si>
   <si>
-    <t>JP3.2_2</t>
+    <t>JP3.2</t>
   </si>
   <si>
     <t>A26</t>
@@ -1591,7 +1591,7 @@
     <t>WBO_VM_J1</t>
   </si>
   <si>
-    <t>JP2.2_2</t>
+    <t>JP2.2</t>
   </si>
   <si>
     <t>Denso 4-wire A/F sensor (plug B18 pin 4; WI-113); not a Bosch LSU</t>
@@ -1663,7 +1663,7 @@
     <t>WBO_UN_J1</t>
   </si>
   <si>
-    <t>JP1.2_2</t>
+    <t>JP1.2</t>
   </si>
   <si>
     <t>Denso 4-wire A/F sensor (plug B18 pin 3; WI-113); not a Bosch LSU</t>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="N20" s="4"/>
     </row>
-    <row r="21" ht="71.25">
+    <row r="21" ht="57.75">
       <c r="A21" s="4">
         <v>20</v>
       </c>

--- a/documents/STI2004-pinout-check.xlsx
+++ b/documents/STI2004-pinout-check.xlsx
@@ -385,7 +385,7 @@
     <t>OUT_MAIN_RELAY</t>
   </si>
   <si>
-    <t>Q5.D_2</t>
+    <t>U12.D_8</t>
   </si>
   <si>
     <t>Not in the I/O table; wiring diagram shows D17 to the main relay coil</t>
@@ -538,7 +538,7 @@
     <t>OUT_INJ4</t>
   </si>
   <si>
-    <t>Q4.D_2</t>
+    <t>U11.D_6</t>
   </si>
   <si>
     <t>C4</t>
@@ -550,7 +550,7 @@
     <t>OUT_INJ3</t>
   </si>
   <si>
-    <t>Q3.D_2</t>
+    <t>U11.D_8</t>
   </si>
   <si>
     <t>C5</t>
@@ -562,7 +562,7 @@
     <t>OUT_INJ2</t>
   </si>
   <si>
-    <t>Q2.D_2</t>
+    <t>U10.D_6</t>
   </si>
   <si>
     <t>C6</t>
@@ -574,7 +574,7 @@
     <t>OUT_INJ1</t>
   </si>
   <si>
-    <t>Q1.D_2</t>
+    <t>U10.D_8</t>
   </si>
   <si>
     <t>C7</t>
@@ -883,7 +883,7 @@
     <t>IN_TUMBLE_SENSOR_RH</t>
   </si>
   <si>
-    <t>M1.IN_MAP3_S19</t>
+    <t>M1.IN_RES2_S14</t>
   </si>
   <si>
     <t>C28</t>
@@ -988,7 +988,7 @@
     <t>OUT_O2_HEATER_REAR</t>
   </si>
   <si>
-    <t>Q14.D_2</t>
+    <t>Q16.D_2</t>
   </si>
   <si>
     <t>B3</t>
@@ -1096,7 +1096,7 @@
     <t>WI-107</t>
   </si>
   <si>
-    <t>Net-(F1-Pad1)</t>
+    <t>Vehicle connector/IGN4_COIL</t>
   </si>
   <si>
     <t>F1 -&gt; OUT_IGN4 -&gt; M1.IGN4_W8</t>
@@ -1111,7 +1111,7 @@
     <t>Ignition control #3</t>
   </si>
   <si>
-    <t>Net-(F2-Pad1)</t>
+    <t>Vehicle connector/IGN3_COIL</t>
   </si>
   <si>
     <t>F2 -&gt; OUT_IGN3 -&gt; M1.IGN3_W9</t>
@@ -1123,7 +1123,7 @@
     <t>Ignition control #2</t>
   </si>
   <si>
-    <t>Net-(F3-Pad1)</t>
+    <t>Vehicle connector/IGN2_COIL</t>
   </si>
   <si>
     <t>F3 -&gt; OUT_IGN2 -&gt; M1.IGN2_W10</t>
@@ -1135,7 +1135,7 @@
     <t>Ignition control #1</t>
   </si>
   <si>
-    <t>Net-(F4-Pad1)</t>
+    <t>Vehicle connector/IGN1_COIL</t>
   </si>
   <si>
     <t>F4 -&gt; OUT_IGN1 -&gt; M1.IGN1_W11</t>
@@ -1198,7 +1198,7 @@
     <t>OUT_FAN_RELAY_2</t>
   </si>
   <si>
-    <t>Q7.D_2</t>
+    <t>U13.D_8</t>
   </si>
   <si>
     <t>Models with A/C only</t>
@@ -1213,7 +1213,7 @@
     <t>OUT_FAN_RELAY_1</t>
   </si>
   <si>
-    <t>Q6.D_2</t>
+    <t>U12.D_6</t>
   </si>
   <si>
     <t>B26</t>
@@ -1279,7 +1279,7 @@
     <t>OUT_AC_RELAY</t>
   </si>
   <si>
-    <t>Q15.D_2</t>
+    <t>U18.D_8</t>
   </si>
   <si>
     <t>I/O table (EN(STi)-19) prints B133 33; wiring diagram shows B33 to the auto A/C module</t>
@@ -1297,7 +1297,7 @@
     <t>OUT_ELECTRONIC_THROTTE_RELAY</t>
   </si>
   <si>
-    <t>Q8.D_2</t>
+    <t>U13.D_6</t>
   </si>
   <si>
     <t>ON whenever the ignition is ON</t>
@@ -1450,7 +1450,7 @@
     <t>OUT_PURGE_CONTROL</t>
   </si>
   <si>
-    <t>Q12.D_2</t>
+    <t>U15.D_6</t>
   </si>
   <si>
     <t>A15</t>
@@ -1465,7 +1465,7 @@
     <t>OUT_CRUISE_MAIN_LIGHT</t>
   </si>
   <si>
-    <t>Q17.D_2</t>
+    <t>U16.D_8</t>
   </si>
   <si>
     <t>A16</t>
@@ -1477,7 +1477,7 @@
     <t>OUT_CRUISE_SET_LIGHT</t>
   </si>
   <si>
-    <t>Q18.D_2</t>
+    <t>U16.D_6</t>
   </si>
   <si>
     <t>A17</t>
@@ -1489,7 +1489,7 @@
     <t>OUT_MIL</t>
   </si>
   <si>
-    <t>Q13.D_2</t>
+    <t>U17.D_8</t>
   </si>
   <si>
     <t>ON &lt;=1 / OFF 10-14</t>
@@ -1555,7 +1555,7 @@
     <t>OUT_TACH</t>
   </si>
   <si>
-    <t>Q16.D_2; R38.1</t>
+    <t>R38.1; U17.D_6</t>
   </si>
   <si>
     <t>A24</t>
@@ -1612,7 +1612,7 @@
     <t>OUT_VVT_RH-</t>
   </si>
   <si>
-    <t>Q10.D_2</t>
+    <t>U14.D_6</t>
   </si>
   <si>
     <t>A29</t>
@@ -1624,7 +1624,7 @@
     <t>OUT_VVT_LH-</t>
   </si>
   <si>
-    <t>Q11.D_2</t>
+    <t>U15.D_8</t>
   </si>
   <si>
     <t>A30</t>
@@ -1648,7 +1648,7 @@
     <t>OUT_WG</t>
   </si>
   <si>
-    <t>Q9.D_2</t>
+    <t>U14.D_8</t>
   </si>
   <si>
     <t>A33</t>
